--- a/Treinamento/IndexacaoFG/Arquivos/Relatório de Recusas 17.12.2025 a 24.12.2025.xlsx
+++ b/Treinamento/IndexacaoFG/Arquivos/Relatório de Recusas 17.12.2025 a 24.12.2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms.sharepoint.com/teams/BR0010-4356589/Shared Documents/BACK-OFFICE SME/Santander/2025/Relatório de Recusas/05. Maio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DEC43E0D-EF42-4E0F-A050-57D18E0FCC18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CFBB6B4F-67C8-41DD-BD54-C6A263512A42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19530" windowHeight="9780" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19530" windowHeight="9780" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="17.12" sheetId="2" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="589" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="753" uniqueCount="248">
   <si>
     <t>SEGURADORA</t>
   </si>
@@ -671,6 +671,190 @@
   </si>
   <si>
     <t xml:space="preserve">LUCAS ISOPPO                                 </t>
+  </si>
+  <si>
+    <t>REDE HIPER DOCE RODOVIARIA II COMERCIO LTDA ME CPF- 26202569000123</t>
+  </si>
+  <si>
+    <t>Chassi irregular, favor corrigir</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JERMESSON ODELY SANTOS PEREIRA               </t>
+  </si>
+  <si>
+    <t>Nup- Cancelamento 19.12.2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ELISANGELA LEAL                              </t>
+  </si>
+  <si>
+    <t>Falta de vistoria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W R CONSTRUCOES E SERVICOS LTDA ME           </t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUCIVANE PEREIRA DE OLIVEIRA                 </t>
+  </si>
+  <si>
+    <t>FRUSTRADO, PRAZO PARA REENVIO EXPIRADO. FOTOS NÃO CORRIGIDAS: Painel com carro ligado (VEICULO DESLIGADO), Chassi (NUMEROS ILEGIVEIS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GILSON MANGABA VALERIANO                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">FRUSTRADO CLIENTE NÃO CORRIGIU AS FOTOS INCORRETAS - PRAZO EXPIRADO FOTOS INCORRETAS: Frente e lateral do passageiro, Painel. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">KLEBER ROBERTO ZACARIAS                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">HERIBERTO CARVALHO DO COUTO NETO             </t>
+  </si>
+  <si>
+    <t xml:space="preserve">***FRUSTRADO**CLIENTE NÃO CORRIGIU AS FOTOS INCORRETAS - PRAZO EXPIRADO Chassi - local incorreto. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">EVERTON BRAGA VIEIRA                         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RENATA RODRIGUES MENDONCA                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">EMANUELLE RODRIGUES FURTADO                  </t>
+  </si>
+  <si>
+    <t>FRUSTRADO, PRAZO PARA REENVIO EXPIRADO. FOTOS NÃO CORRIGIDAS: Chassi (LOCAL INCORRETO)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALEXANDRE COURTES SINIGOI                    </t>
+  </si>
+  <si>
+    <t>Fotos que tiveram repique: Documento da moto, Painel com a motocicleta ligada (VEICULO DESLIGADO) PARA-LAMA DIANT. ARR. (1) TRAS. LAT. DIR. ARR. (1) ESCAP. ARR. (1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUIZ FERNANDO DE CASTRO                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CARLOS ROBERTO MARQUES                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">GREYCIANE MOUTINHO MENDONCA                  </t>
+  </si>
+  <si>
+    <t>Conforme CBE houve sinistro na apólice anterior, portanto a renova
+ção correta é externa COM sinistro, conforme regra diminui uma cla
+sse debônus, assim sendo o correto bônus 9. &lt;br&gt;Com a correção f
+icou 10x R$ 206,76. Podemos emitir desta forma?</t>
+  </si>
+  <si>
+    <t>ECO COM SERVICOS CLIMATIZADORES CONDICIONADOR</t>
+  </si>
+  <si>
+    <t>FRUSTRADO *PRAZO EXP * SEGURADO N CORRIGIU OS PASSOS SOLICITADOS repique: Porta malas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS SERVICOS DE CONSTRUCOES E TRANSPORTE LTDA </t>
+  </si>
+  <si>
+    <t>FRUSTRADO * repique: Frente e lateral do passageiro, Traseira e lateral do motorista, Chassi, Frente e lateral do motorista, Traseira e lateral do passageiro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOARA CHAGAS DA SILVA BARRETO                </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLAYTON ANDERSON LOPES MATA                  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">FRUSTRADO, PRAZO PARA REENVIO EXPIRADO. FOTOS NÃO CORRIGIDAS: Frente e lateral do passageiro, Traseira e lateral do passageiro (NAO TIROU FOTO), Painel com carro ligado, (VEICULO DESLIGADO) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RONALD JESUS DOS PASSOS                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUCIANA LIMA MOURA GONCALVES                 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALVARO AMORIM BASTOS                         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SIMONE MARQUES LOPES                         </t>
+  </si>
+  <si>
+    <t>FRUSTADO. RECUSA: CLIENTE NÃO CONCLUIU A FOTO DENTRO DO PRAZO. FOTO INCORRETA: Frente e lateral do motorista. CHASSI, FRENTE E LATERAL DO PASSAGEIRO E FRENTE E LATERAL DO MOTORISTA.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GUSTAVO GONCALVES DA SILVA                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALQUIRIA PROCOPIO                           </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PERICLES LIMA DE SOUSA                       </t>
+  </si>
+  <si>
+    <t>RECUSA: repique: Painel com carro desligado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EDSON VANDERLEI SAVIAN                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">GISLAINE MAGALHAES AGOSTINHO                 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMAURILIO MOISES QUIRINO DOS SANTOS          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">EDSON SEIZO MORI                             </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROBERTA SANTOS DE ALMEIDA                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLIENTE NÃO CORRIGIU AS FOTOS INCORRETAS - PRAZO EXPIRADO FOTO INCORRETA: Frente e lateral do passageiro, Porta malas aberto, Chassi, Frente e lateral do motorista, Motor e placa </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARIA ENILDA MIRANDA DOS SANTOS              </t>
+  </si>
+  <si>
+    <t>Favor enviar cópia completa d
+a apólice anterior 2024/2025.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUIZ JONAS FRANCISCO DOS SANTOS              </t>
+  </si>
+  <si>
+    <t xml:space="preserve">NAUAN FELIPE DA SILVA                        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">GILBERTO SOARES ARAUJO                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARIA MADALENA MORAIS DA COSTA               </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JEAN DE ASSIS FERREIRA                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">NMAP TELECOM LTDA EPP                        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUCAS CARDOSO PINHEIRO                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">HENRIQUE LAFAETE DA SILVA BARROS             </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALESSANDRA BLAESSING                         </t>
+  </si>
+  <si>
+    <t>J E PARQUE DE DIVERSAO PRINCESA DO AGRESTE LT</t>
+  </si>
+  <si>
+    <t>LUIZ CARLOS SIMONETTI PIRES CPF 84097191934</t>
+  </si>
+  <si>
+    <t>Chassi irregular</t>
   </si>
 </sst>
 </file>
@@ -735,7 +919,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="17">
+  <borders count="18">
     <border>
       <left/>
       <right/>
@@ -945,12 +1129,23 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="80">
+  <cellXfs count="81">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -993,9 +1188,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -1030,13 +1222,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1139,10 +1327,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -1152,9 +1336,25 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1560,25 +1760,25 @@
       <c r="B2" s="7">
         <v>45996</v>
       </c>
-      <c r="C2" s="24">
+      <c r="C2" s="23">
         <v>46008</v>
       </c>
-      <c r="D2" s="63">
+      <c r="D2" s="58">
         <v>135855706</v>
       </c>
-      <c r="E2" s="63">
+      <c r="E2" s="58">
         <v>3450175476</v>
       </c>
-      <c r="F2" s="67" t="s">
+      <c r="F2" s="62" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="41" t="s">
+      <c r="G2" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="44" t="s">
+      <c r="H2" s="39" t="s">
         <v>12</v>
       </c>
-      <c r="I2" s="43"/>
+      <c r="I2" s="38"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
@@ -1587,25 +1787,25 @@
       <c r="B3" s="7">
         <v>45996</v>
       </c>
-      <c r="C3" s="24">
+      <c r="C3" s="23">
         <v>46008</v>
       </c>
-      <c r="D3" s="65" t="s">
+      <c r="D3" s="60" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="66">
+      <c r="E3" s="61">
         <v>3450175498</v>
       </c>
-      <c r="F3" s="68" t="s">
+      <c r="F3" s="63" t="s">
         <v>10</v>
       </c>
-      <c r="G3" s="41" t="s">
+      <c r="G3" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="H3" s="44" t="s">
+      <c r="H3" s="39" t="s">
         <v>12</v>
       </c>
-      <c r="I3" s="43"/>
+      <c r="I3" s="38"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
@@ -1614,10 +1814,10 @@
       <c r="B4" s="7">
         <v>45995</v>
       </c>
-      <c r="C4" s="24">
+      <c r="C4" s="23">
         <v>46008</v>
       </c>
-      <c r="D4" s="22">
+      <c r="D4" s="21">
         <v>135684911</v>
       </c>
       <c r="E4" s="17">
@@ -1626,13 +1826,13 @@
       <c r="F4" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="G4" s="64" t="s">
+      <c r="G4" s="59" t="s">
         <v>15</v>
       </c>
-      <c r="H4" s="44" t="s">
+      <c r="H4" s="39" t="s">
         <v>16</v>
       </c>
-      <c r="I4" s="43">
+      <c r="I4" s="38">
         <v>45999</v>
       </c>
     </row>
@@ -1643,10 +1843,10 @@
       <c r="B5" s="7">
         <v>45995</v>
       </c>
-      <c r="C5" s="24">
+      <c r="C5" s="23">
         <v>46008</v>
       </c>
-      <c r="D5" s="22">
+      <c r="D5" s="21">
         <v>135700820</v>
       </c>
       <c r="E5" s="17">
@@ -1655,13 +1855,13 @@
       <c r="F5" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="G5" s="64" t="s">
+      <c r="G5" s="59" t="s">
         <v>15</v>
       </c>
-      <c r="H5" s="44" t="s">
+      <c r="H5" s="39" t="s">
         <v>18</v>
       </c>
-      <c r="I5" s="43">
+      <c r="I5" s="38">
         <v>46000</v>
       </c>
     </row>
@@ -1672,10 +1872,10 @@
       <c r="B6" s="7">
         <v>46000</v>
       </c>
-      <c r="C6" s="24">
+      <c r="C6" s="23">
         <v>46008</v>
       </c>
-      <c r="D6" s="22">
+      <c r="D6" s="21">
         <v>135702760</v>
       </c>
       <c r="E6" s="17">
@@ -1684,13 +1884,13 @@
       <c r="F6" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="G6" s="64" t="s">
+      <c r="G6" s="59" t="s">
         <v>15</v>
       </c>
-      <c r="H6" s="44" t="s">
+      <c r="H6" s="39" t="s">
         <v>16</v>
       </c>
-      <c r="I6" s="43">
+      <c r="I6" s="38">
         <v>46000</v>
       </c>
     </row>
@@ -1701,10 +1901,10 @@
       <c r="B7" s="7">
         <v>46001</v>
       </c>
-      <c r="C7" s="24">
+      <c r="C7" s="23">
         <v>46008</v>
       </c>
-      <c r="D7" s="22">
+      <c r="D7" s="21">
         <v>135783562</v>
       </c>
       <c r="E7" s="17">
@@ -1713,13 +1913,13 @@
       <c r="F7" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="G7" s="64" t="s">
+      <c r="G7" s="59" t="s">
         <v>21</v>
       </c>
-      <c r="H7" s="45" t="s">
+      <c r="H7" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="I7" s="43">
+      <c r="I7" s="38">
         <v>46001</v>
       </c>
     </row>
@@ -1730,10 +1930,10 @@
       <c r="B8" s="7">
         <v>46002</v>
       </c>
-      <c r="C8" s="24">
+      <c r="C8" s="23">
         <v>46008</v>
       </c>
-      <c r="D8" s="22">
+      <c r="D8" s="21">
         <v>135816367</v>
       </c>
       <c r="E8" s="17">
@@ -1742,13 +1942,13 @@
       <c r="F8" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="G8" s="64" t="s">
+      <c r="G8" s="59" t="s">
         <v>21</v>
       </c>
-      <c r="H8" s="45" t="s">
+      <c r="H8" s="40" t="s">
         <v>24</v>
       </c>
-      <c r="I8" s="43">
+      <c r="I8" s="38">
         <v>46002</v>
       </c>
     </row>
@@ -1759,10 +1959,10 @@
       <c r="B9" s="7">
         <v>46002</v>
       </c>
-      <c r="C9" s="24">
+      <c r="C9" s="23">
         <v>46008</v>
       </c>
-      <c r="D9" s="22">
+      <c r="D9" s="21">
         <v>135815893</v>
       </c>
       <c r="E9" s="17">
@@ -1771,13 +1971,13 @@
       <c r="F9" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="G9" s="64" t="s">
+      <c r="G9" s="59" t="s">
         <v>21</v>
       </c>
-      <c r="H9" s="44" t="s">
+      <c r="H9" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="I9" s="43">
+      <c r="I9" s="38">
         <v>46002</v>
       </c>
     </row>
@@ -1788,10 +1988,10 @@
       <c r="B10" s="7">
         <v>46002</v>
       </c>
-      <c r="C10" s="24">
+      <c r="C10" s="23">
         <v>46008</v>
       </c>
-      <c r="D10" s="22">
+      <c r="D10" s="21">
         <v>135805130</v>
       </c>
       <c r="E10" s="17">
@@ -1800,13 +2000,13 @@
       <c r="F10" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="G10" s="64" t="s">
+      <c r="G10" s="59" t="s">
         <v>21</v>
       </c>
-      <c r="H10" s="44" t="s">
+      <c r="H10" s="39" t="s">
         <v>28</v>
       </c>
-      <c r="I10" s="43">
+      <c r="I10" s="38">
         <v>46002</v>
       </c>
     </row>
@@ -1817,10 +2017,10 @@
       <c r="B11" s="7">
         <v>46002</v>
       </c>
-      <c r="C11" s="24">
+      <c r="C11" s="23">
         <v>46008</v>
       </c>
-      <c r="D11" s="22">
+      <c r="D11" s="21">
         <v>135808542</v>
       </c>
       <c r="E11" s="17">
@@ -1829,13 +2029,13 @@
       <c r="F11" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="G11" s="64" t="s">
+      <c r="G11" s="59" t="s">
         <v>21</v>
       </c>
-      <c r="H11" s="44" t="s">
+      <c r="H11" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="I11" s="43">
+      <c r="I11" s="38">
         <v>46002</v>
       </c>
     </row>
@@ -1846,10 +2046,10 @@
       <c r="B12" s="7">
         <v>46002</v>
       </c>
-      <c r="C12" s="24">
+      <c r="C12" s="23">
         <v>46008</v>
       </c>
-      <c r="D12" s="22">
+      <c r="D12" s="21">
         <v>135809133</v>
       </c>
       <c r="E12" s="17">
@@ -1858,13 +2058,13 @@
       <c r="F12" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="G12" s="64" t="s">
+      <c r="G12" s="59" t="s">
         <v>21</v>
       </c>
-      <c r="H12" s="44" t="s">
+      <c r="H12" s="39" t="s">
         <v>32</v>
       </c>
-      <c r="I12" s="43">
+      <c r="I12" s="38">
         <v>46002</v>
       </c>
     </row>
@@ -1875,10 +2075,10 @@
       <c r="B13" s="7">
         <v>46000</v>
       </c>
-      <c r="C13" s="24">
+      <c r="C13" s="23">
         <v>46008</v>
       </c>
-      <c r="D13" s="22">
+      <c r="D13" s="21">
         <v>135828439</v>
       </c>
       <c r="E13" s="17">
@@ -1887,13 +2087,13 @@
       <c r="F13" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="G13" s="64" t="s">
+      <c r="G13" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="H13" s="44" t="s">
+      <c r="H13" s="39" t="s">
         <v>34</v>
       </c>
-      <c r="I13" s="43">
+      <c r="I13" s="38">
         <v>46007</v>
       </c>
     </row>
@@ -1904,10 +2104,10 @@
       <c r="B14" s="7">
         <v>46002</v>
       </c>
-      <c r="C14" s="24">
+      <c r="C14" s="23">
         <v>46008</v>
       </c>
-      <c r="D14" s="22">
+      <c r="D14" s="21">
         <v>135839030</v>
       </c>
       <c r="E14" s="17">
@@ -1916,13 +2116,13 @@
       <c r="F14" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="G14" s="64" t="s">
+      <c r="G14" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="H14" s="44" t="s">
+      <c r="H14" s="39" t="s">
         <v>34</v>
       </c>
-      <c r="I14" s="43">
+      <c r="I14" s="38">
         <v>46007</v>
       </c>
     </row>
@@ -1933,10 +2133,10 @@
       <c r="B15" s="7">
         <v>46003</v>
       </c>
-      <c r="C15" s="24">
+      <c r="C15" s="23">
         <v>46008</v>
       </c>
-      <c r="D15" s="22">
+      <c r="D15" s="21">
         <v>135843288</v>
       </c>
       <c r="E15" s="17">
@@ -1945,13 +2145,13 @@
       <c r="F15" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="G15" s="64" t="s">
+      <c r="G15" s="59" t="s">
         <v>37</v>
       </c>
-      <c r="H15" s="44" t="s">
+      <c r="H15" s="39" t="s">
         <v>38</v>
       </c>
-      <c r="I15" s="43">
+      <c r="I15" s="38">
         <v>46003</v>
       </c>
     </row>
@@ -1962,10 +2162,10 @@
       <c r="B16" s="7">
         <v>45998</v>
       </c>
-      <c r="C16" s="24">
+      <c r="C16" s="23">
         <v>46008</v>
       </c>
-      <c r="D16" s="22">
+      <c r="D16" s="21">
         <v>135742047</v>
       </c>
       <c r="E16" s="17">
@@ -1974,13 +2174,13 @@
       <c r="F16" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="G16" s="64" t="s">
+      <c r="G16" s="59" t="s">
         <v>40</v>
       </c>
-      <c r="H16" s="44" t="s">
+      <c r="H16" s="39" t="s">
         <v>41</v>
       </c>
-      <c r="I16" s="43">
+      <c r="I16" s="38">
         <v>45998</v>
       </c>
     </row>
@@ -1991,10 +2191,10 @@
       <c r="B17" s="7">
         <v>46002</v>
       </c>
-      <c r="C17" s="24">
+      <c r="C17" s="23">
         <v>46008</v>
       </c>
-      <c r="D17" s="22">
+      <c r="D17" s="21">
         <v>135822642</v>
       </c>
       <c r="E17" s="17">
@@ -2003,13 +2203,13 @@
       <c r="F17" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="G17" s="64" t="s">
+      <c r="G17" s="59" t="s">
         <v>21</v>
       </c>
-      <c r="H17" s="44" t="s">
+      <c r="H17" s="39" t="s">
         <v>43</v>
       </c>
-      <c r="I17" s="43">
+      <c r="I17" s="38">
         <v>46002</v>
       </c>
     </row>
@@ -2020,10 +2220,10 @@
       <c r="B18" s="7">
         <v>46002</v>
       </c>
-      <c r="C18" s="24">
+      <c r="C18" s="23">
         <v>46008</v>
       </c>
-      <c r="D18" s="22">
+      <c r="D18" s="21">
         <v>135815124</v>
       </c>
       <c r="E18" s="17">
@@ -2032,13 +2232,13 @@
       <c r="F18" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="G18" s="64" t="s">
+      <c r="G18" s="59" t="s">
         <v>21</v>
       </c>
-      <c r="H18" s="44" t="s">
+      <c r="H18" s="39" t="s">
         <v>45</v>
       </c>
-      <c r="I18" s="43">
+      <c r="I18" s="38">
         <v>46002</v>
       </c>
     </row>
@@ -2049,10 +2249,10 @@
       <c r="B19" s="7">
         <v>46002</v>
       </c>
-      <c r="C19" s="24">
+      <c r="C19" s="23">
         <v>46008</v>
       </c>
-      <c r="D19" s="22">
+      <c r="D19" s="21">
         <v>135808917</v>
       </c>
       <c r="E19" s="17">
@@ -2061,13 +2261,13 @@
       <c r="F19" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="G19" s="64" t="s">
+      <c r="G19" s="59" t="s">
         <v>21</v>
       </c>
-      <c r="H19" s="44" t="s">
+      <c r="H19" s="39" t="s">
         <v>47</v>
       </c>
-      <c r="I19" s="43">
+      <c r="I19" s="38">
         <v>46002</v>
       </c>
     </row>
@@ -2078,10 +2278,10 @@
       <c r="B20" s="7">
         <v>46001</v>
       </c>
-      <c r="C20" s="24">
+      <c r="C20" s="23">
         <v>46008</v>
       </c>
-      <c r="D20" s="22">
+      <c r="D20" s="21">
         <v>135788041</v>
       </c>
       <c r="E20" s="17">
@@ -2090,13 +2290,13 @@
       <c r="F20" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="G20" s="64" t="s">
+      <c r="G20" s="59" t="s">
         <v>37</v>
       </c>
-      <c r="H20" s="44" t="s">
+      <c r="H20" s="39" t="s">
         <v>49</v>
       </c>
-      <c r="I20" s="43">
+      <c r="I20" s="38">
         <v>46001</v>
       </c>
     </row>
@@ -2107,10 +2307,10 @@
       <c r="B21" s="7">
         <v>46001</v>
       </c>
-      <c r="C21" s="24">
+      <c r="C21" s="23">
         <v>46008</v>
       </c>
-      <c r="D21" s="22">
+      <c r="D21" s="21">
         <v>135795377</v>
       </c>
       <c r="E21" s="17">
@@ -2119,13 +2319,13 @@
       <c r="F21" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="G21" s="64" t="s">
+      <c r="G21" s="59" t="s">
         <v>21</v>
       </c>
-      <c r="H21" s="44" t="s">
+      <c r="H21" s="39" t="s">
         <v>51</v>
       </c>
-      <c r="I21" s="43">
+      <c r="I21" s="38">
         <v>46001</v>
       </c>
     </row>
@@ -2136,10 +2336,10 @@
       <c r="B22" s="7">
         <v>46006</v>
       </c>
-      <c r="C22" s="24">
+      <c r="C22" s="23">
         <v>46008</v>
       </c>
-      <c r="D22" s="22">
+      <c r="D22" s="21">
         <v>135865718</v>
       </c>
       <c r="E22" s="17">
@@ -2148,13 +2348,13 @@
       <c r="F22" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="G22" s="64" t="s">
+      <c r="G22" s="59" t="s">
         <v>37</v>
       </c>
-      <c r="H22" s="44" t="s">
+      <c r="H22" s="39" t="s">
         <v>38</v>
       </c>
-      <c r="I22" s="43">
+      <c r="I22" s="38">
         <v>46006</v>
       </c>
     </row>
@@ -2165,10 +2365,10 @@
       <c r="B23" s="7">
         <v>45996</v>
       </c>
-      <c r="C23" s="24">
+      <c r="C23" s="23">
         <v>46008</v>
       </c>
-      <c r="D23" s="22">
+      <c r="D23" s="21">
         <v>135855706</v>
       </c>
       <c r="E23" s="17">
@@ -2177,13 +2377,13 @@
       <c r="F23" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="G23" s="64" t="s">
+      <c r="G23" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="H23" s="44" t="s">
+      <c r="H23" s="39" t="s">
         <v>34</v>
       </c>
-      <c r="I23" s="43">
+      <c r="I23" s="38">
         <v>46007</v>
       </c>
     </row>
@@ -2194,10 +2394,10 @@
       <c r="B24" s="7">
         <v>46005</v>
       </c>
-      <c r="C24" s="24">
+      <c r="C24" s="23">
         <v>46008</v>
       </c>
-      <c r="D24" s="22">
+      <c r="D24" s="21">
         <v>135678729</v>
       </c>
       <c r="E24" s="17">
@@ -2206,13 +2406,13 @@
       <c r="F24" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="G24" s="64" t="s">
+      <c r="G24" s="59" t="s">
         <v>55</v>
       </c>
-      <c r="H24" s="44" t="s">
+      <c r="H24" s="39" t="s">
         <v>56</v>
       </c>
-      <c r="I24" s="43">
+      <c r="I24" s="38">
         <v>45999</v>
       </c>
     </row>
@@ -2223,10 +2423,10 @@
       <c r="B25" s="7">
         <v>46005</v>
       </c>
-      <c r="C25" s="24">
+      <c r="C25" s="23">
         <v>46008</v>
       </c>
-      <c r="D25" s="22">
+      <c r="D25" s="21">
         <v>135709501</v>
       </c>
       <c r="E25" s="17">
@@ -2235,13 +2435,13 @@
       <c r="F25" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="G25" s="64" t="s">
+      <c r="G25" s="59" t="s">
         <v>55</v>
       </c>
-      <c r="H25" s="44" t="s">
+      <c r="H25" s="39" t="s">
         <v>58</v>
       </c>
-      <c r="I25" s="43">
+      <c r="I25" s="38">
         <v>46000</v>
       </c>
     </row>
@@ -2249,13 +2449,13 @@
       <c r="A26" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B26" s="46">
+      <c r="B26" s="41">
         <v>45995</v>
       </c>
-      <c r="C26" s="24">
+      <c r="C26" s="23">
         <v>46008</v>
       </c>
-      <c r="D26" s="22">
+      <c r="D26" s="21">
         <v>135711128</v>
       </c>
       <c r="E26" s="17">
@@ -2264,13 +2464,13 @@
       <c r="F26" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="G26" s="64" t="s">
+      <c r="G26" s="59" t="s">
         <v>60</v>
       </c>
-      <c r="H26" s="44" t="s">
+      <c r="H26" s="39" t="s">
         <v>61</v>
       </c>
-      <c r="I26" s="43">
+      <c r="I26" s="38">
         <v>46000</v>
       </c>
     </row>
@@ -2281,10 +2481,10 @@
       <c r="B27" s="7">
         <v>46001</v>
       </c>
-      <c r="C27" s="24">
+      <c r="C27" s="23">
         <v>46008</v>
       </c>
-      <c r="D27" s="22">
+      <c r="D27" s="21">
         <v>135675077</v>
       </c>
       <c r="E27" s="17">
@@ -2293,13 +2493,13 @@
       <c r="F27" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="G27" s="64" t="s">
+      <c r="G27" s="59" t="s">
         <v>11</v>
       </c>
       <c r="H27" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="I27" s="43">
+      <c r="I27" s="38">
         <v>46007</v>
       </c>
     </row>
@@ -2310,10 +2510,10 @@
       <c r="B28" s="7">
         <v>45995</v>
       </c>
-      <c r="C28" s="24">
+      <c r="C28" s="23">
         <v>46008</v>
       </c>
-      <c r="D28" s="22">
+      <c r="D28" s="21">
         <v>135709015</v>
       </c>
       <c r="E28" s="17">
@@ -2322,13 +2522,13 @@
       <c r="F28" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="G28" s="64" t="s">
+      <c r="G28" s="59" t="s">
         <v>11</v>
       </c>
       <c r="H28" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="I28" s="43">
+      <c r="I28" s="38">
         <v>46007</v>
       </c>
     </row>
@@ -2339,10 +2539,10 @@
       <c r="B29" s="7">
         <v>46001</v>
       </c>
-      <c r="C29" s="24">
+      <c r="C29" s="23">
         <v>46008</v>
       </c>
-      <c r="D29" s="22">
+      <c r="D29" s="21">
         <v>135790179</v>
       </c>
       <c r="E29" s="17">
@@ -2351,13 +2551,13 @@
       <c r="F29" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="G29" s="64" t="s">
+      <c r="G29" s="59" t="s">
         <v>21</v>
       </c>
       <c r="H29" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="I29" s="43">
+      <c r="I29" s="38">
         <v>46001</v>
       </c>
     </row>
@@ -2368,10 +2568,10 @@
       <c r="B30" s="7">
         <v>45999</v>
       </c>
-      <c r="C30" s="24">
+      <c r="C30" s="23">
         <v>46008</v>
       </c>
-      <c r="D30" s="22">
+      <c r="D30" s="21">
         <v>135812863</v>
       </c>
       <c r="E30" s="17">
@@ -2380,13 +2580,13 @@
       <c r="F30" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="G30" s="64" t="s">
+      <c r="G30" s="59" t="s">
         <v>21</v>
       </c>
       <c r="H30" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="I30" s="43">
+      <c r="I30" s="38">
         <v>45999</v>
       </c>
     </row>
@@ -2397,10 +2597,10 @@
       <c r="B31" s="7">
         <v>46002</v>
       </c>
-      <c r="C31" s="24">
+      <c r="C31" s="23">
         <v>46008</v>
       </c>
-      <c r="D31" s="22">
+      <c r="D31" s="21">
         <v>135767899</v>
       </c>
       <c r="E31" s="17">
@@ -2409,13 +2609,13 @@
       <c r="F31" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="G31" s="64" t="s">
+      <c r="G31" s="59" t="s">
         <v>11</v>
       </c>
       <c r="H31" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="I31" s="43">
+      <c r="I31" s="38">
         <v>46007</v>
       </c>
     </row>
@@ -2426,10 +2626,10 @@
       <c r="B32" s="7">
         <v>46011</v>
       </c>
-      <c r="C32" s="24">
+      <c r="C32" s="23">
         <v>46008</v>
       </c>
-      <c r="D32" s="22">
+      <c r="D32" s="21">
         <v>135767580</v>
       </c>
       <c r="E32" s="17">
@@ -2438,13 +2638,13 @@
       <c r="F32" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="G32" s="64" t="s">
+      <c r="G32" s="59" t="s">
         <v>11</v>
       </c>
       <c r="H32" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="I32" s="43">
+      <c r="I32" s="38">
         <v>46007</v>
       </c>
     </row>
@@ -2455,10 +2655,10 @@
       <c r="B33" s="7">
         <v>46000</v>
       </c>
-      <c r="C33" s="24">
+      <c r="C33" s="23">
         <v>46008</v>
       </c>
-      <c r="D33" s="22">
+      <c r="D33" s="21">
         <v>135756056</v>
       </c>
       <c r="E33" s="17">
@@ -2467,13 +2667,13 @@
       <c r="F33" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="G33" s="64" t="s">
+      <c r="G33" s="59" t="s">
         <v>15</v>
       </c>
       <c r="H33" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="I33" s="43">
+      <c r="I33" s="38">
         <v>46002</v>
       </c>
     </row>
@@ -2484,10 +2684,10 @@
       <c r="B34" s="7">
         <v>45995</v>
       </c>
-      <c r="C34" s="24">
+      <c r="C34" s="23">
         <v>46008</v>
       </c>
-      <c r="D34" s="22">
+      <c r="D34" s="21">
         <v>135698156</v>
       </c>
       <c r="E34" s="17">
@@ -2496,13 +2696,13 @@
       <c r="F34" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="G34" s="64" t="s">
+      <c r="G34" s="59" t="s">
         <v>15</v>
       </c>
       <c r="H34" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="I34" s="43">
+      <c r="I34" s="38">
         <v>46000</v>
       </c>
     </row>
@@ -2513,10 +2713,10 @@
       <c r="B35" s="7">
         <v>46006</v>
       </c>
-      <c r="C35" s="24">
+      <c r="C35" s="23">
         <v>46008</v>
       </c>
-      <c r="D35" s="22">
+      <c r="D35" s="21">
         <v>135698933</v>
       </c>
       <c r="E35" s="17">
@@ -2525,13 +2725,13 @@
       <c r="F35" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="G35" s="64" t="s">
+      <c r="G35" s="59" t="s">
         <v>15</v>
       </c>
       <c r="H35" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="I35" s="43">
+      <c r="I35" s="38">
         <v>46000</v>
       </c>
     </row>
@@ -2542,10 +2742,10 @@
       <c r="B36" s="7">
         <v>45997</v>
       </c>
-      <c r="C36" s="24">
+      <c r="C36" s="23">
         <v>46008</v>
       </c>
-      <c r="D36" s="22">
+      <c r="D36" s="21">
         <v>135700316</v>
       </c>
       <c r="E36" s="17">
@@ -2554,13 +2754,13 @@
       <c r="F36" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="G36" s="64" t="s">
+      <c r="G36" s="59" t="s">
         <v>15</v>
       </c>
       <c r="H36" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="I36" s="43">
+      <c r="I36" s="38">
         <v>46000</v>
       </c>
     </row>
@@ -2571,10 +2771,10 @@
       <c r="B37" s="7">
         <v>45998</v>
       </c>
-      <c r="C37" s="24">
+      <c r="C37" s="23">
         <v>46008</v>
       </c>
-      <c r="D37" s="22">
+      <c r="D37" s="21">
         <v>135700772</v>
       </c>
       <c r="E37" s="17">
@@ -2583,13 +2783,13 @@
       <c r="F37" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="G37" s="64" t="s">
+      <c r="G37" s="59" t="s">
         <v>15</v>
       </c>
       <c r="H37" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="I37" s="43">
+      <c r="I37" s="38">
         <v>46000</v>
       </c>
     </row>
@@ -2600,10 +2800,10 @@
       <c r="B38" s="7">
         <v>45997</v>
       </c>
-      <c r="C38" s="24">
+      <c r="C38" s="23">
         <v>46008</v>
       </c>
-      <c r="D38" s="22">
+      <c r="D38" s="21">
         <v>135703412</v>
       </c>
       <c r="E38" s="17">
@@ -2612,13 +2812,13 @@
       <c r="F38" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="G38" s="64" t="s">
+      <c r="G38" s="59" t="s">
         <v>15</v>
       </c>
       <c r="H38" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="I38" s="43">
+      <c r="I38" s="38">
         <v>46000</v>
       </c>
     </row>
@@ -2629,10 +2829,10 @@
       <c r="B39" s="7">
         <v>46001</v>
       </c>
-      <c r="C39" s="24">
+      <c r="C39" s="23">
         <v>46008</v>
       </c>
-      <c r="D39" s="22">
+      <c r="D39" s="21">
         <v>135798895</v>
       </c>
       <c r="E39" s="17">
@@ -2641,13 +2841,13 @@
       <c r="F39" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="G39" s="64" t="s">
+      <c r="G39" s="59" t="s">
         <v>21</v>
       </c>
       <c r="H39" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="I39" s="48">
+      <c r="I39" s="43">
         <v>46001</v>
       </c>
     </row>
@@ -2658,10 +2858,10 @@
       <c r="B40" s="7">
         <v>45995</v>
       </c>
-      <c r="C40" s="24">
+      <c r="C40" s="23">
         <v>46008</v>
       </c>
-      <c r="D40" s="22">
+      <c r="D40" s="21">
         <v>135708156</v>
       </c>
       <c r="E40" s="17">
@@ -2670,25 +2870,25 @@
       <c r="F40" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="G40" s="64" t="s">
+      <c r="G40" s="59" t="s">
         <v>15</v>
       </c>
       <c r="H40" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="I40" s="48">
+      <c r="I40" s="43">
         <v>46000</v>
       </c>
     </row>
     <row r="41" spans="1:9">
       <c r="A41" s="6"/>
       <c r="B41" s="7"/>
-      <c r="C41" s="24"/>
-      <c r="D41" s="22"/>
+      <c r="C41" s="23"/>
+      <c r="D41" s="21"/>
       <c r="E41" s="17"/>
       <c r="F41" s="11"/>
-      <c r="G41" s="64"/>
-      <c r="H41" s="47"/>
+      <c r="G41" s="59"/>
+      <c r="H41" s="42"/>
       <c r="I41" s="12"/>
     </row>
   </sheetData>
@@ -2726,60 +2926,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="50" t="s">
+      <c r="A1" s="45" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="51" t="s">
+      <c r="B1" s="46" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="51" t="s">
+      <c r="C1" s="46" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="52" t="s">
+      <c r="D1" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="52" t="s">
+      <c r="E1" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="50" t="s">
+      <c r="F1" s="45" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="50" t="s">
+      <c r="G1" s="45" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="53" t="s">
+      <c r="H1" s="48" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="50" t="s">
+      <c r="I1" s="45" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="49" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" s="54">
+      <c r="A2" s="44" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="49">
         <v>46000</v>
       </c>
-      <c r="C2" s="55">
+      <c r="C2" s="50">
         <v>46009</v>
       </c>
-      <c r="D2" s="59" t="s">
+      <c r="D2" s="54" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="69">
+      <c r="E2" s="64">
         <v>3450178534</v>
       </c>
-      <c r="F2" s="67" t="s">
+      <c r="F2" s="62" t="s">
         <v>83</v>
       </c>
-      <c r="G2" s="57" t="s">
+      <c r="G2" s="52" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="30" t="s">
+      <c r="H2" s="29" t="s">
         <v>84</v>
       </c>
-      <c r="I2" s="58"/>
+      <c r="I2" s="53"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
@@ -2788,25 +2988,25 @@
       <c r="B3" s="7">
         <v>46002</v>
       </c>
-      <c r="C3" s="55">
+      <c r="C3" s="50">
         <v>46009</v>
       </c>
-      <c r="D3" s="59" t="s">
+      <c r="D3" s="54" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="69">
+      <c r="E3" s="64">
         <v>3450180987</v>
       </c>
-      <c r="F3" s="67" t="s">
+      <c r="F3" s="62" t="s">
         <v>85</v>
       </c>
-      <c r="G3" s="41" t="s">
+      <c r="G3" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="H3" s="30" t="s">
+      <c r="H3" s="29" t="s">
         <v>84</v>
       </c>
-      <c r="I3" s="43"/>
+      <c r="I3" s="38"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
@@ -2815,25 +3015,25 @@
       <c r="B4" s="7">
         <v>46006</v>
       </c>
-      <c r="C4" s="55">
+      <c r="C4" s="50">
         <v>46009</v>
       </c>
-      <c r="D4" s="59" t="s">
+      <c r="D4" s="54" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="63">
+      <c r="E4" s="58">
         <v>3450184892</v>
       </c>
-      <c r="F4" s="67" t="s">
+      <c r="F4" s="62" t="s">
         <v>86</v>
       </c>
-      <c r="G4" s="41" t="s">
+      <c r="G4" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="H4" s="30" t="s">
+      <c r="H4" s="29" t="s">
         <v>84</v>
       </c>
-      <c r="I4" s="43"/>
+      <c r="I4" s="38"/>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="6" t="s">
@@ -2842,25 +3042,25 @@
       <c r="B5" s="7">
         <v>46006</v>
       </c>
-      <c r="C5" s="55">
+      <c r="C5" s="50">
         <v>46009</v>
       </c>
-      <c r="D5" s="70" t="s">
+      <c r="D5" s="65" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="71">
+      <c r="E5" s="66">
         <v>3450185079</v>
       </c>
-      <c r="F5" s="68" t="s">
+      <c r="F5" s="63" t="s">
         <v>86</v>
       </c>
-      <c r="G5" s="41" t="s">
+      <c r="G5" s="36" t="s">
         <v>11</v>
       </c>
       <c r="H5" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="I5" s="43"/>
+      <c r="I5" s="38"/>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="6" t="s">
@@ -2869,10 +3069,10 @@
       <c r="B6" s="7">
         <v>45999</v>
       </c>
-      <c r="C6" s="55">
+      <c r="C6" s="50">
         <v>46009</v>
       </c>
-      <c r="D6" s="22">
+      <c r="D6" s="21">
         <v>135746284</v>
       </c>
       <c r="E6" s="17">
@@ -2881,13 +3081,13 @@
       <c r="F6" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="G6" s="64" t="s">
+      <c r="G6" s="59" t="s">
         <v>40</v>
       </c>
       <c r="H6" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="I6" s="43">
+      <c r="I6" s="38">
         <v>45999</v>
       </c>
     </row>
@@ -2898,10 +3098,10 @@
       <c r="B7" s="7">
         <v>45999</v>
       </c>
-      <c r="C7" s="55">
+      <c r="C7" s="50">
         <v>46009</v>
       </c>
-      <c r="D7" s="22">
+      <c r="D7" s="21">
         <v>135734427</v>
       </c>
       <c r="E7" s="17">
@@ -2910,13 +3110,13 @@
       <c r="F7" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="G7" s="64" t="s">
+      <c r="G7" s="59" t="s">
         <v>15</v>
       </c>
       <c r="H7" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="I7" s="43">
+      <c r="I7" s="38">
         <v>46001</v>
       </c>
     </row>
@@ -2927,10 +3127,10 @@
       <c r="B8" s="7">
         <v>45999</v>
       </c>
-      <c r="C8" s="55">
+      <c r="C8" s="50">
         <v>46009</v>
       </c>
-      <c r="D8" s="22">
+      <c r="D8" s="21">
         <v>135754186</v>
       </c>
       <c r="E8" s="17">
@@ -2939,13 +3139,13 @@
       <c r="F8" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="G8" s="64" t="s">
+      <c r="G8" s="59" t="s">
         <v>40</v>
       </c>
       <c r="H8" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="I8" s="43">
+      <c r="I8" s="38">
         <v>45999</v>
       </c>
     </row>
@@ -2956,10 +3156,10 @@
       <c r="B9" s="7">
         <v>45976</v>
       </c>
-      <c r="C9" s="55">
+      <c r="C9" s="50">
         <v>46009</v>
       </c>
-      <c r="D9" s="22">
+      <c r="D9" s="21">
         <v>135748063</v>
       </c>
       <c r="E9" s="17">
@@ -2968,13 +3168,13 @@
       <c r="F9" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="G9" s="64" t="s">
+      <c r="G9" s="59" t="s">
         <v>40</v>
       </c>
       <c r="H9" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="I9" s="43">
+      <c r="I9" s="38">
         <v>46006</v>
       </c>
     </row>
@@ -2985,10 +3185,10 @@
       <c r="B10" s="7">
         <v>45999</v>
       </c>
-      <c r="C10" s="55">
+      <c r="C10" s="50">
         <v>46009</v>
       </c>
-      <c r="D10" s="22">
+      <c r="D10" s="21">
         <v>135756398</v>
       </c>
       <c r="E10" s="17">
@@ -2997,13 +3197,13 @@
       <c r="F10" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="G10" s="64" t="s">
+      <c r="G10" s="59" t="s">
         <v>40</v>
       </c>
       <c r="H10" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="I10" s="43">
+      <c r="I10" s="38">
         <v>45999</v>
       </c>
     </row>
@@ -3014,10 +3214,10 @@
       <c r="B11" s="7">
         <v>46000</v>
       </c>
-      <c r="C11" s="55">
+      <c r="C11" s="50">
         <v>46009</v>
       </c>
-      <c r="D11" s="22">
+      <c r="D11" s="21">
         <v>135774211</v>
       </c>
       <c r="E11" s="17">
@@ -3026,13 +3226,13 @@
       <c r="F11" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="G11" s="64" t="s">
+      <c r="G11" s="59" t="s">
         <v>11</v>
       </c>
       <c r="H11" s="12" t="s">
         <v>93</v>
       </c>
-      <c r="I11" s="43">
+      <c r="I11" s="38">
         <v>46003</v>
       </c>
     </row>
@@ -3043,10 +3243,10 @@
       <c r="B12" s="7">
         <v>46001</v>
       </c>
-      <c r="C12" s="55">
+      <c r="C12" s="50">
         <v>46009</v>
       </c>
-      <c r="D12" s="22">
+      <c r="D12" s="21">
         <v>135792516</v>
       </c>
       <c r="E12" s="17">
@@ -3055,13 +3255,13 @@
       <c r="F12" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="G12" s="64" t="s">
+      <c r="G12" s="59" t="s">
         <v>11</v>
       </c>
       <c r="H12" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="I12" s="43">
+      <c r="I12" s="38">
         <v>46008</v>
       </c>
     </row>
@@ -3072,10 +3272,10 @@
       <c r="B13" s="7">
         <v>45999</v>
       </c>
-      <c r="C13" s="55">
+      <c r="C13" s="50">
         <v>46009</v>
       </c>
-      <c r="D13" s="22">
+      <c r="D13" s="21">
         <v>135824778</v>
       </c>
       <c r="E13" s="17">
@@ -3084,13 +3284,13 @@
       <c r="F13" s="11" t="s">
         <v>95</v>
       </c>
-      <c r="G13" s="64" t="s">
+      <c r="G13" s="59" t="s">
         <v>21</v>
       </c>
       <c r="H13" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="I13" s="43">
+      <c r="I13" s="38">
         <v>45999</v>
       </c>
     </row>
@@ -3101,10 +3301,10 @@
       <c r="B14" s="7">
         <v>46003</v>
       </c>
-      <c r="C14" s="55">
+      <c r="C14" s="50">
         <v>46009</v>
       </c>
-      <c r="D14" s="22">
+      <c r="D14" s="21">
         <v>135826371</v>
       </c>
       <c r="E14" s="17">
@@ -3113,13 +3313,13 @@
       <c r="F14" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="G14" s="64" t="s">
+      <c r="G14" s="59" t="s">
         <v>21</v>
       </c>
       <c r="H14" s="12" t="s">
         <v>98</v>
       </c>
-      <c r="I14" s="43">
+      <c r="I14" s="38">
         <v>46003</v>
       </c>
     </row>
@@ -3130,10 +3330,10 @@
       <c r="B15" s="7">
         <v>46003</v>
       </c>
-      <c r="C15" s="55">
+      <c r="C15" s="50">
         <v>46009</v>
       </c>
-      <c r="D15" s="22">
+      <c r="D15" s="21">
         <v>135842081</v>
       </c>
       <c r="E15" s="17">
@@ -3142,13 +3342,13 @@
       <c r="F15" s="11" t="s">
         <v>99</v>
       </c>
-      <c r="G15" s="64" t="s">
+      <c r="G15" s="59" t="s">
         <v>21</v>
       </c>
       <c r="H15" s="12" t="s">
         <v>100</v>
       </c>
-      <c r="I15" s="43">
+      <c r="I15" s="38">
         <v>46003</v>
       </c>
     </row>
@@ -3159,10 +3359,10 @@
       <c r="B16" s="7">
         <v>46003</v>
       </c>
-      <c r="C16" s="55">
+      <c r="C16" s="50">
         <v>46009</v>
       </c>
-      <c r="D16" s="22">
+      <c r="D16" s="21">
         <v>135841199</v>
       </c>
       <c r="E16" s="17">
@@ -3171,13 +3371,13 @@
       <c r="F16" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="G16" s="64" t="s">
+      <c r="G16" s="59" t="s">
         <v>21</v>
       </c>
       <c r="H16" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="I16" s="43">
+      <c r="I16" s="38">
         <v>46003</v>
       </c>
     </row>
@@ -3188,10 +3388,10 @@
       <c r="B17" s="7">
         <v>46003</v>
       </c>
-      <c r="C17" s="55">
+      <c r="C17" s="50">
         <v>46009</v>
       </c>
-      <c r="D17" s="22">
+      <c r="D17" s="21">
         <v>135843448</v>
       </c>
       <c r="E17" s="17">
@@ -3200,13 +3400,13 @@
       <c r="F17" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="G17" s="64" t="s">
+      <c r="G17" s="59" t="s">
         <v>37</v>
       </c>
       <c r="H17" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="I17" s="43">
+      <c r="I17" s="38">
         <v>46003</v>
       </c>
     </row>
@@ -3217,10 +3417,10 @@
       <c r="B18" s="7">
         <v>46003</v>
       </c>
-      <c r="C18" s="55">
+      <c r="C18" s="50">
         <v>46009</v>
       </c>
-      <c r="D18" s="22">
+      <c r="D18" s="21">
         <v>135832589</v>
       </c>
       <c r="E18" s="17">
@@ -3229,13 +3429,13 @@
       <c r="F18" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="G18" s="64" t="s">
+      <c r="G18" s="59" t="s">
         <v>21</v>
       </c>
       <c r="H18" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="I18" s="43">
+      <c r="I18" s="38">
         <v>46003</v>
       </c>
     </row>
@@ -3246,10 +3446,10 @@
       <c r="B19" s="7">
         <v>46003</v>
       </c>
-      <c r="C19" s="55">
+      <c r="C19" s="50">
         <v>46009</v>
       </c>
-      <c r="D19" s="22">
+      <c r="D19" s="21">
         <v>135838725</v>
       </c>
       <c r="E19" s="17">
@@ -3258,13 +3458,13 @@
       <c r="F19" s="11" t="s">
         <v>105</v>
       </c>
-      <c r="G19" s="64" t="s">
+      <c r="G19" s="59" t="s">
         <v>21</v>
       </c>
       <c r="H19" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="I19" s="43">
+      <c r="I19" s="38">
         <v>46003</v>
       </c>
     </row>
@@ -3275,10 +3475,10 @@
       <c r="B20" s="7">
         <v>46003</v>
       </c>
-      <c r="C20" s="55">
+      <c r="C20" s="50">
         <v>46009</v>
       </c>
-      <c r="D20" s="22">
+      <c r="D20" s="21">
         <v>135845288</v>
       </c>
       <c r="E20" s="17">
@@ -3287,13 +3487,13 @@
       <c r="F20" s="11" t="s">
         <v>107</v>
       </c>
-      <c r="G20" s="64" t="s">
+      <c r="G20" s="59" t="s">
         <v>21</v>
       </c>
       <c r="H20" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="I20" s="43">
+      <c r="I20" s="38">
         <v>46003</v>
       </c>
     </row>
@@ -3304,10 +3504,10 @@
       <c r="B21" s="7">
         <v>46003</v>
       </c>
-      <c r="C21" s="55">
+      <c r="C21" s="50">
         <v>46009</v>
       </c>
-      <c r="D21" s="22">
+      <c r="D21" s="21">
         <v>135843233</v>
       </c>
       <c r="E21" s="17">
@@ -3316,13 +3516,13 @@
       <c r="F21" s="11" t="s">
         <v>109</v>
       </c>
-      <c r="G21" s="64" t="s">
+      <c r="G21" s="59" t="s">
         <v>21</v>
       </c>
       <c r="H21" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="I21" s="43">
+      <c r="I21" s="38">
         <v>46003</v>
       </c>
     </row>
@@ -3333,10 +3533,10 @@
       <c r="B22" s="7">
         <v>46003</v>
       </c>
-      <c r="C22" s="55">
+      <c r="C22" s="50">
         <v>46009</v>
       </c>
-      <c r="D22" s="22">
+      <c r="D22" s="21">
         <v>135827636</v>
       </c>
       <c r="E22" s="17">
@@ -3345,13 +3545,13 @@
       <c r="F22" s="11" t="s">
         <v>111</v>
       </c>
-      <c r="G22" s="64" t="s">
+      <c r="G22" s="59" t="s">
         <v>21</v>
       </c>
       <c r="H22" s="12" t="s">
         <v>112</v>
       </c>
-      <c r="I22" s="43">
+      <c r="I22" s="38">
         <v>46003</v>
       </c>
     </row>
@@ -3362,10 +3562,10 @@
       <c r="B23" s="7">
         <v>46003</v>
       </c>
-      <c r="C23" s="55">
+      <c r="C23" s="50">
         <v>46009</v>
       </c>
-      <c r="D23" s="22">
+      <c r="D23" s="21">
         <v>135841511</v>
       </c>
       <c r="E23" s="17">
@@ -3374,13 +3574,13 @@
       <c r="F23" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="G23" s="64" t="s">
+      <c r="G23" s="59" t="s">
         <v>21</v>
       </c>
       <c r="H23" s="12" t="s">
         <v>114</v>
       </c>
-      <c r="I23" s="43">
+      <c r="I23" s="38">
         <v>46003</v>
       </c>
     </row>
@@ -3391,10 +3591,10 @@
       <c r="B24" s="7">
         <v>46000</v>
       </c>
-      <c r="C24" s="55">
+      <c r="C24" s="50">
         <v>46009</v>
       </c>
-      <c r="D24" s="22">
+      <c r="D24" s="21">
         <v>135827103</v>
       </c>
       <c r="E24" s="17">
@@ -3403,13 +3603,13 @@
       <c r="F24" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="G24" s="64" t="s">
+      <c r="G24" s="59" t="s">
         <v>21</v>
       </c>
       <c r="H24" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="I24" s="43">
+      <c r="I24" s="38">
         <v>46000</v>
       </c>
     </row>
@@ -3420,10 +3620,10 @@
       <c r="B25" s="7">
         <v>46003</v>
       </c>
-      <c r="C25" s="55">
+      <c r="C25" s="50">
         <v>46009</v>
       </c>
-      <c r="D25" s="22">
+      <c r="D25" s="21">
         <v>135830047</v>
       </c>
       <c r="E25" s="17">
@@ -3432,13 +3632,13 @@
       <c r="F25" s="11" t="s">
         <v>117</v>
       </c>
-      <c r="G25" s="64" t="s">
+      <c r="G25" s="59" t="s">
         <v>21</v>
       </c>
       <c r="H25" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="I25" s="43">
+      <c r="I25" s="38">
         <v>46003</v>
       </c>
     </row>
@@ -3449,10 +3649,10 @@
       <c r="B26" s="7">
         <v>46003</v>
       </c>
-      <c r="C26" s="55">
+      <c r="C26" s="50">
         <v>46009</v>
       </c>
-      <c r="D26" s="22">
+      <c r="D26" s="21">
         <v>135830570</v>
       </c>
       <c r="E26" s="17">
@@ -3461,13 +3661,13 @@
       <c r="F26" s="11" t="s">
         <v>119</v>
       </c>
-      <c r="G26" s="64" t="s">
+      <c r="G26" s="59" t="s">
         <v>21</v>
       </c>
       <c r="H26" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="I26" s="43">
+      <c r="I26" s="38">
         <v>46003</v>
       </c>
     </row>
@@ -3478,10 +3678,10 @@
       <c r="B27" s="7">
         <v>46002</v>
       </c>
-      <c r="C27" s="55">
+      <c r="C27" s="50">
         <v>46009</v>
       </c>
-      <c r="D27" s="22">
+      <c r="D27" s="21">
         <v>135807456</v>
       </c>
       <c r="E27" s="17">
@@ -3490,13 +3690,13 @@
       <c r="F27" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="G27" s="64" t="s">
+      <c r="G27" s="59" t="s">
         <v>21</v>
       </c>
       <c r="H27" s="12" t="s">
         <v>121</v>
       </c>
-      <c r="I27" s="43">
+      <c r="I27" s="38">
         <v>46002</v>
       </c>
     </row>
@@ -3507,10 +3707,10 @@
       <c r="B28" s="7">
         <v>46008</v>
       </c>
-      <c r="C28" s="55">
+      <c r="C28" s="50">
         <v>46009</v>
       </c>
-      <c r="D28" s="22">
+      <c r="D28" s="21">
         <v>135904291</v>
       </c>
       <c r="E28" s="17">
@@ -3519,13 +3719,13 @@
       <c r="F28" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="G28" s="64" t="s">
+      <c r="G28" s="59" t="s">
         <v>37</v>
       </c>
       <c r="H28" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="I28" s="43">
+      <c r="I28" s="38">
         <v>46008</v>
       </c>
     </row>
@@ -3536,10 +3736,10 @@
       <c r="B29" s="7">
         <v>46008</v>
       </c>
-      <c r="C29" s="55">
+      <c r="C29" s="50">
         <v>46009</v>
       </c>
-      <c r="D29" s="22">
+      <c r="D29" s="21">
         <v>135902313</v>
       </c>
       <c r="E29" s="17">
@@ -3548,13 +3748,13 @@
       <c r="F29" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="G29" s="64" t="s">
+      <c r="G29" s="59" t="s">
         <v>37</v>
       </c>
       <c r="H29" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="I29" s="43">
+      <c r="I29" s="38">
         <v>46008</v>
       </c>
     </row>
@@ -3565,10 +3765,10 @@
       <c r="B30" s="7">
         <v>46002</v>
       </c>
-      <c r="C30" s="55">
+      <c r="C30" s="50">
         <v>46009</v>
       </c>
-      <c r="D30" s="22">
+      <c r="D30" s="21">
         <v>135819352</v>
       </c>
       <c r="E30" s="17">
@@ -3577,13 +3777,13 @@
       <c r="F30" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="G30" s="64" t="s">
+      <c r="G30" s="59" t="s">
         <v>21</v>
       </c>
       <c r="H30" s="12" t="s">
         <v>125</v>
       </c>
-      <c r="I30" s="43">
+      <c r="I30" s="38">
         <v>46002</v>
       </c>
     </row>
@@ -3594,10 +3794,10 @@
       <c r="B31" s="7">
         <v>45996</v>
       </c>
-      <c r="C31" s="55">
+      <c r="C31" s="50">
         <v>46009</v>
       </c>
-      <c r="D31" s="22">
+      <c r="D31" s="21">
         <v>135723618</v>
       </c>
       <c r="E31" s="17">
@@ -3606,13 +3806,13 @@
       <c r="F31" s="11" t="s">
         <v>126</v>
       </c>
-      <c r="G31" s="64" t="s">
+      <c r="G31" s="59" t="s">
         <v>15</v>
       </c>
       <c r="H31" s="12" t="s">
         <v>127</v>
       </c>
-      <c r="I31" s="43">
+      <c r="I31" s="38">
         <v>46008</v>
       </c>
     </row>
@@ -3623,10 +3823,10 @@
       <c r="B32" s="7">
         <v>46011</v>
       </c>
-      <c r="C32" s="55">
+      <c r="C32" s="50">
         <v>46009</v>
       </c>
-      <c r="D32" s="22">
+      <c r="D32" s="21">
         <v>135717557</v>
       </c>
       <c r="E32" s="17">
@@ -3635,13 +3835,13 @@
       <c r="F32" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="G32" s="64" t="s">
+      <c r="G32" s="59" t="s">
         <v>55</v>
       </c>
       <c r="H32" s="12" t="s">
         <v>129</v>
       </c>
-      <c r="I32" s="43">
+      <c r="I32" s="38">
         <v>46000</v>
       </c>
     </row>
@@ -3652,10 +3852,10 @@
       <c r="B33" s="7">
         <v>46009</v>
       </c>
-      <c r="C33" s="55">
+      <c r="C33" s="50">
         <v>46009</v>
       </c>
-      <c r="D33" s="22">
+      <c r="D33" s="21">
         <v>135673204</v>
       </c>
       <c r="E33" s="17">
@@ -3664,13 +3864,13 @@
       <c r="F33" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="G33" s="64" t="s">
+      <c r="G33" s="59" t="s">
         <v>15</v>
       </c>
       <c r="H33" s="12" t="s">
         <v>131</v>
       </c>
-      <c r="I33" s="43">
+      <c r="I33" s="38">
         <v>45999</v>
       </c>
     </row>
@@ -3681,10 +3881,10 @@
       <c r="B34" s="7">
         <v>45996</v>
       </c>
-      <c r="C34" s="55">
+      <c r="C34" s="50">
         <v>46009</v>
       </c>
-      <c r="D34" s="22">
+      <c r="D34" s="21">
         <v>135718964</v>
       </c>
       <c r="E34" s="17">
@@ -3693,13 +3893,13 @@
       <c r="F34" s="11" t="s">
         <v>132</v>
       </c>
-      <c r="G34" s="64" t="s">
+      <c r="G34" s="59" t="s">
         <v>15</v>
       </c>
       <c r="H34" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="I34" s="43">
+      <c r="I34" s="38">
         <v>46001</v>
       </c>
     </row>
@@ -3710,10 +3910,10 @@
       <c r="B35" s="7">
         <v>46001</v>
       </c>
-      <c r="C35" s="55">
+      <c r="C35" s="50">
         <v>46009</v>
       </c>
-      <c r="D35" s="22">
+      <c r="D35" s="21">
         <v>135796375</v>
       </c>
       <c r="E35" s="17">
@@ -3722,13 +3922,13 @@
       <c r="F35" s="11" t="s">
         <v>134</v>
       </c>
-      <c r="G35" s="64" t="s">
+      <c r="G35" s="59" t="s">
         <v>21</v>
       </c>
       <c r="H35" s="12" t="s">
         <v>135</v>
       </c>
-      <c r="I35" s="43">
+      <c r="I35" s="38">
         <v>46001</v>
       </c>
     </row>
@@ -3739,10 +3939,10 @@
       <c r="B36" s="7">
         <v>46003</v>
       </c>
-      <c r="C36" s="55">
+      <c r="C36" s="50">
         <v>46009</v>
       </c>
-      <c r="D36" s="22">
+      <c r="D36" s="21">
         <v>135845061</v>
       </c>
       <c r="E36" s="17">
@@ -3751,13 +3951,13 @@
       <c r="F36" s="11" t="s">
         <v>136</v>
       </c>
-      <c r="G36" s="64" t="s">
+      <c r="G36" s="59" t="s">
         <v>21</v>
       </c>
       <c r="H36" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="I36" s="43">
+      <c r="I36" s="38">
         <v>46003</v>
       </c>
     </row>
@@ -3768,10 +3968,10 @@
       <c r="B37" s="7">
         <v>46003</v>
       </c>
-      <c r="C37" s="55">
+      <c r="C37" s="50">
         <v>46009</v>
       </c>
-      <c r="D37" s="22">
+      <c r="D37" s="21">
         <v>135831981</v>
       </c>
       <c r="E37" s="17">
@@ -3780,13 +3980,13 @@
       <c r="F37" s="11" t="s">
         <v>137</v>
       </c>
-      <c r="G37" s="64" t="s">
+      <c r="G37" s="59" t="s">
         <v>21</v>
       </c>
       <c r="H37" s="12" t="s">
         <v>138</v>
       </c>
-      <c r="I37" s="43">
+      <c r="I37" s="38">
         <v>46003</v>
       </c>
     </row>
@@ -3797,10 +3997,10 @@
       <c r="B38" s="7">
         <v>46003</v>
       </c>
-      <c r="C38" s="55">
+      <c r="C38" s="50">
         <v>46009</v>
       </c>
-      <c r="D38" s="22">
+      <c r="D38" s="21">
         <v>135829936</v>
       </c>
       <c r="E38" s="17">
@@ -3809,13 +4009,13 @@
       <c r="F38" s="11" t="s">
         <v>139</v>
       </c>
-      <c r="G38" s="64" t="s">
+      <c r="G38" s="59" t="s">
         <v>21</v>
       </c>
       <c r="H38" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="I38" s="43">
+      <c r="I38" s="38">
         <v>46003</v>
       </c>
     </row>
@@ -3826,10 +4026,10 @@
       <c r="B39" s="7">
         <v>46003</v>
       </c>
-      <c r="C39" s="55">
+      <c r="C39" s="50">
         <v>46009</v>
       </c>
-      <c r="D39" s="22">
+      <c r="D39" s="21">
         <v>135844741</v>
       </c>
       <c r="E39" s="17">
@@ -3838,13 +4038,13 @@
       <c r="F39" s="11" t="s">
         <v>140</v>
       </c>
-      <c r="G39" s="64" t="s">
+      <c r="G39" s="59" t="s">
         <v>21</v>
       </c>
       <c r="H39" s="12" t="s">
         <v>141</v>
       </c>
-      <c r="I39" s="43">
+      <c r="I39" s="38">
         <v>46003</v>
       </c>
     </row>
@@ -3855,10 +4055,10 @@
       <c r="B40" s="7">
         <v>46020</v>
       </c>
-      <c r="C40" s="55">
+      <c r="C40" s="50">
         <v>46009</v>
       </c>
-      <c r="D40" s="22">
+      <c r="D40" s="21">
         <v>135717757</v>
       </c>
       <c r="E40" s="17">
@@ -3867,13 +4067,13 @@
       <c r="F40" s="11" t="s">
         <v>142</v>
       </c>
-      <c r="G40" s="64" t="s">
+      <c r="G40" s="59" t="s">
         <v>15</v>
       </c>
       <c r="H40" s="12" t="s">
         <v>143</v>
       </c>
-      <c r="I40" s="43">
+      <c r="I40" s="38">
         <v>46006</v>
       </c>
     </row>
@@ -3884,10 +4084,10 @@
       <c r="B41" s="7">
         <v>45996</v>
       </c>
-      <c r="C41" s="55">
+      <c r="C41" s="50">
         <v>46009</v>
       </c>
-      <c r="D41" s="22">
+      <c r="D41" s="21">
         <v>135726634</v>
       </c>
       <c r="E41" s="17">
@@ -3896,13 +4096,13 @@
       <c r="F41" s="11" t="s">
         <v>144</v>
       </c>
-      <c r="G41" s="64" t="s">
+      <c r="G41" s="59" t="s">
         <v>15</v>
       </c>
       <c r="H41" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="I41" s="43">
+      <c r="I41" s="38">
         <v>46001</v>
       </c>
     </row>
@@ -3913,10 +4113,10 @@
       <c r="B42" s="7">
         <v>46007</v>
       </c>
-      <c r="C42" s="55">
+      <c r="C42" s="50">
         <v>46009</v>
       </c>
-      <c r="D42" s="22">
+      <c r="D42" s="21">
         <v>135728374</v>
       </c>
       <c r="E42" s="17">
@@ -3925,13 +4125,13 @@
       <c r="F42" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="G42" s="64" t="s">
+      <c r="G42" s="59" t="s">
         <v>15</v>
       </c>
       <c r="H42" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="I42" s="43">
+      <c r="I42" s="38">
         <v>46001</v>
       </c>
     </row>
@@ -3942,10 +4142,10 @@
       <c r="B43" s="7">
         <v>46000</v>
       </c>
-      <c r="C43" s="55">
+      <c r="C43" s="50">
         <v>46009</v>
       </c>
-      <c r="D43" s="22">
+      <c r="D43" s="21">
         <v>135776357</v>
       </c>
       <c r="E43" s="17">
@@ -3954,13 +4154,13 @@
       <c r="F43" s="11" t="s">
         <v>147</v>
       </c>
-      <c r="G43" s="64" t="s">
+      <c r="G43" s="59" t="s">
         <v>11</v>
       </c>
       <c r="H43" s="12" t="s">
         <v>93</v>
       </c>
-      <c r="I43" s="43">
+      <c r="I43" s="38">
         <v>46008</v>
       </c>
     </row>
@@ -3971,10 +4171,10 @@
       <c r="B44" s="7">
         <v>46032</v>
       </c>
-      <c r="C44" s="55">
+      <c r="C44" s="50">
         <v>46009</v>
       </c>
-      <c r="D44" s="22">
+      <c r="D44" s="21">
         <v>135830066</v>
       </c>
       <c r="E44" s="17">
@@ -3983,13 +4183,13 @@
       <c r="F44" s="11" t="s">
         <v>148</v>
       </c>
-      <c r="G44" s="64" t="s">
+      <c r="G44" s="59" t="s">
         <v>11</v>
       </c>
       <c r="H44" s="12" t="s">
         <v>93</v>
       </c>
-      <c r="I44" s="43">
+      <c r="I44" s="38">
         <v>46008</v>
       </c>
     </row>
@@ -4000,10 +4200,10 @@
       <c r="B45" s="7">
         <v>46008</v>
       </c>
-      <c r="C45" s="55">
+      <c r="C45" s="50">
         <v>46009</v>
       </c>
-      <c r="D45" s="22">
+      <c r="D45" s="21">
         <v>135786851</v>
       </c>
       <c r="E45" s="17">
@@ -4012,13 +4212,13 @@
       <c r="F45" s="11" t="s">
         <v>149</v>
       </c>
-      <c r="G45" s="64" t="s">
+      <c r="G45" s="59" t="s">
         <v>11</v>
       </c>
       <c r="H45" s="12" t="s">
         <v>93</v>
       </c>
-      <c r="I45" s="43">
+      <c r="I45" s="38">
         <v>46008</v>
       </c>
     </row>
@@ -4029,10 +4229,10 @@
       <c r="B46" s="7">
         <v>45996</v>
       </c>
-      <c r="C46" s="55">
+      <c r="C46" s="50">
         <v>46009</v>
       </c>
-      <c r="D46" s="22">
+      <c r="D46" s="21">
         <v>135747838</v>
       </c>
       <c r="E46" s="17">
@@ -4041,13 +4241,13 @@
       <c r="F46" s="11" t="s">
         <v>150</v>
       </c>
-      <c r="G46" s="64" t="s">
+      <c r="G46" s="59" t="s">
         <v>40</v>
       </c>
       <c r="H46" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="I46" s="43">
+      <c r="I46" s="38">
         <v>45996</v>
       </c>
     </row>
@@ -4058,10 +4258,10 @@
       <c r="B47" s="7">
         <v>45999</v>
       </c>
-      <c r="C47" s="55">
+      <c r="C47" s="50">
         <v>46009</v>
       </c>
-      <c r="D47" s="22">
+      <c r="D47" s="21">
         <v>135751871</v>
       </c>
       <c r="E47" s="17">
@@ -4070,13 +4270,13 @@
       <c r="F47" s="11" t="s">
         <v>151</v>
       </c>
-      <c r="G47" s="64" t="s">
+      <c r="G47" s="59" t="s">
         <v>40</v>
       </c>
       <c r="H47" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="I47" s="43">
+      <c r="I47" s="38">
         <v>45999</v>
       </c>
     </row>
@@ -4087,10 +4287,10 @@
       <c r="B48" s="7">
         <v>45999</v>
       </c>
-      <c r="C48" s="55">
+      <c r="C48" s="50">
         <v>46009</v>
       </c>
-      <c r="D48" s="22">
+      <c r="D48" s="21">
         <v>135752734</v>
       </c>
       <c r="E48" s="17">
@@ -4099,13 +4299,13 @@
       <c r="F48" s="11" t="s">
         <v>152</v>
       </c>
-      <c r="G48" s="64" t="s">
+      <c r="G48" s="59" t="s">
         <v>40</v>
       </c>
       <c r="H48" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="I48" s="43">
+      <c r="I48" s="38">
         <v>45999</v>
       </c>
     </row>
@@ -4116,10 +4316,10 @@
       <c r="B49" s="7">
         <v>45999</v>
       </c>
-      <c r="C49" s="55">
+      <c r="C49" s="50">
         <v>46009</v>
       </c>
-      <c r="D49" s="22">
+      <c r="D49" s="21">
         <v>135755034</v>
       </c>
       <c r="E49" s="17">
@@ -4128,13 +4328,13 @@
       <c r="F49" s="11" t="s">
         <v>153</v>
       </c>
-      <c r="G49" s="64" t="s">
+      <c r="G49" s="59" t="s">
         <v>40</v>
       </c>
       <c r="H49" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="I49" s="43">
+      <c r="I49" s="38">
         <v>45999</v>
       </c>
     </row>
@@ -4145,10 +4345,10 @@
       <c r="B50" s="7">
         <v>45999</v>
       </c>
-      <c r="C50" s="55">
+      <c r="C50" s="50">
         <v>46009</v>
       </c>
-      <c r="D50" s="22">
+      <c r="D50" s="21">
         <v>135758273</v>
       </c>
       <c r="E50" s="17">
@@ -4157,26 +4357,26 @@
       <c r="F50" s="11" t="s">
         <v>154</v>
       </c>
-      <c r="G50" s="64" t="s">
+      <c r="G50" s="59" t="s">
         <v>40</v>
       </c>
       <c r="H50" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="I50" s="43">
+      <c r="I50" s="38">
         <v>45999</v>
       </c>
     </row>
     <row r="51" spans="1:9">
       <c r="A51" s="6"/>
       <c r="B51" s="7"/>
-      <c r="C51" s="55"/>
-      <c r="D51" s="59"/>
-      <c r="E51" s="56"/>
-      <c r="F51" s="30"/>
-      <c r="G51" s="41"/>
+      <c r="C51" s="50"/>
+      <c r="D51" s="54"/>
+      <c r="E51" s="51"/>
+      <c r="F51" s="29"/>
+      <c r="G51" s="36"/>
       <c r="H51" s="12"/>
-      <c r="I51" s="43"/>
+      <c r="I51" s="38"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B1:C1">
@@ -4208,7 +4408,7 @@
     <col min="6" max="6" width="30.140625" customWidth="1"/>
     <col min="7" max="7" width="20.28515625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="31.5703125" customWidth="1"/>
-    <col min="9" max="9" width="21" style="23" customWidth="1"/>
+    <col min="9" max="9" width="21" style="22" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -4236,7 +4436,7 @@
       <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="27" t="s">
+      <c r="I1" s="26" t="s">
         <v>8</v>
       </c>
     </row>
@@ -4244,28 +4444,28 @@
       <c r="A2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="60">
+      <c r="B2" s="55">
         <v>46003</v>
       </c>
-      <c r="C2" s="24">
+      <c r="C2" s="23">
         <v>46010</v>
       </c>
-      <c r="D2" s="61">
+      <c r="D2" s="56">
         <v>135894726</v>
       </c>
-      <c r="E2" s="75">
+      <c r="E2" s="68">
         <v>3450184133</v>
       </c>
-      <c r="F2" s="76" t="s">
+      <c r="F2" s="69" t="s">
         <v>155</v>
       </c>
-      <c r="G2" s="41" t="s">
+      <c r="G2" s="36" t="s">
         <v>11</v>
       </c>
       <c r="H2" s="12" t="s">
         <v>156</v>
       </c>
-      <c r="I2" s="43">
+      <c r="I2" s="38">
         <v>46009</v>
       </c>
     </row>
@@ -4273,28 +4473,28 @@
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="60">
+      <c r="B3" s="55">
         <v>45996</v>
       </c>
-      <c r="C3" s="24">
+      <c r="C3" s="23">
         <v>46010</v>
       </c>
-      <c r="D3" s="73">
+      <c r="D3" s="21">
         <v>135684503</v>
       </c>
       <c r="E3" s="17">
         <v>3450171417</v>
       </c>
-      <c r="F3" s="72" t="s">
+      <c r="F3" s="11" t="s">
         <v>157</v>
       </c>
-      <c r="G3" s="64" t="s">
+      <c r="G3" s="59" t="s">
         <v>15</v>
       </c>
-      <c r="H3" s="77" t="s">
+      <c r="H3" s="11" t="s">
         <v>131</v>
       </c>
-      <c r="I3" s="43">
+      <c r="I3" s="38">
         <v>45999</v>
       </c>
     </row>
@@ -4302,28 +4502,28 @@
       <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="60">
+      <c r="B4" s="55">
         <v>46001</v>
       </c>
-      <c r="C4" s="24">
+      <c r="C4" s="23">
         <v>46010</v>
       </c>
-      <c r="D4" s="73">
+      <c r="D4" s="21">
         <v>135739166</v>
       </c>
       <c r="E4" s="17">
         <v>3450175575</v>
       </c>
-      <c r="F4" s="72" t="s">
+      <c r="F4" s="11" t="s">
         <v>158</v>
       </c>
-      <c r="G4" s="64" t="s">
+      <c r="G4" s="59" t="s">
         <v>15</v>
       </c>
-      <c r="H4" s="77" t="s">
+      <c r="H4" s="11" t="s">
         <v>159</v>
       </c>
-      <c r="I4" s="43">
+      <c r="I4" s="38">
         <v>46001</v>
       </c>
     </row>
@@ -4331,28 +4531,28 @@
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="60">
+      <c r="B5" s="55">
         <v>46000</v>
       </c>
-      <c r="C5" s="24">
+      <c r="C5" s="23">
         <v>46010</v>
       </c>
-      <c r="D5" s="73">
+      <c r="D5" s="21">
         <v>135778337</v>
       </c>
       <c r="E5" s="17">
         <v>3450178479</v>
       </c>
-      <c r="F5" s="72" t="s">
+      <c r="F5" s="11" t="s">
         <v>160</v>
       </c>
-      <c r="G5" s="64" t="s">
+      <c r="G5" s="59" t="s">
         <v>40</v>
       </c>
       <c r="H5" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="I5" s="43">
+      <c r="I5" s="38">
         <v>46000</v>
       </c>
     </row>
@@ -4360,28 +4560,28 @@
       <c r="A6" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="60">
+      <c r="B6" s="55">
         <v>46000</v>
       </c>
-      <c r="C6" s="24">
+      <c r="C6" s="23">
         <v>46010</v>
       </c>
-      <c r="D6" s="73">
+      <c r="D6" s="21">
         <v>135766819</v>
       </c>
       <c r="E6" s="17">
         <v>3450177456</v>
       </c>
-      <c r="F6" s="72" t="s">
+      <c r="F6" s="11" t="s">
         <v>161</v>
       </c>
-      <c r="G6" s="64" t="s">
+      <c r="G6" s="59" t="s">
         <v>40</v>
       </c>
       <c r="H6" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="I6" s="43">
+      <c r="I6" s="38">
         <v>46000</v>
       </c>
     </row>
@@ -4389,28 +4589,28 @@
       <c r="A7" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="60">
+      <c r="B7" s="55">
         <v>46003</v>
       </c>
-      <c r="C7" s="24">
+      <c r="C7" s="23">
         <v>46010</v>
       </c>
-      <c r="D7" s="73">
+      <c r="D7" s="21">
         <v>135812151</v>
       </c>
       <c r="E7" s="17">
         <v>3450176830</v>
       </c>
-      <c r="F7" s="72" t="s">
+      <c r="F7" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="G7" s="64" t="s">
+      <c r="G7" s="59" t="s">
         <v>11</v>
       </c>
       <c r="H7" s="12" t="s">
         <v>163</v>
       </c>
-      <c r="I7" s="43">
+      <c r="I7" s="38">
         <v>46009</v>
       </c>
     </row>
@@ -4418,28 +4618,28 @@
       <c r="A8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="60">
+      <c r="B8" s="55">
         <v>46012</v>
       </c>
-      <c r="C8" s="24">
+      <c r="C8" s="23">
         <v>46010</v>
       </c>
-      <c r="D8" s="73">
+      <c r="D8" s="21">
         <v>135823672</v>
       </c>
       <c r="E8" s="17">
         <v>3450182208</v>
       </c>
-      <c r="F8" s="72" t="s">
+      <c r="F8" s="11" t="s">
         <v>164</v>
       </c>
-      <c r="G8" s="64" t="s">
+      <c r="G8" s="59" t="s">
         <v>11</v>
       </c>
       <c r="H8" s="12" t="s">
         <v>163</v>
       </c>
-      <c r="I8" s="43">
+      <c r="I8" s="38">
         <v>46009</v>
       </c>
     </row>
@@ -4447,28 +4647,28 @@
       <c r="A9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="60">
+      <c r="B9" s="55">
         <v>46003</v>
       </c>
-      <c r="C9" s="24">
+      <c r="C9" s="23">
         <v>46010</v>
       </c>
-      <c r="D9" s="73">
+      <c r="D9" s="21">
         <v>135841920</v>
       </c>
       <c r="E9" s="17">
         <v>3450183858</v>
       </c>
-      <c r="F9" s="72" t="s">
+      <c r="F9" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="G9" s="64" t="s">
+      <c r="G9" s="59" t="s">
         <v>11</v>
       </c>
       <c r="H9" s="11" t="s">
         <v>163</v>
       </c>
-      <c r="I9" s="43">
+      <c r="I9" s="38">
         <v>46009</v>
       </c>
     </row>
@@ -4476,28 +4676,28 @@
       <c r="A10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="60">
+      <c r="B10" s="55">
         <v>46007</v>
       </c>
-      <c r="C10" s="24">
+      <c r="C10" s="23">
         <v>46010</v>
       </c>
-      <c r="D10" s="73">
+      <c r="D10" s="21">
         <v>135892469</v>
       </c>
       <c r="E10" s="17">
         <v>3450187906</v>
       </c>
-      <c r="F10" s="72" t="s">
+      <c r="F10" s="11" t="s">
         <v>166</v>
       </c>
-      <c r="G10" s="74" t="s">
+      <c r="G10" s="67" t="s">
         <v>37</v>
       </c>
       <c r="H10" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="I10" s="43">
+      <c r="I10" s="38">
         <v>46007</v>
       </c>
     </row>
@@ -4505,28 +4705,28 @@
       <c r="A11" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="60">
+      <c r="B11" s="55">
         <v>46000</v>
       </c>
-      <c r="C11" s="24">
+      <c r="C11" s="23">
         <v>46010</v>
       </c>
-      <c r="D11" s="73">
+      <c r="D11" s="21">
         <v>135774607</v>
       </c>
       <c r="E11" s="17">
         <v>3450178116</v>
       </c>
-      <c r="F11" s="72" t="s">
+      <c r="F11" s="11" t="s">
         <v>167</v>
       </c>
-      <c r="G11" s="64" t="s">
+      <c r="G11" s="59" t="s">
         <v>11</v>
       </c>
       <c r="H11" s="12" t="s">
         <v>163</v>
       </c>
-      <c r="I11" s="43">
+      <c r="I11" s="38">
         <v>46009</v>
       </c>
     </row>
@@ -4534,28 +4734,28 @@
       <c r="A12" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="60">
+      <c r="B12" s="55">
         <v>46009</v>
       </c>
-      <c r="C12" s="24">
+      <c r="C12" s="23">
         <v>46010</v>
       </c>
-      <c r="D12" s="73">
+      <c r="D12" s="21">
         <v>135921089</v>
       </c>
       <c r="E12" s="17">
         <v>3450189886</v>
       </c>
-      <c r="F12" s="72" t="s">
+      <c r="F12" s="11" t="s">
         <v>168</v>
       </c>
-      <c r="G12" s="64" t="s">
+      <c r="G12" s="59" t="s">
         <v>11</v>
       </c>
       <c r="H12" s="12" t="s">
         <v>169</v>
       </c>
-      <c r="I12" s="43">
+      <c r="I12" s="38">
         <v>46010</v>
       </c>
     </row>
@@ -4563,28 +4763,28 @@
       <c r="A13" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="60">
+      <c r="B13" s="55">
         <v>46009</v>
       </c>
-      <c r="C13" s="24">
+      <c r="C13" s="23">
         <v>46010</v>
       </c>
-      <c r="D13" s="73">
+      <c r="D13" s="21">
         <v>135933634</v>
       </c>
       <c r="E13" s="17">
         <v>3450191217</v>
       </c>
-      <c r="F13" s="72" t="s">
+      <c r="F13" s="11" t="s">
         <v>170</v>
       </c>
-      <c r="G13" s="74" t="s">
+      <c r="G13" s="67" t="s">
         <v>37</v>
       </c>
       <c r="H13" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="I13" s="43">
+      <c r="I13" s="38">
         <v>46009</v>
       </c>
     </row>
@@ -4592,28 +4792,28 @@
       <c r="A14" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="60">
+      <c r="B14" s="55">
         <v>46010</v>
       </c>
-      <c r="C14" s="24">
+      <c r="C14" s="23">
         <v>46010</v>
       </c>
-      <c r="D14" s="73">
+      <c r="D14" s="21">
         <v>135686031</v>
       </c>
       <c r="E14" s="17">
         <v>3450171637</v>
       </c>
-      <c r="F14" s="72" t="s">
+      <c r="F14" s="11" t="s">
         <v>171</v>
       </c>
-      <c r="G14" s="64" t="s">
+      <c r="G14" s="59" t="s">
         <v>15</v>
       </c>
-      <c r="H14" s="78" t="s">
+      <c r="H14" s="12" t="s">
         <v>172</v>
       </c>
-      <c r="I14" s="43">
+      <c r="I14" s="38">
         <v>45999</v>
       </c>
     </row>
@@ -4621,28 +4821,28 @@
       <c r="A15" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B15" s="60">
+      <c r="B15" s="55">
         <v>45997</v>
       </c>
-      <c r="C15" s="24">
+      <c r="C15" s="23">
         <v>46010</v>
       </c>
-      <c r="D15" s="73">
+      <c r="D15" s="21">
         <v>135739165</v>
       </c>
       <c r="E15" s="17">
         <v>3450175564</v>
       </c>
-      <c r="F15" s="72" t="s">
+      <c r="F15" s="11" t="s">
         <v>173</v>
       </c>
-      <c r="G15" s="64" t="s">
+      <c r="G15" s="59" t="s">
         <v>15</v>
       </c>
-      <c r="H15" s="78" t="s">
+      <c r="H15" s="12" t="s">
         <v>174</v>
       </c>
-      <c r="I15" s="43">
+      <c r="I15" s="38">
         <v>46001</v>
       </c>
     </row>
@@ -4653,25 +4853,25 @@
       <c r="B16" s="7">
         <v>46003</v>
       </c>
-      <c r="C16" s="24">
+      <c r="C16" s="23">
         <v>46010</v>
       </c>
-      <c r="D16" s="73">
+      <c r="D16" s="21">
         <v>135833562</v>
       </c>
       <c r="E16" s="17">
         <v>3450182923</v>
       </c>
-      <c r="F16" s="72" t="s">
+      <c r="F16" s="11" t="s">
         <v>175</v>
       </c>
-      <c r="G16" s="64" t="s">
+      <c r="G16" s="59" t="s">
         <v>21</v>
       </c>
       <c r="H16" s="12" t="s">
         <v>176</v>
       </c>
-      <c r="I16" s="43">
+      <c r="I16" s="38">
         <v>46003</v>
       </c>
     </row>
@@ -4682,25 +4882,25 @@
       <c r="B17" s="7">
         <v>46000</v>
       </c>
-      <c r="C17" s="24">
+      <c r="C17" s="23">
         <v>46010</v>
       </c>
-      <c r="D17" s="73">
+      <c r="D17" s="21">
         <v>135760750</v>
       </c>
       <c r="E17" s="17">
         <v>3450177016</v>
       </c>
-      <c r="F17" s="72" t="s">
+      <c r="F17" s="11" t="s">
         <v>177</v>
       </c>
-      <c r="G17" s="74" t="s">
+      <c r="G17" s="67" t="s">
         <v>40</v>
       </c>
       <c r="H17" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="I17" s="43">
+      <c r="I17" s="38">
         <v>46000</v>
       </c>
     </row>
@@ -4711,25 +4911,25 @@
       <c r="B18" s="7">
         <v>46000</v>
       </c>
-      <c r="C18" s="24">
+      <c r="C18" s="23">
         <v>46010</v>
       </c>
-      <c r="D18" s="73">
+      <c r="D18" s="21">
         <v>135762192</v>
       </c>
       <c r="E18" s="17">
         <v>3450177071</v>
       </c>
-      <c r="F18" s="72" t="s">
+      <c r="F18" s="11" t="s">
         <v>178</v>
       </c>
-      <c r="G18" s="74" t="s">
+      <c r="G18" s="67" t="s">
         <v>40</v>
       </c>
       <c r="H18" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="I18" s="43">
+      <c r="I18" s="38">
         <v>46000</v>
       </c>
     </row>
@@ -4740,25 +4940,25 @@
       <c r="B19" s="7">
         <v>46000</v>
       </c>
-      <c r="C19" s="24">
+      <c r="C19" s="23">
         <v>46010</v>
       </c>
-      <c r="D19" s="73">
+      <c r="D19" s="21">
         <v>135767139</v>
       </c>
       <c r="E19" s="17">
         <v>3450177522</v>
       </c>
-      <c r="F19" s="72" t="s">
+      <c r="F19" s="11" t="s">
         <v>179</v>
       </c>
-      <c r="G19" s="74" t="s">
+      <c r="G19" s="67" t="s">
         <v>40</v>
       </c>
       <c r="H19" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="I19" s="43">
+      <c r="I19" s="38">
         <v>46000</v>
       </c>
     </row>
@@ -4769,25 +4969,25 @@
       <c r="B20" s="7">
         <v>45996</v>
       </c>
-      <c r="C20" s="24">
+      <c r="C20" s="23">
         <v>46010</v>
       </c>
-      <c r="D20" s="73">
+      <c r="D20" s="21">
         <v>135767429</v>
       </c>
       <c r="E20" s="17">
         <v>3450175201</v>
       </c>
-      <c r="F20" s="72" t="s">
+      <c r="F20" s="11" t="s">
         <v>180</v>
       </c>
-      <c r="G20" s="74" t="s">
+      <c r="G20" s="67" t="s">
         <v>40</v>
       </c>
       <c r="H20" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="I20" s="43">
+      <c r="I20" s="38">
         <v>45996</v>
       </c>
     </row>
@@ -4798,25 +4998,25 @@
       <c r="B21" s="7">
         <v>46032</v>
       </c>
-      <c r="C21" s="24">
+      <c r="C21" s="23">
         <v>46010</v>
       </c>
-      <c r="D21" s="73">
+      <c r="D21" s="21">
         <v>135829887</v>
       </c>
       <c r="E21" s="17">
         <v>3450182494</v>
       </c>
-      <c r="F21" s="72" t="s">
+      <c r="F21" s="11" t="s">
         <v>148</v>
       </c>
-      <c r="G21" s="74" t="s">
+      <c r="G21" s="67" t="s">
         <v>11</v>
       </c>
       <c r="H21" s="12" t="s">
         <v>163</v>
       </c>
-      <c r="I21" s="43">
+      <c r="I21" s="38">
         <v>46009</v>
       </c>
     </row>
@@ -4827,25 +5027,25 @@
       <c r="B22" s="7">
         <v>46000</v>
       </c>
-      <c r="C22" s="24">
+      <c r="C22" s="23">
         <v>46010</v>
       </c>
-      <c r="D22" s="73">
+      <c r="D22" s="21">
         <v>135773164</v>
       </c>
       <c r="E22" s="17">
         <v>3450177995</v>
       </c>
-      <c r="F22" s="72" t="s">
+      <c r="F22" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="G22" s="74" t="s">
+      <c r="G22" s="67" t="s">
         <v>11</v>
       </c>
       <c r="H22" s="12" t="s">
         <v>163</v>
       </c>
-      <c r="I22" s="43">
+      <c r="I22" s="38">
         <v>46009</v>
       </c>
     </row>
@@ -4856,25 +5056,25 @@
       <c r="B23" s="7">
         <v>46000</v>
       </c>
-      <c r="C23" s="24">
+      <c r="C23" s="23">
         <v>46010</v>
       </c>
-      <c r="D23" s="73">
+      <c r="D23" s="21">
         <v>135778040</v>
       </c>
       <c r="E23" s="17">
         <v>3450178457</v>
       </c>
-      <c r="F23" s="72" t="s">
+      <c r="F23" s="11" t="s">
         <v>181</v>
       </c>
-      <c r="G23" s="74" t="s">
+      <c r="G23" s="67" t="s">
         <v>40</v>
       </c>
       <c r="H23" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="I23" s="48">
+      <c r="I23" s="43">
         <v>46000</v>
       </c>
     </row>
@@ -4885,25 +5085,25 @@
       <c r="B24" s="7">
         <v>46000</v>
       </c>
-      <c r="C24" s="24">
+      <c r="C24" s="23">
         <v>46010</v>
       </c>
-      <c r="D24" s="73">
+      <c r="D24" s="21">
         <v>135775679</v>
       </c>
       <c r="E24" s="17">
         <v>3450178237</v>
       </c>
-      <c r="F24" s="72" t="s">
+      <c r="F24" s="11" t="s">
         <v>182</v>
       </c>
-      <c r="G24" s="74" t="s">
+      <c r="G24" s="67" t="s">
         <v>40</v>
       </c>
       <c r="H24" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="I24" s="48">
+      <c r="I24" s="43">
         <v>46000</v>
       </c>
     </row>
@@ -4911,12 +5111,12 @@
       <c r="A25" s="6"/>
       <c r="B25" s="8"/>
       <c r="C25" s="7"/>
-      <c r="D25" s="20"/>
-      <c r="E25" s="20"/>
+      <c r="D25" s="19"/>
+      <c r="E25" s="19"/>
       <c r="F25" s="14"/>
       <c r="G25" s="6"/>
-      <c r="H25" s="47"/>
-      <c r="I25" s="43"/>
+      <c r="H25" s="42"/>
+      <c r="I25" s="38"/>
     </row>
     <row r="26" spans="1:9">
       <c r="A26" s="6"/>
@@ -4926,8 +5126,8 @@
       <c r="E26" s="8"/>
       <c r="F26" s="9"/>
       <c r="G26" s="6"/>
-      <c r="H26" s="47"/>
-      <c r="I26" s="43"/>
+      <c r="H26" s="42"/>
+      <c r="I26" s="38"/>
     </row>
     <row r="27" spans="1:9">
       <c r="A27" s="6"/>
@@ -4937,8 +5137,8 @@
       <c r="E27" s="8"/>
       <c r="F27" s="9"/>
       <c r="G27" s="6"/>
-      <c r="H27" s="47"/>
-      <c r="I27" s="43"/>
+      <c r="H27" s="42"/>
+      <c r="I27" s="38"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B1:C1">
@@ -5011,28 +5211,28 @@
       <c r="A2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="24">
+      <c r="B2" s="23">
         <v>46006</v>
       </c>
-      <c r="C2" s="24">
+      <c r="C2" s="23">
         <v>46011</v>
       </c>
-      <c r="D2" s="73">
+      <c r="D2" s="21">
         <v>135735276</v>
       </c>
       <c r="E2" s="17">
         <v>3450175432</v>
       </c>
-      <c r="F2" s="72" t="s">
+      <c r="F2" s="11" t="s">
         <v>183</v>
       </c>
-      <c r="G2" s="21" t="s">
+      <c r="G2" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="H2" s="79" t="s">
+      <c r="H2" s="42" t="s">
         <v>184</v>
       </c>
-      <c r="I2" s="43">
+      <c r="I2" s="38">
         <v>46001</v>
       </c>
     </row>
@@ -5040,28 +5240,28 @@
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="24">
+      <c r="B3" s="23">
         <v>45996</v>
       </c>
-      <c r="C3" s="24">
+      <c r="C3" s="23">
         <v>46011</v>
       </c>
-      <c r="D3" s="73">
+      <c r="D3" s="21">
         <v>135744670</v>
       </c>
       <c r="E3" s="17">
         <v>3450175773</v>
       </c>
-      <c r="F3" s="72" t="s">
+      <c r="F3" s="11" t="s">
         <v>185</v>
       </c>
-      <c r="G3" s="21" t="s">
+      <c r="G3" s="20" t="s">
         <v>55</v>
       </c>
-      <c r="H3" s="79" t="s">
+      <c r="H3" s="42" t="s">
         <v>186</v>
       </c>
-      <c r="I3" s="43">
+      <c r="I3" s="38">
         <v>46001</v>
       </c>
     </row>
@@ -5069,28 +5269,28 @@
       <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="24">
+      <c r="B4" s="23">
         <v>46001</v>
       </c>
-      <c r="C4" s="24">
+      <c r="C4" s="23">
         <v>46011</v>
       </c>
-      <c r="D4" s="73">
+      <c r="D4" s="21">
         <v>135777498</v>
       </c>
       <c r="E4" s="17">
         <v>3450178413</v>
       </c>
-      <c r="F4" s="72" t="s">
+      <c r="F4" s="11" t="s">
         <v>187</v>
       </c>
-      <c r="G4" s="21" t="s">
+      <c r="G4" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="H4" s="79" t="s">
+      <c r="H4" s="42" t="s">
         <v>174</v>
       </c>
-      <c r="I4" s="48">
+      <c r="I4" s="43">
         <v>46006</v>
       </c>
     </row>
@@ -5099,13 +5299,13 @@
         <v>9</v>
       </c>
       <c r="B5" s="7"/>
-      <c r="C5" s="24"/>
-      <c r="D5" s="25"/>
+      <c r="C5" s="23"/>
+      <c r="D5" s="24"/>
       <c r="E5" s="17"/>
       <c r="F5" s="11"/>
-      <c r="G5" s="21"/>
-      <c r="H5" s="47"/>
-      <c r="I5" s="43"/>
+      <c r="G5" s="20"/>
+      <c r="H5" s="42"/>
+      <c r="I5" s="38"/>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="6" t="s">
@@ -5113,89 +5313,89 @@
       </c>
       <c r="B6" s="7"/>
       <c r="C6" s="7"/>
-      <c r="D6" s="62"/>
-      <c r="E6" s="20"/>
-      <c r="F6" s="30"/>
-      <c r="G6" s="26"/>
-      <c r="H6" s="47"/>
-      <c r="I6" s="43"/>
+      <c r="D6" s="57"/>
+      <c r="E6" s="19"/>
+      <c r="F6" s="29"/>
+      <c r="G6" s="25"/>
+      <c r="H6" s="42"/>
+      <c r="I6" s="38"/>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="6"/>
       <c r="B7" s="7"/>
       <c r="C7" s="7"/>
-      <c r="D7" s="25"/>
+      <c r="D7" s="24"/>
       <c r="E7" s="8"/>
       <c r="F7" s="11"/>
-      <c r="G7" s="26"/>
-      <c r="H7" s="47"/>
-      <c r="I7" s="43"/>
+      <c r="G7" s="25"/>
+      <c r="H7" s="42"/>
+      <c r="I7" s="38"/>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="6"/>
       <c r="B8" s="7"/>
       <c r="C8" s="7"/>
-      <c r="D8" s="25"/>
+      <c r="D8" s="24"/>
       <c r="E8" s="8"/>
       <c r="F8" s="11"/>
-      <c r="G8" s="26"/>
-      <c r="H8" s="47"/>
-      <c r="I8" s="43"/>
+      <c r="G8" s="25"/>
+      <c r="H8" s="42"/>
+      <c r="I8" s="38"/>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="6"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
-      <c r="D9" s="25"/>
+      <c r="D9" s="24"/>
       <c r="E9" s="8"/>
       <c r="F9" s="11"/>
-      <c r="G9" s="26"/>
-      <c r="H9" s="47"/>
-      <c r="I9" s="43"/>
+      <c r="G9" s="25"/>
+      <c r="H9" s="42"/>
+      <c r="I9" s="38"/>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="6"/>
       <c r="B10" s="7"/>
       <c r="C10" s="7"/>
-      <c r="D10" s="25"/>
+      <c r="D10" s="24"/>
       <c r="E10" s="8"/>
       <c r="F10" s="11"/>
-      <c r="G10" s="26"/>
-      <c r="H10" s="47"/>
-      <c r="I10" s="43"/>
+      <c r="G10" s="25"/>
+      <c r="H10" s="42"/>
+      <c r="I10" s="38"/>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="6"/>
       <c r="B11" s="7"/>
       <c r="C11" s="7"/>
-      <c r="D11" s="25"/>
+      <c r="D11" s="24"/>
       <c r="E11" s="8"/>
       <c r="F11" s="11"/>
-      <c r="G11" s="26"/>
-      <c r="H11" s="47"/>
-      <c r="I11" s="43"/>
+      <c r="G11" s="25"/>
+      <c r="H11" s="42"/>
+      <c r="I11" s="38"/>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="6"/>
       <c r="B12" s="7"/>
       <c r="C12" s="7"/>
-      <c r="D12" s="25"/>
+      <c r="D12" s="24"/>
       <c r="E12" s="8"/>
       <c r="F12" s="11"/>
-      <c r="G12" s="26"/>
-      <c r="H12" s="47"/>
-      <c r="I12" s="43"/>
+      <c r="G12" s="25"/>
+      <c r="H12" s="42"/>
+      <c r="I12" s="38"/>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="6"/>
       <c r="B13" s="7"/>
       <c r="C13" s="7"/>
-      <c r="D13" s="25"/>
+      <c r="D13" s="24"/>
       <c r="E13" s="8"/>
       <c r="F13" s="11"/>
-      <c r="G13" s="26"/>
-      <c r="H13" s="47"/>
-      <c r="I13" s="43"/>
+      <c r="G13" s="25"/>
+      <c r="H13" s="42"/>
+      <c r="I13" s="38"/>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="6"/>
@@ -5205,8 +5405,8 @@
       <c r="E14" s="13"/>
       <c r="F14" s="11"/>
       <c r="G14" s="6"/>
-      <c r="H14" s="47"/>
-      <c r="I14" s="43"/>
+      <c r="H14" s="42"/>
+      <c r="I14" s="38"/>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="6"/>
@@ -5216,8 +5416,8 @@
       <c r="E15" s="13"/>
       <c r="F15" s="11"/>
       <c r="G15" s="6"/>
-      <c r="H15" s="47"/>
-      <c r="I15" s="43"/>
+      <c r="H15" s="42"/>
+      <c r="I15" s="38"/>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="6"/>
@@ -5227,8 +5427,8 @@
       <c r="E16" s="13"/>
       <c r="F16" s="12"/>
       <c r="G16" s="6"/>
-      <c r="H16" s="47"/>
-      <c r="I16" s="48"/>
+      <c r="H16" s="42"/>
+      <c r="I16" s="43"/>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="6"/>
@@ -5238,8 +5438,8 @@
       <c r="E17" s="8"/>
       <c r="F17" s="14"/>
       <c r="G17" s="6"/>
-      <c r="H17" s="47"/>
-      <c r="I17" s="43"/>
+      <c r="H17" s="42"/>
+      <c r="I17" s="38"/>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="6"/>
@@ -5249,7 +5449,7 @@
       <c r="E18" s="8"/>
       <c r="F18" s="9"/>
       <c r="G18" s="6"/>
-      <c r="H18" s="47"/>
+      <c r="H18" s="42"/>
       <c r="I18" s="12"/>
     </row>
     <row r="19" spans="1:9">
@@ -5260,7 +5460,7 @@
       <c r="E19" s="8"/>
       <c r="F19" s="9"/>
       <c r="G19" s="6"/>
-      <c r="H19" s="47"/>
+      <c r="H19" s="42"/>
       <c r="I19" s="12"/>
     </row>
     <row r="20" spans="1:9">
@@ -5271,7 +5471,7 @@
       <c r="E20" s="8"/>
       <c r="F20" s="9"/>
       <c r="G20" s="6"/>
-      <c r="H20" s="47"/>
+      <c r="H20" s="42"/>
       <c r="I20" s="12"/>
     </row>
     <row r="21" spans="1:9">
@@ -5282,7 +5482,7 @@
       <c r="E21" s="8"/>
       <c r="F21" s="9"/>
       <c r="G21" s="6"/>
-      <c r="H21" s="47"/>
+      <c r="H21" s="42"/>
       <c r="I21" s="12"/>
     </row>
     <row r="22" spans="1:9">
@@ -5293,7 +5493,7 @@
       <c r="E22" s="8"/>
       <c r="F22" s="9"/>
       <c r="G22" s="6"/>
-      <c r="H22" s="47"/>
+      <c r="H22" s="42"/>
       <c r="I22" s="12"/>
     </row>
     <row r="23" spans="1:9">
@@ -5304,7 +5504,7 @@
       <c r="E23" s="8"/>
       <c r="F23" s="9"/>
       <c r="G23" s="6"/>
-      <c r="H23" s="47"/>
+      <c r="H23" s="42"/>
       <c r="I23" s="12"/>
     </row>
     <row r="24" spans="1:9">
@@ -5315,7 +5515,7 @@
       <c r="E24" s="8"/>
       <c r="F24" s="9"/>
       <c r="G24" s="6"/>
-      <c r="H24" s="47"/>
+      <c r="H24" s="42"/>
       <c r="I24" s="12"/>
     </row>
     <row r="25" spans="1:9">
@@ -5326,7 +5526,7 @@
       <c r="E25" s="8"/>
       <c r="F25" s="9"/>
       <c r="G25" s="6"/>
-      <c r="H25" s="47"/>
+      <c r="H25" s="42"/>
       <c r="I25" s="12"/>
     </row>
     <row r="26" spans="1:9">
@@ -5337,7 +5537,7 @@
       <c r="E26" s="8"/>
       <c r="F26" s="9"/>
       <c r="G26" s="6"/>
-      <c r="H26" s="47"/>
+      <c r="H26" s="42"/>
       <c r="I26" s="12"/>
     </row>
     <row r="27" spans="1:9">
@@ -5348,7 +5548,7 @@
       <c r="E27" s="8"/>
       <c r="F27" s="9"/>
       <c r="G27" s="6"/>
-      <c r="H27" s="47"/>
+      <c r="H27" s="42"/>
       <c r="I27" s="12"/>
     </row>
   </sheetData>
@@ -5421,63 +5621,63 @@
         <v>9</v>
       </c>
       <c r="B2" s="7"/>
-      <c r="C2" s="24"/>
-      <c r="D2" s="22"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="21"/>
       <c r="E2" s="17"/>
       <c r="F2" s="11"/>
-      <c r="G2" s="19"/>
+      <c r="G2" s="18"/>
       <c r="H2" s="9"/>
-      <c r="I2" s="23"/>
+      <c r="I2" s="22"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B3" s="7"/>
-      <c r="C3" s="24"/>
-      <c r="D3" s="22"/>
+      <c r="C3" s="23"/>
+      <c r="D3" s="21"/>
       <c r="E3" s="17"/>
       <c r="F3" s="11"/>
-      <c r="G3" s="19"/>
+      <c r="G3" s="18"/>
       <c r="H3" s="9"/>
-      <c r="I3" s="32"/>
+      <c r="I3" s="30"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B4" s="7"/>
-      <c r="C4" s="24"/>
-      <c r="D4" s="22"/>
+      <c r="C4" s="23"/>
+      <c r="D4" s="21"/>
       <c r="E4" s="17"/>
       <c r="F4" s="11"/>
-      <c r="G4" s="19"/>
+      <c r="G4" s="18"/>
       <c r="H4" s="9"/>
-      <c r="I4" s="23"/>
+      <c r="I4" s="22"/>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B5" s="7"/>
-      <c r="C5" s="24"/>
-      <c r="D5" s="22"/>
+      <c r="C5" s="23"/>
+      <c r="D5" s="21"/>
       <c r="E5" s="17"/>
       <c r="F5" s="11"/>
-      <c r="G5" s="19"/>
+      <c r="G5" s="18"/>
       <c r="H5" s="9"/>
-      <c r="I5" s="23"/>
+      <c r="I5" s="22"/>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="6"/>
       <c r="B6" s="7"/>
       <c r="C6" s="7"/>
-      <c r="D6" s="20"/>
-      <c r="E6" s="29"/>
-      <c r="F6" s="30"/>
+      <c r="D6" s="19"/>
+      <c r="E6" s="28"/>
+      <c r="F6" s="29"/>
       <c r="G6" s="6"/>
       <c r="H6" s="9"/>
-      <c r="I6" s="23"/>
+      <c r="I6" s="22"/>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="6"/>
@@ -5968,7 +6168,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43D38813-FAE5-45C6-9D51-7607EDAA916D}">
-  <dimension ref="A1:I55"/>
+  <dimension ref="A1:I46"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
@@ -6004,7 +6204,7 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="38" t="s">
+      <c r="H1" s="33" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="5" t="s">
@@ -6012,644 +6212,1301 @@
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="24"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="36"/>
-      <c r="H2" s="33"/>
-      <c r="I2" s="23"/>
+      <c r="A2" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="7">
+        <v>46006</v>
+      </c>
+      <c r="C2" s="23">
+        <v>46013</v>
+      </c>
+      <c r="D2" s="76" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="77">
+        <v>3450186223</v>
+      </c>
+      <c r="F2" s="78" t="s">
+        <v>188</v>
+      </c>
+      <c r="G2" s="31" t="s">
+        <v>60</v>
+      </c>
+      <c r="H2" s="70" t="s">
+        <v>189</v>
+      </c>
+      <c r="I2" s="38"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="7"/>
-      <c r="C3" s="24"/>
-      <c r="D3" s="22"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="18"/>
-      <c r="G3" s="36"/>
-      <c r="H3" s="33"/>
-      <c r="I3" s="23"/>
+      <c r="B3" s="7">
+        <v>46000</v>
+      </c>
+      <c r="C3" s="23">
+        <v>46013</v>
+      </c>
+      <c r="D3" s="79">
+        <v>135808481</v>
+      </c>
+      <c r="E3" s="17">
+        <v>3450177005</v>
+      </c>
+      <c r="F3" s="74" t="s">
+        <v>190</v>
+      </c>
+      <c r="G3" s="31" t="s">
+        <v>11</v>
+      </c>
+      <c r="H3" s="71" t="s">
+        <v>191</v>
+      </c>
+      <c r="I3" s="38">
+        <v>46010</v>
+      </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="7"/>
-      <c r="C4" s="24"/>
-      <c r="D4" s="22"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="18"/>
-      <c r="G4" s="36"/>
-      <c r="H4" s="33"/>
-      <c r="I4" s="23"/>
+      <c r="B4" s="7">
+        <v>45999</v>
+      </c>
+      <c r="C4" s="23">
+        <v>46013</v>
+      </c>
+      <c r="D4" s="79">
+        <v>135812315</v>
+      </c>
+      <c r="E4" s="17">
+        <v>3450176829</v>
+      </c>
+      <c r="F4" s="74" t="s">
+        <v>192</v>
+      </c>
+      <c r="G4" s="31" t="s">
+        <v>40</v>
+      </c>
+      <c r="H4" s="71" t="s">
+        <v>193</v>
+      </c>
+      <c r="I4" s="38">
+        <v>45999</v>
+      </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="7"/>
-      <c r="C5" s="24"/>
-      <c r="D5" s="22"/>
-      <c r="E5" s="17"/>
-      <c r="F5" s="18"/>
-      <c r="G5" s="36"/>
-      <c r="H5" s="34"/>
-      <c r="I5" s="23"/>
+      <c r="B5" s="7">
+        <v>46002</v>
+      </c>
+      <c r="C5" s="23">
+        <v>46013</v>
+      </c>
+      <c r="D5" s="79">
+        <v>135811117</v>
+      </c>
+      <c r="E5" s="17">
+        <v>3450180900</v>
+      </c>
+      <c r="F5" s="74" t="s">
+        <v>194</v>
+      </c>
+      <c r="G5" s="31" t="s">
+        <v>40</v>
+      </c>
+      <c r="H5" s="72" t="s">
+        <v>193</v>
+      </c>
+      <c r="I5" s="38">
+        <v>46002</v>
+      </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="7"/>
-      <c r="C6" s="24"/>
-      <c r="D6" s="22"/>
-      <c r="E6" s="17"/>
-      <c r="F6" s="18"/>
-      <c r="G6" s="37"/>
-      <c r="H6" s="35"/>
-      <c r="I6" s="23"/>
+      <c r="B6" s="7">
+        <v>46006</v>
+      </c>
+      <c r="C6" s="23">
+        <v>46013</v>
+      </c>
+      <c r="D6" s="79">
+        <v>135862092</v>
+      </c>
+      <c r="E6" s="17">
+        <v>3450185398</v>
+      </c>
+      <c r="F6" s="74" t="s">
+        <v>195</v>
+      </c>
+      <c r="G6" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="H6" s="73" t="s">
+        <v>196</v>
+      </c>
+      <c r="I6" s="38">
+        <v>46006</v>
+      </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="7"/>
-      <c r="C7" s="24"/>
-      <c r="D7" s="22"/>
-      <c r="E7" s="17"/>
-      <c r="F7" s="18"/>
-      <c r="G7" s="39"/>
-      <c r="H7" s="35"/>
-      <c r="I7" s="23"/>
+      <c r="B7" s="7">
+        <v>46006</v>
+      </c>
+      <c r="C7" s="23">
+        <v>46013</v>
+      </c>
+      <c r="D7" s="79">
+        <v>135866772</v>
+      </c>
+      <c r="E7" s="17">
+        <v>3450185860</v>
+      </c>
+      <c r="F7" s="74" t="s">
+        <v>197</v>
+      </c>
+      <c r="G7" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="H7" s="73" t="s">
+        <v>198</v>
+      </c>
+      <c r="I7" s="38">
+        <v>46006</v>
+      </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="24"/>
-      <c r="D8" s="22"/>
-      <c r="E8" s="17"/>
-      <c r="F8" s="18"/>
-      <c r="G8" s="40"/>
-      <c r="H8" s="35"/>
-      <c r="I8" s="23"/>
+      <c r="B8" s="7">
+        <v>46001</v>
+      </c>
+      <c r="C8" s="23">
+        <v>46013</v>
+      </c>
+      <c r="D8" s="79">
+        <v>135871496</v>
+      </c>
+      <c r="E8" s="17">
+        <v>3450179425</v>
+      </c>
+      <c r="F8" s="74" t="s">
+        <v>199</v>
+      </c>
+      <c r="G8" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="H8" s="73" t="s">
+        <v>43</v>
+      </c>
+      <c r="I8" s="38">
+        <v>46001</v>
+      </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="7"/>
-      <c r="C9" s="24"/>
-      <c r="D9" s="22"/>
-      <c r="E9" s="17"/>
-      <c r="F9" s="18"/>
-      <c r="G9" s="40"/>
-      <c r="H9" s="33"/>
-      <c r="I9" s="23"/>
+      <c r="B9" s="7">
+        <v>46001</v>
+      </c>
+      <c r="C9" s="23">
+        <v>46013</v>
+      </c>
+      <c r="D9" s="79">
+        <v>135871623</v>
+      </c>
+      <c r="E9" s="17">
+        <v>3450179106</v>
+      </c>
+      <c r="F9" s="74" t="s">
+        <v>200</v>
+      </c>
+      <c r="G9" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="H9" s="73" t="s">
+        <v>201</v>
+      </c>
+      <c r="I9" s="38">
+        <v>46001</v>
+      </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="7"/>
-      <c r="C10" s="24"/>
-      <c r="D10" s="22"/>
-      <c r="E10" s="17"/>
-      <c r="F10" s="18"/>
-      <c r="G10" s="40"/>
-      <c r="H10" s="33"/>
-      <c r="I10" s="23"/>
+      <c r="B10" s="7">
+        <v>45999</v>
+      </c>
+      <c r="C10" s="23">
+        <v>46013</v>
+      </c>
+      <c r="D10" s="79">
+        <v>135752257</v>
+      </c>
+      <c r="E10" s="17">
+        <v>3450176565</v>
+      </c>
+      <c r="F10" s="74" t="s">
+        <v>202</v>
+      </c>
+      <c r="G10" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="H10" s="80" t="s">
+        <v>63</v>
+      </c>
+      <c r="I10" s="38">
+        <v>46010</v>
+      </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="7"/>
-      <c r="C11" s="24"/>
-      <c r="D11" s="22"/>
-      <c r="E11" s="17"/>
-      <c r="F11" s="18"/>
-      <c r="G11" s="40"/>
-      <c r="H11" s="33"/>
-      <c r="I11" s="23"/>
+      <c r="B11" s="7">
+        <v>46006</v>
+      </c>
+      <c r="C11" s="23">
+        <v>46013</v>
+      </c>
+      <c r="D11" s="79">
+        <v>135868110</v>
+      </c>
+      <c r="E11" s="17">
+        <v>3450185970</v>
+      </c>
+      <c r="F11" s="74" t="s">
+        <v>203</v>
+      </c>
+      <c r="G11" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="H11" s="73" t="s">
+        <v>63</v>
+      </c>
+      <c r="I11" s="38">
+        <v>46010</v>
+      </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="7"/>
-      <c r="C12" s="24"/>
-      <c r="D12" s="22"/>
-      <c r="E12" s="17"/>
-      <c r="F12" s="18"/>
-      <c r="G12" s="40"/>
-      <c r="H12" s="33"/>
-      <c r="I12" s="23"/>
+      <c r="B12" s="7">
+        <v>46006</v>
+      </c>
+      <c r="C12" s="23">
+        <v>46013</v>
+      </c>
+      <c r="D12" s="79">
+        <v>135861776</v>
+      </c>
+      <c r="E12" s="17">
+        <v>3450185354</v>
+      </c>
+      <c r="F12" s="74" t="s">
+        <v>204</v>
+      </c>
+      <c r="G12" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="H12" s="73" t="s">
+        <v>205</v>
+      </c>
+      <c r="I12" s="38">
+        <v>46006</v>
+      </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="7"/>
-      <c r="C13" s="24"/>
-      <c r="D13" s="22"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="18"/>
-      <c r="G13" s="40"/>
-      <c r="H13" s="33"/>
-      <c r="I13" s="23"/>
+      <c r="B13" s="7">
+        <v>46007</v>
+      </c>
+      <c r="C13" s="23">
+        <v>46013</v>
+      </c>
+      <c r="D13" s="79">
+        <v>135888226</v>
+      </c>
+      <c r="E13" s="17">
+        <v>3450187455</v>
+      </c>
+      <c r="F13" s="74" t="s">
+        <v>206</v>
+      </c>
+      <c r="G13" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="H13" s="73" t="s">
+        <v>207</v>
+      </c>
+      <c r="I13" s="38">
+        <v>46007</v>
+      </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="7"/>
-      <c r="C14" s="24"/>
-      <c r="D14" s="22"/>
-      <c r="E14" s="17"/>
-      <c r="F14" s="18"/>
-      <c r="G14" s="40"/>
-      <c r="H14" s="33"/>
-      <c r="I14" s="23"/>
+      <c r="B14" s="7">
+        <v>46007</v>
+      </c>
+      <c r="C14" s="23">
+        <v>46013</v>
+      </c>
+      <c r="D14" s="79">
+        <v>135875849</v>
+      </c>
+      <c r="E14" s="17">
+        <v>3450186388</v>
+      </c>
+      <c r="F14" s="74" t="s">
+        <v>208</v>
+      </c>
+      <c r="G14" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="H14" s="73" t="s">
+        <v>191</v>
+      </c>
+      <c r="I14" s="38">
+        <v>46010</v>
+      </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B15" s="7"/>
-      <c r="C15" s="24"/>
-      <c r="D15" s="22"/>
-      <c r="E15" s="17"/>
-      <c r="F15" s="18"/>
-      <c r="G15" s="40"/>
-      <c r="H15" s="33"/>
-      <c r="I15" s="23"/>
+      <c r="B15" s="7">
+        <v>46007</v>
+      </c>
+      <c r="C15" s="23">
+        <v>46013</v>
+      </c>
+      <c r="D15" s="79">
+        <v>135886383</v>
+      </c>
+      <c r="E15" s="17">
+        <v>3450187257</v>
+      </c>
+      <c r="F15" s="74" t="s">
+        <v>209</v>
+      </c>
+      <c r="G15" s="32" t="s">
+        <v>37</v>
+      </c>
+      <c r="H15" s="73" t="s">
+        <v>38</v>
+      </c>
+      <c r="I15" s="38">
+        <v>46007</v>
+      </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B16" s="7"/>
-      <c r="C16" s="24"/>
-      <c r="D16" s="22"/>
-      <c r="E16" s="17"/>
-      <c r="F16" s="11"/>
-      <c r="G16" s="40"/>
-      <c r="H16" s="33"/>
-      <c r="I16" s="23"/>
-    </row>
-    <row r="17" spans="1:9" ht="15" customHeight="1">
-      <c r="A17" s="26" t="s">
-        <v>9</v>
-      </c>
-      <c r="B17" s="7"/>
-      <c r="C17" s="24"/>
-      <c r="D17" s="22"/>
-      <c r="E17" s="17"/>
-      <c r="F17" s="11"/>
-      <c r="G17" s="36"/>
-      <c r="H17" s="33"/>
-      <c r="I17" s="23"/>
+      <c r="B16" s="7">
+        <v>46026</v>
+      </c>
+      <c r="C16" s="23">
+        <v>46013</v>
+      </c>
+      <c r="D16" s="79">
+        <v>135890986</v>
+      </c>
+      <c r="E16" s="17">
+        <v>3450187708</v>
+      </c>
+      <c r="F16" s="74" t="s">
+        <v>210</v>
+      </c>
+      <c r="G16" s="32" t="s">
+        <v>15</v>
+      </c>
+      <c r="H16" s="80" t="s">
+        <v>211</v>
+      </c>
+      <c r="I16" s="38">
+        <v>46009</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B17" s="7">
+        <v>46003</v>
+      </c>
+      <c r="C17" s="23">
+        <v>46013</v>
+      </c>
+      <c r="D17" s="79">
+        <v>135894834</v>
+      </c>
+      <c r="E17" s="17">
+        <v>3450183495</v>
+      </c>
+      <c r="F17" s="74" t="s">
+        <v>212</v>
+      </c>
+      <c r="G17" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="H17" s="73" t="s">
+        <v>213</v>
+      </c>
+      <c r="I17" s="38">
+        <v>46003</v>
+      </c>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B18" s="7"/>
-      <c r="C18" s="24"/>
-      <c r="D18" s="22"/>
-      <c r="E18" s="17"/>
-      <c r="F18" s="11"/>
-      <c r="G18" s="40"/>
-      <c r="H18" s="33"/>
-      <c r="I18" s="23"/>
+      <c r="B18" s="7">
+        <v>46002</v>
+      </c>
+      <c r="C18" s="23">
+        <v>46013</v>
+      </c>
+      <c r="D18" s="79">
+        <v>135894378</v>
+      </c>
+      <c r="E18" s="17">
+        <v>3450181493</v>
+      </c>
+      <c r="F18" s="74" t="s">
+        <v>214</v>
+      </c>
+      <c r="G18" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="H18" s="73" t="s">
+        <v>215</v>
+      </c>
+      <c r="I18" s="38">
+        <v>46002</v>
+      </c>
     </row>
     <row r="19" spans="1:9">
-      <c r="A19" s="6"/>
-      <c r="B19" s="8"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="20"/>
-      <c r="E19" s="29"/>
-      <c r="F19" s="31"/>
-      <c r="G19" s="28"/>
-      <c r="H19" s="9"/>
-      <c r="I19" s="23"/>
+      <c r="A19" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B19" s="7">
+        <v>46008</v>
+      </c>
+      <c r="C19" s="23">
+        <v>46013</v>
+      </c>
+      <c r="D19" s="79">
+        <v>135911447</v>
+      </c>
+      <c r="E19" s="17">
+        <v>3450189370</v>
+      </c>
+      <c r="F19" s="74" t="s">
+        <v>216</v>
+      </c>
+      <c r="G19" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="H19" s="73" t="s">
+        <v>191</v>
+      </c>
+      <c r="I19" s="38">
+        <v>46010</v>
+      </c>
     </row>
     <row r="20" spans="1:9">
-      <c r="A20" s="6"/>
-      <c r="B20" s="8"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="8"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="28"/>
-      <c r="H20" s="9"/>
-      <c r="I20" s="23"/>
+      <c r="A20" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B20" s="7">
+        <v>46007</v>
+      </c>
+      <c r="C20" s="23">
+        <v>46013</v>
+      </c>
+      <c r="D20" s="79">
+        <v>135881322</v>
+      </c>
+      <c r="E20" s="17">
+        <v>3450186850</v>
+      </c>
+      <c r="F20" s="74" t="s">
+        <v>217</v>
+      </c>
+      <c r="G20" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="H20" s="73" t="s">
+        <v>218</v>
+      </c>
+      <c r="I20" s="38">
+        <v>46007</v>
+      </c>
     </row>
     <row r="21" spans="1:9">
-      <c r="A21" s="6"/>
-      <c r="B21" s="8"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="8"/>
-      <c r="E21" s="8"/>
-      <c r="F21" s="9"/>
-      <c r="G21" s="28"/>
-      <c r="H21" s="9"/>
-      <c r="I21" s="23"/>
+      <c r="A21" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B21" s="7">
+        <v>46008</v>
+      </c>
+      <c r="C21" s="23">
+        <v>46013</v>
+      </c>
+      <c r="D21" s="79">
+        <v>135896317</v>
+      </c>
+      <c r="E21" s="17">
+        <v>3450188148</v>
+      </c>
+      <c r="F21" s="74" t="s">
+        <v>219</v>
+      </c>
+      <c r="G21" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="H21" s="73" t="s">
+        <v>191</v>
+      </c>
+      <c r="I21" s="38">
+        <v>46010</v>
+      </c>
     </row>
     <row r="22" spans="1:9">
-      <c r="A22" s="6"/>
-      <c r="B22" s="8"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="8"/>
-      <c r="E22" s="8"/>
-      <c r="F22" s="9"/>
-      <c r="G22" s="28"/>
-      <c r="H22" s="9"/>
-      <c r="I22" s="23"/>
+      <c r="A22" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B22" s="7">
+        <v>46008</v>
+      </c>
+      <c r="C22" s="23">
+        <v>46013</v>
+      </c>
+      <c r="D22" s="79">
+        <v>135912171</v>
+      </c>
+      <c r="E22" s="17">
+        <v>3450189446</v>
+      </c>
+      <c r="F22" s="74" t="s">
+        <v>220</v>
+      </c>
+      <c r="G22" s="32" t="s">
+        <v>37</v>
+      </c>
+      <c r="H22" s="73" t="s">
+        <v>38</v>
+      </c>
+      <c r="I22" s="38">
+        <v>46008</v>
+      </c>
     </row>
     <row r="23" spans="1:9">
-      <c r="A23" s="6"/>
-      <c r="B23" s="8"/>
-      <c r="C23" s="7"/>
-      <c r="D23" s="8"/>
-      <c r="E23" s="8"/>
-      <c r="F23" s="9"/>
-      <c r="G23" s="28"/>
-      <c r="H23" s="9"/>
-      <c r="I23" s="23"/>
+      <c r="A23" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B23" s="7">
+        <v>46009</v>
+      </c>
+      <c r="C23" s="23">
+        <v>46013</v>
+      </c>
+      <c r="D23" s="79">
+        <v>135924259</v>
+      </c>
+      <c r="E23" s="17">
+        <v>3450190205</v>
+      </c>
+      <c r="F23" s="74" t="s">
+        <v>221</v>
+      </c>
+      <c r="G23" s="32" t="s">
+        <v>37</v>
+      </c>
+      <c r="H23" s="73" t="s">
+        <v>38</v>
+      </c>
+      <c r="I23" s="38">
+        <v>46009</v>
+      </c>
     </row>
     <row r="24" spans="1:9">
-      <c r="A24" s="6"/>
-      <c r="B24" s="8"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="8"/>
-      <c r="E24" s="8"/>
-      <c r="F24" s="9"/>
-      <c r="G24" s="28"/>
-      <c r="H24" s="9"/>
-      <c r="I24" s="23"/>
+      <c r="A24" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B24" s="7">
+        <v>46002</v>
+      </c>
+      <c r="C24" s="23">
+        <v>46013</v>
+      </c>
+      <c r="D24" s="79">
+        <v>135894649</v>
+      </c>
+      <c r="E24" s="17">
+        <v>3450180184</v>
+      </c>
+      <c r="F24" s="74" t="s">
+        <v>222</v>
+      </c>
+      <c r="G24" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="H24" s="73" t="s">
+        <v>223</v>
+      </c>
+      <c r="I24" s="38">
+        <v>46002</v>
+      </c>
     </row>
     <row r="25" spans="1:9">
-      <c r="A25" s="6"/>
-      <c r="B25" s="8"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="8"/>
-      <c r="E25" s="8"/>
-      <c r="F25" s="9"/>
-      <c r="G25" s="6"/>
-      <c r="H25" s="9"/>
-      <c r="I25" s="23"/>
+      <c r="A25" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B25" s="7">
+        <v>46036</v>
+      </c>
+      <c r="C25" s="23">
+        <v>46013</v>
+      </c>
+      <c r="D25" s="79">
+        <v>135931820</v>
+      </c>
+      <c r="E25" s="17">
+        <v>3450191063</v>
+      </c>
+      <c r="F25" s="74" t="s">
+        <v>224</v>
+      </c>
+      <c r="G25" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="H25" s="73" t="s">
+        <v>191</v>
+      </c>
+      <c r="I25" s="38">
+        <v>46010</v>
+      </c>
     </row>
     <row r="26" spans="1:9">
-      <c r="A26" s="6"/>
-      <c r="B26" s="8"/>
-      <c r="C26" s="7"/>
-      <c r="D26" s="8"/>
-      <c r="E26" s="8"/>
-      <c r="F26" s="9"/>
-      <c r="G26" s="6"/>
-      <c r="H26" s="9"/>
-      <c r="I26" s="23"/>
+      <c r="A26" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B26" s="7">
+        <v>46009</v>
+      </c>
+      <c r="C26" s="23">
+        <v>46013</v>
+      </c>
+      <c r="D26" s="79">
+        <v>135925147</v>
+      </c>
+      <c r="E26" s="17">
+        <v>3450190425</v>
+      </c>
+      <c r="F26" s="74" t="s">
+        <v>225</v>
+      </c>
+      <c r="G26" s="34" t="s">
+        <v>11</v>
+      </c>
+      <c r="H26" s="73" t="s">
+        <v>191</v>
+      </c>
+      <c r="I26" s="38">
+        <v>46010</v>
+      </c>
     </row>
     <row r="27" spans="1:9">
-      <c r="A27" s="6"/>
-      <c r="B27" s="8"/>
-      <c r="C27" s="7"/>
-      <c r="D27" s="8"/>
-      <c r="E27" s="8"/>
-      <c r="F27" s="9"/>
-      <c r="G27" s="6"/>
-      <c r="H27" s="9"/>
-      <c r="I27" s="23"/>
+      <c r="A27" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B27" s="7">
+        <v>46002</v>
+      </c>
+      <c r="C27" s="23">
+        <v>46013</v>
+      </c>
+      <c r="D27" s="79">
+        <v>135873601</v>
+      </c>
+      <c r="E27" s="17">
+        <v>3450182142</v>
+      </c>
+      <c r="F27" s="74" t="s">
+        <v>226</v>
+      </c>
+      <c r="G27" s="35" t="s">
+        <v>21</v>
+      </c>
+      <c r="H27" s="73" t="s">
+        <v>227</v>
+      </c>
+      <c r="I27" s="38">
+        <v>46002</v>
+      </c>
     </row>
     <row r="28" spans="1:9">
-      <c r="A28" s="6"/>
-      <c r="B28" s="8"/>
-      <c r="C28" s="7"/>
-      <c r="D28" s="8"/>
-      <c r="E28" s="8"/>
-      <c r="F28" s="9"/>
-      <c r="G28" s="6"/>
-      <c r="H28" s="9"/>
-      <c r="I28" s="23"/>
+      <c r="A28" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B28" s="7">
+        <v>46013</v>
+      </c>
+      <c r="C28" s="23">
+        <v>46013</v>
+      </c>
+      <c r="D28" s="79">
+        <v>135926970</v>
+      </c>
+      <c r="E28" s="17">
+        <v>3450190634</v>
+      </c>
+      <c r="F28" s="74" t="s">
+        <v>228</v>
+      </c>
+      <c r="G28" s="35" t="s">
+        <v>11</v>
+      </c>
+      <c r="H28" s="71" t="s">
+        <v>191</v>
+      </c>
+      <c r="I28" s="38">
+        <v>46010</v>
+      </c>
     </row>
     <row r="29" spans="1:9">
-      <c r="A29" s="6"/>
-      <c r="B29" s="8"/>
-      <c r="C29" s="7"/>
-      <c r="D29" s="8"/>
-      <c r="E29" s="8"/>
-      <c r="F29" s="9"/>
-      <c r="G29" s="6"/>
-      <c r="H29" s="9"/>
-      <c r="I29" s="23"/>
+      <c r="A29" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B29" s="7">
+        <v>46038</v>
+      </c>
+      <c r="C29" s="23">
+        <v>46013</v>
+      </c>
+      <c r="D29" s="79">
+        <v>135942800</v>
+      </c>
+      <c r="E29" s="17">
+        <v>3450191833</v>
+      </c>
+      <c r="F29" s="74" t="s">
+        <v>229</v>
+      </c>
+      <c r="G29" s="35" t="s">
+        <v>11</v>
+      </c>
+      <c r="H29" s="71" t="s">
+        <v>191</v>
+      </c>
+      <c r="I29" s="38">
+        <v>46010</v>
+      </c>
     </row>
     <row r="30" spans="1:9">
-      <c r="A30" s="6"/>
-      <c r="B30" s="8"/>
-      <c r="C30" s="7"/>
-      <c r="D30" s="8"/>
-      <c r="E30" s="8"/>
-      <c r="F30" s="9"/>
-      <c r="G30" s="6"/>
-      <c r="H30" s="9"/>
-      <c r="I30" s="23"/>
+      <c r="A30" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B30" s="7">
+        <v>46000</v>
+      </c>
+      <c r="C30" s="23">
+        <v>46013</v>
+      </c>
+      <c r="D30" s="79">
+        <v>135750474</v>
+      </c>
+      <c r="E30" s="17">
+        <v>3450176400</v>
+      </c>
+      <c r="F30" s="74" t="s">
+        <v>230</v>
+      </c>
+      <c r="G30" s="35" t="s">
+        <v>15</v>
+      </c>
+      <c r="H30" s="70" t="s">
+        <v>174</v>
+      </c>
+      <c r="I30" s="38">
+        <v>46002</v>
+      </c>
     </row>
     <row r="31" spans="1:9">
-      <c r="A31" s="6"/>
-      <c r="B31" s="8"/>
-      <c r="C31" s="7"/>
-      <c r="D31" s="8"/>
-      <c r="E31" s="8"/>
-      <c r="F31" s="9"/>
-      <c r="G31" s="6"/>
-      <c r="H31" s="9"/>
-      <c r="I31" s="23"/>
+      <c r="A31" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B31" s="7">
+        <v>46000</v>
+      </c>
+      <c r="C31" s="23">
+        <v>46013</v>
+      </c>
+      <c r="D31" s="79">
+        <v>135762373</v>
+      </c>
+      <c r="E31" s="17">
+        <v>3450177082</v>
+      </c>
+      <c r="F31" s="74" t="s">
+        <v>231</v>
+      </c>
+      <c r="G31" s="35" t="s">
+        <v>11</v>
+      </c>
+      <c r="H31" s="71" t="s">
+        <v>191</v>
+      </c>
+      <c r="I31" s="38">
+        <v>46010</v>
+      </c>
     </row>
     <row r="32" spans="1:9">
-      <c r="A32" s="6"/>
-      <c r="B32" s="8"/>
-      <c r="C32" s="7"/>
-      <c r="D32" s="8"/>
-      <c r="E32" s="8"/>
-      <c r="F32" s="9"/>
-      <c r="G32" s="6"/>
-      <c r="H32" s="9"/>
-      <c r="I32" s="23"/>
+      <c r="A32" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B32" s="7">
+        <v>45996</v>
+      </c>
+      <c r="C32" s="23">
+        <v>46013</v>
+      </c>
+      <c r="D32" s="79">
+        <v>135859177</v>
+      </c>
+      <c r="E32" s="17">
+        <v>3450174497</v>
+      </c>
+      <c r="F32" s="74" t="s">
+        <v>232</v>
+      </c>
+      <c r="G32" s="35" t="s">
+        <v>21</v>
+      </c>
+      <c r="H32" s="71" t="s">
+        <v>233</v>
+      </c>
+      <c r="I32" s="38">
+        <v>45996</v>
+      </c>
     </row>
     <row r="33" spans="1:9">
-      <c r="A33" s="6"/>
-      <c r="B33" s="8"/>
-      <c r="C33" s="7"/>
-      <c r="D33" s="8"/>
-      <c r="E33" s="8"/>
-      <c r="F33" s="9"/>
-      <c r="G33" s="6"/>
-      <c r="H33" s="9"/>
-      <c r="I33" s="23"/>
+      <c r="A33" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B33" s="7">
+        <v>46000</v>
+      </c>
+      <c r="C33" s="23">
+        <v>46013</v>
+      </c>
+      <c r="D33" s="79">
+        <v>135777470</v>
+      </c>
+      <c r="E33" s="17">
+        <v>3450178402</v>
+      </c>
+      <c r="F33" s="74" t="s">
+        <v>234</v>
+      </c>
+      <c r="G33" s="35" t="s">
+        <v>15</v>
+      </c>
+      <c r="H33" s="70" t="s">
+        <v>235</v>
+      </c>
+      <c r="I33" s="38">
+        <v>46003</v>
+      </c>
     </row>
     <row r="34" spans="1:9">
-      <c r="A34" s="6"/>
-      <c r="B34" s="8"/>
-      <c r="C34" s="7"/>
-      <c r="D34" s="8"/>
-      <c r="E34" s="8"/>
-      <c r="F34" s="9"/>
-      <c r="G34" s="6"/>
-      <c r="H34" s="9"/>
-      <c r="I34" s="23"/>
-    </row>
-    <row r="35" spans="1:9">
-      <c r="A35" s="6"/>
-      <c r="B35" s="8"/>
-      <c r="C35" s="7"/>
-      <c r="D35" s="8"/>
-      <c r="E35" s="8"/>
-      <c r="F35" s="9"/>
-      <c r="G35" s="6"/>
-      <c r="H35" s="9"/>
-      <c r="I35" s="23"/>
+      <c r="A34" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B34" s="7">
+        <v>46001</v>
+      </c>
+      <c r="C34" s="23">
+        <v>46013</v>
+      </c>
+      <c r="D34" s="79">
+        <v>135787457</v>
+      </c>
+      <c r="E34" s="17">
+        <v>3450178732</v>
+      </c>
+      <c r="F34" s="74" t="s">
+        <v>236</v>
+      </c>
+      <c r="G34" s="35" t="s">
+        <v>40</v>
+      </c>
+      <c r="H34" s="71" t="s">
+        <v>193</v>
+      </c>
+      <c r="I34" s="38">
+        <v>46001</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" ht="15" customHeight="1">
+      <c r="A35" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="B35" s="7">
+        <v>45996</v>
+      </c>
+      <c r="C35" s="23">
+        <v>46013</v>
+      </c>
+      <c r="D35" s="79">
+        <v>135790032</v>
+      </c>
+      <c r="E35" s="17">
+        <v>3450174783</v>
+      </c>
+      <c r="F35" s="74" t="s">
+        <v>237</v>
+      </c>
+      <c r="G35" s="31" t="s">
+        <v>40</v>
+      </c>
+      <c r="H35" s="71" t="s">
+        <v>193</v>
+      </c>
+      <c r="I35" s="38">
+        <v>45996</v>
+      </c>
     </row>
     <row r="36" spans="1:9">
-      <c r="A36" s="6"/>
-      <c r="B36" s="8"/>
-      <c r="C36" s="7"/>
-      <c r="D36" s="8"/>
-      <c r="E36" s="8"/>
-      <c r="F36" s="9"/>
-      <c r="G36" s="6"/>
-      <c r="H36" s="9"/>
-      <c r="I36"/>
+      <c r="A36" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B36" s="7">
+        <v>46001</v>
+      </c>
+      <c r="C36" s="23">
+        <v>46013</v>
+      </c>
+      <c r="D36" s="79">
+        <v>135790996</v>
+      </c>
+      <c r="E36" s="17">
+        <v>3450179117</v>
+      </c>
+      <c r="F36" s="74" t="s">
+        <v>238</v>
+      </c>
+      <c r="G36" s="35" t="s">
+        <v>40</v>
+      </c>
+      <c r="H36" s="71" t="s">
+        <v>193</v>
+      </c>
+      <c r="I36" s="38">
+        <v>46001</v>
+      </c>
     </row>
     <row r="37" spans="1:9">
-      <c r="A37" s="6"/>
-      <c r="B37" s="8"/>
-      <c r="C37" s="7"/>
-      <c r="D37" s="8"/>
-      <c r="E37" s="8"/>
-      <c r="F37" s="9"/>
-      <c r="G37" s="6"/>
-      <c r="H37" s="9"/>
-      <c r="I37"/>
+      <c r="A37" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B37" s="7">
+        <v>46001</v>
+      </c>
+      <c r="C37" s="23">
+        <v>46013</v>
+      </c>
+      <c r="D37" s="79">
+        <v>135792794</v>
+      </c>
+      <c r="E37" s="17">
+        <v>3450179304</v>
+      </c>
+      <c r="F37" s="74" t="s">
+        <v>239</v>
+      </c>
+      <c r="G37" s="75" t="s">
+        <v>40</v>
+      </c>
+      <c r="H37" s="42" t="s">
+        <v>193</v>
+      </c>
+      <c r="I37" s="38">
+        <v>46001</v>
+      </c>
     </row>
     <row r="38" spans="1:9">
-      <c r="A38" s="6"/>
-      <c r="B38" s="8"/>
-      <c r="C38" s="7"/>
-      <c r="D38" s="8"/>
-      <c r="E38" s="8"/>
-      <c r="F38" s="9"/>
-      <c r="G38" s="6"/>
-      <c r="H38" s="9"/>
-      <c r="I38"/>
+      <c r="A38" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B38" s="7">
+        <v>46001</v>
+      </c>
+      <c r="C38" s="23">
+        <v>46013</v>
+      </c>
+      <c r="D38" s="79">
+        <v>135798684</v>
+      </c>
+      <c r="E38" s="17">
+        <v>3450179821</v>
+      </c>
+      <c r="F38" s="74" t="s">
+        <v>240</v>
+      </c>
+      <c r="G38" s="75" t="s">
+        <v>40</v>
+      </c>
+      <c r="H38" s="42" t="s">
+        <v>193</v>
+      </c>
+      <c r="I38" s="38">
+        <v>46001</v>
+      </c>
     </row>
     <row r="39" spans="1:9">
-      <c r="A39" s="6"/>
-      <c r="B39" s="8"/>
-      <c r="C39" s="7"/>
-      <c r="D39" s="8"/>
-      <c r="E39" s="8"/>
-      <c r="F39" s="9"/>
-      <c r="G39" s="6"/>
-      <c r="H39" s="9"/>
-      <c r="I39"/>
+      <c r="A39" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B39" s="7">
+        <v>46001</v>
+      </c>
+      <c r="C39" s="23">
+        <v>46013</v>
+      </c>
+      <c r="D39" s="79">
+        <v>135800468</v>
+      </c>
+      <c r="E39" s="17">
+        <v>3450179997</v>
+      </c>
+      <c r="F39" s="74" t="s">
+        <v>241</v>
+      </c>
+      <c r="G39" s="75" t="s">
+        <v>40</v>
+      </c>
+      <c r="H39" s="42" t="s">
+        <v>193</v>
+      </c>
+      <c r="I39" s="38">
+        <v>46001</v>
+      </c>
     </row>
     <row r="40" spans="1:9">
-      <c r="A40" s="6"/>
-      <c r="B40" s="8"/>
-      <c r="C40" s="7"/>
-      <c r="D40" s="8"/>
-      <c r="E40" s="8"/>
-      <c r="F40" s="9"/>
-      <c r="G40" s="6"/>
-      <c r="H40" s="9"/>
-      <c r="I40"/>
+      <c r="A40" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B40" s="7">
+        <v>46001</v>
+      </c>
+      <c r="C40" s="23">
+        <v>46013</v>
+      </c>
+      <c r="D40" s="79">
+        <v>135800568</v>
+      </c>
+      <c r="E40" s="17">
+        <v>3450180008</v>
+      </c>
+      <c r="F40" s="74" t="s">
+        <v>170</v>
+      </c>
+      <c r="G40" s="75" t="s">
+        <v>40</v>
+      </c>
+      <c r="H40" s="42" t="s">
+        <v>193</v>
+      </c>
+      <c r="I40" s="38">
+        <v>46001</v>
+      </c>
     </row>
     <row r="41" spans="1:9">
-      <c r="A41" s="6"/>
-      <c r="B41" s="8"/>
-      <c r="C41" s="7"/>
-      <c r="D41" s="8"/>
-      <c r="E41" s="8"/>
-      <c r="F41" s="9"/>
-      <c r="G41" s="6"/>
-      <c r="H41" s="9"/>
-      <c r="I41"/>
+      <c r="A41" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B41" s="7">
+        <v>46002</v>
+      </c>
+      <c r="C41" s="23">
+        <v>46013</v>
+      </c>
+      <c r="D41" s="79">
+        <v>135806463</v>
+      </c>
+      <c r="E41" s="17">
+        <v>3450180350</v>
+      </c>
+      <c r="F41" s="74" t="s">
+        <v>242</v>
+      </c>
+      <c r="G41" s="75" t="s">
+        <v>40</v>
+      </c>
+      <c r="H41" s="42" t="s">
+        <v>193</v>
+      </c>
+      <c r="I41" s="38">
+        <v>46002</v>
+      </c>
     </row>
     <row r="42" spans="1:9">
-      <c r="A42" s="6"/>
-      <c r="B42" s="8"/>
-      <c r="C42" s="7"/>
-      <c r="D42" s="8"/>
-      <c r="E42" s="8"/>
-      <c r="F42" s="9"/>
-      <c r="G42" s="6"/>
-      <c r="H42" s="9"/>
-      <c r="I42"/>
+      <c r="A42" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B42" s="7">
+        <v>46002</v>
+      </c>
+      <c r="C42" s="23">
+        <v>46013</v>
+      </c>
+      <c r="D42" s="79">
+        <v>135806730</v>
+      </c>
+      <c r="E42" s="17">
+        <v>3450180404</v>
+      </c>
+      <c r="F42" s="74" t="s">
+        <v>243</v>
+      </c>
+      <c r="G42" s="75" t="s">
+        <v>40</v>
+      </c>
+      <c r="H42" s="42" t="s">
+        <v>193</v>
+      </c>
+      <c r="I42" s="38">
+        <v>46002</v>
+      </c>
     </row>
     <row r="43" spans="1:9">
-      <c r="A43" s="6"/>
-      <c r="B43" s="8"/>
-      <c r="C43" s="7"/>
-      <c r="D43" s="8"/>
-      <c r="E43" s="8"/>
-      <c r="F43" s="9"/>
-      <c r="G43" s="6"/>
-      <c r="H43" s="9"/>
-      <c r="I43"/>
+      <c r="A43" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B43" s="7">
+        <v>46002</v>
+      </c>
+      <c r="C43" s="23">
+        <v>46013</v>
+      </c>
+      <c r="D43" s="79">
+        <v>135807335</v>
+      </c>
+      <c r="E43" s="17">
+        <v>3450180481</v>
+      </c>
+      <c r="F43" s="74" t="s">
+        <v>243</v>
+      </c>
+      <c r="G43" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="H43" s="42" t="s">
+        <v>193</v>
+      </c>
+      <c r="I43" s="38">
+        <v>46002</v>
+      </c>
     </row>
     <row r="44" spans="1:9">
-      <c r="A44" s="6"/>
-      <c r="B44" s="8"/>
-      <c r="C44" s="7"/>
-      <c r="D44" s="8"/>
-      <c r="E44" s="8"/>
-      <c r="F44" s="9"/>
-      <c r="G44" s="6"/>
-      <c r="H44" s="9"/>
-      <c r="I44"/>
+      <c r="A44" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B44" s="7">
+        <v>46002</v>
+      </c>
+      <c r="C44" s="23">
+        <v>46013</v>
+      </c>
+      <c r="D44" s="79">
+        <v>135809115</v>
+      </c>
+      <c r="E44" s="17">
+        <v>3450180657</v>
+      </c>
+      <c r="F44" s="74" t="s">
+        <v>244</v>
+      </c>
+      <c r="G44" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="H44" s="42" t="s">
+        <v>193</v>
+      </c>
+      <c r="I44" s="38">
+        <v>46002</v>
+      </c>
     </row>
     <row r="45" spans="1:9">
-      <c r="A45" s="6"/>
-      <c r="B45" s="8"/>
-      <c r="C45" s="7"/>
-      <c r="D45" s="8"/>
-      <c r="E45" s="8"/>
-      <c r="F45" s="9"/>
-      <c r="G45" s="6"/>
-      <c r="H45" s="9"/>
-      <c r="I45"/>
+      <c r="A45" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B45" s="7">
+        <v>46002</v>
+      </c>
+      <c r="C45" s="23">
+        <v>46013</v>
+      </c>
+      <c r="D45" s="79">
+        <v>135809266</v>
+      </c>
+      <c r="E45" s="17">
+        <v>3450180679</v>
+      </c>
+      <c r="F45" s="74" t="s">
+        <v>245</v>
+      </c>
+      <c r="G45" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="H45" s="42" t="s">
+        <v>193</v>
+      </c>
+      <c r="I45" s="38">
+        <v>46002</v>
+      </c>
     </row>
     <row r="46" spans="1:9">
       <c r="A46" s="6"/>
       <c r="B46" s="8"/>
       <c r="C46" s="7"/>
-      <c r="D46" s="8"/>
-      <c r="E46" s="8"/>
-      <c r="F46" s="9"/>
+      <c r="D46" s="19"/>
+      <c r="E46" s="19"/>
+      <c r="F46" s="14"/>
       <c r="G46" s="6"/>
-      <c r="H46" s="9"/>
-      <c r="I46"/>
-    </row>
-    <row r="47" spans="1:9">
-      <c r="A47" s="6"/>
-      <c r="B47" s="8"/>
-      <c r="C47" s="7"/>
-      <c r="D47" s="8"/>
-      <c r="E47" s="8"/>
-      <c r="F47" s="9"/>
-      <c r="G47" s="6"/>
-      <c r="H47" s="9"/>
-      <c r="I47"/>
-    </row>
-    <row r="48" spans="1:9">
-      <c r="A48" s="6"/>
-      <c r="B48" s="8"/>
-      <c r="C48" s="7"/>
-      <c r="D48" s="8"/>
-      <c r="E48" s="8"/>
-      <c r="F48" s="9"/>
-      <c r="G48" s="6"/>
-      <c r="H48" s="9"/>
-      <c r="I48"/>
-    </row>
-    <row r="49" spans="1:9">
-      <c r="A49" s="6"/>
-      <c r="B49" s="8"/>
-      <c r="C49" s="7"/>
-      <c r="D49" s="8"/>
-      <c r="E49" s="8"/>
-      <c r="F49" s="9"/>
-      <c r="G49" s="6"/>
-      <c r="H49" s="9"/>
-      <c r="I49"/>
-    </row>
-    <row r="50" spans="1:9">
-      <c r="A50" s="6"/>
-      <c r="B50" s="8"/>
-      <c r="C50" s="7"/>
-      <c r="D50" s="8"/>
-      <c r="E50" s="8"/>
-      <c r="F50" s="9"/>
-      <c r="G50" s="6"/>
-      <c r="H50" s="9"/>
-      <c r="I50"/>
-    </row>
-    <row r="51" spans="1:9">
-      <c r="A51" s="6"/>
-      <c r="B51" s="8"/>
-      <c r="C51" s="7"/>
-      <c r="D51" s="8"/>
-      <c r="E51" s="8"/>
-      <c r="F51" s="9"/>
-      <c r="G51" s="6"/>
-      <c r="H51" s="9"/>
-      <c r="I51"/>
-    </row>
-    <row r="52" spans="1:9">
-      <c r="A52" s="6"/>
-      <c r="B52" s="8"/>
-      <c r="C52" s="7"/>
-      <c r="D52" s="8"/>
-      <c r="E52" s="8"/>
-      <c r="F52" s="9"/>
-      <c r="G52" s="6"/>
-      <c r="H52" s="9"/>
-      <c r="I52"/>
-    </row>
-    <row r="53" spans="1:9">
-      <c r="A53" s="6"/>
-      <c r="B53" s="8"/>
-      <c r="C53" s="7"/>
-      <c r="D53" s="8"/>
-      <c r="E53" s="8"/>
-      <c r="F53" s="9"/>
-      <c r="G53" s="6"/>
-      <c r="H53" s="9"/>
-      <c r="I53"/>
-    </row>
-    <row r="54" spans="1:9">
-      <c r="A54" s="6"/>
-      <c r="B54" s="8"/>
-      <c r="C54" s="7"/>
-      <c r="D54" s="8"/>
-      <c r="E54" s="8"/>
-      <c r="F54" s="9"/>
-      <c r="G54" s="6"/>
-      <c r="H54" s="9"/>
-      <c r="I54"/>
-    </row>
-    <row r="55" spans="1:9">
-      <c r="A55" s="6"/>
-      <c r="B55" s="8"/>
-      <c r="C55" s="7"/>
-      <c r="D55" s="8"/>
-      <c r="E55" s="8"/>
-      <c r="F55" s="9"/>
-      <c r="G55" s="6"/>
-      <c r="H55" s="9"/>
-      <c r="I55"/>
+      <c r="H46" s="42"/>
+      <c r="I46" s="38"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B1:C1">
-    <cfRule type="notContainsBlanks" priority="2">
+    <cfRule type="notContainsBlanks" priority="4">
       <formula>LEN(TRIM(B1))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A18" xr:uid="{33F609D2-9B9D-4D52-B406-6DFCF1363D87}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A45" xr:uid="{33F609D2-9B9D-4D52-B406-6DFCF1363D87}">
       <formula1>#REF!</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G41" xr:uid="{1B2A036A-428B-43C6-B539-9B85A74E7043}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G46" xr:uid="{1B2A036A-428B-43C6-B539-9B85A74E7043}">
       <formula1>"Vistoria Frustrada;,Vistoria Recusada,Bônus;,Desistência;,Inadimplência;,Política de Aceitação;,Duplicidade;,Demais Motivos,Falta de Vistoria;,"</formula1>
     </dataValidation>
   </dataValidations>
@@ -6706,482 +7563,496 @@
       <c r="A2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="24"/>
-      <c r="D2" s="42"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="41"/>
-      <c r="H2" s="44"/>
-      <c r="I2" s="43"/>
+      <c r="B2" s="7">
+        <v>46006</v>
+      </c>
+      <c r="C2" s="23">
+        <v>46014</v>
+      </c>
+      <c r="D2" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="17">
+        <v>3450184859</v>
+      </c>
+      <c r="F2" s="11" t="s">
+        <v>246</v>
+      </c>
+      <c r="G2" s="36" t="s">
+        <v>60</v>
+      </c>
+      <c r="H2" s="39" t="s">
+        <v>247</v>
+      </c>
+      <c r="I2" s="38"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B3" s="7"/>
-      <c r="C3" s="24"/>
-      <c r="D3" s="42"/>
+      <c r="C3" s="23"/>
+      <c r="D3" s="37"/>
       <c r="E3" s="17"/>
       <c r="F3" s="11"/>
-      <c r="G3" s="41"/>
-      <c r="H3" s="44"/>
-      <c r="I3" s="43"/>
+      <c r="G3" s="36"/>
+      <c r="H3" s="39"/>
+      <c r="I3" s="38"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B4" s="7"/>
-      <c r="C4" s="24"/>
-      <c r="D4" s="42"/>
+      <c r="C4" s="23"/>
+      <c r="D4" s="37"/>
       <c r="E4" s="17"/>
       <c r="F4" s="11"/>
-      <c r="G4" s="41"/>
-      <c r="H4" s="44"/>
-      <c r="I4" s="43"/>
+      <c r="G4" s="36"/>
+      <c r="H4" s="39"/>
+      <c r="I4" s="38"/>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B5" s="7"/>
-      <c r="C5" s="24"/>
-      <c r="D5" s="42"/>
+      <c r="C5" s="23"/>
+      <c r="D5" s="37"/>
       <c r="E5" s="17"/>
       <c r="F5" s="11"/>
-      <c r="G5" s="41"/>
-      <c r="H5" s="44"/>
-      <c r="I5" s="43"/>
+      <c r="G5" s="36"/>
+      <c r="H5" s="39"/>
+      <c r="I5" s="38"/>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B6" s="7"/>
-      <c r="C6" s="24"/>
-      <c r="D6" s="42"/>
+      <c r="C6" s="23"/>
+      <c r="D6" s="37"/>
       <c r="E6" s="17"/>
       <c r="F6" s="11"/>
-      <c r="G6" s="41"/>
-      <c r="H6" s="45"/>
-      <c r="I6" s="43"/>
+      <c r="G6" s="36"/>
+      <c r="H6" s="40"/>
+      <c r="I6" s="38"/>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B7" s="7"/>
-      <c r="C7" s="24"/>
-      <c r="D7" s="42"/>
+      <c r="C7" s="23"/>
+      <c r="D7" s="37"/>
       <c r="E7" s="17"/>
       <c r="F7" s="11"/>
-      <c r="G7" s="41"/>
-      <c r="H7" s="45"/>
-      <c r="I7" s="43"/>
+      <c r="G7" s="36"/>
+      <c r="H7" s="40"/>
+      <c r="I7" s="38"/>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B8" s="7"/>
-      <c r="C8" s="24"/>
-      <c r="D8" s="42"/>
+      <c r="C8" s="23"/>
+      <c r="D8" s="37"/>
       <c r="E8" s="17"/>
       <c r="F8" s="11"/>
-      <c r="G8" s="41"/>
-      <c r="H8" s="44"/>
-      <c r="I8" s="43"/>
+      <c r="G8" s="36"/>
+      <c r="H8" s="39"/>
+      <c r="I8" s="38"/>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B9" s="7"/>
-      <c r="C9" s="24"/>
-      <c r="D9" s="42"/>
+      <c r="C9" s="23"/>
+      <c r="D9" s="37"/>
       <c r="E9" s="17"/>
       <c r="F9" s="11"/>
-      <c r="G9" s="41"/>
-      <c r="H9" s="44"/>
-      <c r="I9" s="43"/>
+      <c r="G9" s="36"/>
+      <c r="H9" s="39"/>
+      <c r="I9" s="38"/>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B10" s="7"/>
-      <c r="C10" s="24"/>
-      <c r="D10" s="42"/>
+      <c r="C10" s="23"/>
+      <c r="D10" s="37"/>
       <c r="E10" s="17"/>
       <c r="F10" s="11"/>
-      <c r="G10" s="41"/>
-      <c r="H10" s="44"/>
-      <c r="I10" s="43"/>
+      <c r="G10" s="36"/>
+      <c r="H10" s="39"/>
+      <c r="I10" s="38"/>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B11" s="7"/>
-      <c r="C11" s="24"/>
-      <c r="D11" s="42"/>
+      <c r="C11" s="23"/>
+      <c r="D11" s="37"/>
       <c r="E11" s="17"/>
       <c r="F11" s="11"/>
-      <c r="G11" s="41"/>
-      <c r="H11" s="44"/>
-      <c r="I11" s="43"/>
+      <c r="G11" s="36"/>
+      <c r="H11" s="39"/>
+      <c r="I11" s="38"/>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B12" s="7"/>
-      <c r="C12" s="24"/>
-      <c r="D12" s="42"/>
+      <c r="C12" s="23"/>
+      <c r="D12" s="37"/>
       <c r="E12" s="17"/>
       <c r="F12" s="11"/>
-      <c r="G12" s="41"/>
-      <c r="H12" s="44"/>
-      <c r="I12" s="43"/>
+      <c r="G12" s="36"/>
+      <c r="H12" s="39"/>
+      <c r="I12" s="38"/>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B13" s="7"/>
-      <c r="C13" s="24"/>
-      <c r="D13" s="42"/>
+      <c r="C13" s="23"/>
+      <c r="D13" s="37"/>
       <c r="E13" s="17"/>
       <c r="F13" s="11"/>
-      <c r="G13" s="41"/>
-      <c r="H13" s="44"/>
-      <c r="I13" s="43"/>
+      <c r="G13" s="36"/>
+      <c r="H13" s="39"/>
+      <c r="I13" s="38"/>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B14" s="7"/>
-      <c r="C14" s="24"/>
-      <c r="D14" s="42"/>
+      <c r="C14" s="23"/>
+      <c r="D14" s="37"/>
       <c r="E14" s="17"/>
       <c r="F14" s="11"/>
-      <c r="G14" s="41"/>
-      <c r="H14" s="44"/>
-      <c r="I14" s="43"/>
+      <c r="G14" s="36"/>
+      <c r="H14" s="39"/>
+      <c r="I14" s="38"/>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B15" s="7"/>
-      <c r="C15" s="24"/>
-      <c r="D15" s="42"/>
+      <c r="C15" s="23"/>
+      <c r="D15" s="37"/>
       <c r="E15" s="17"/>
       <c r="F15" s="11"/>
-      <c r="G15" s="41"/>
-      <c r="H15" s="44"/>
-      <c r="I15" s="43"/>
+      <c r="G15" s="36"/>
+      <c r="H15" s="39"/>
+      <c r="I15" s="38"/>
     </row>
     <row r="16" spans="1:9">
-      <c r="A16" s="26" t="s">
+      <c r="A16" s="25" t="s">
         <v>9</v>
       </c>
       <c r="B16" s="7"/>
-      <c r="C16" s="24"/>
-      <c r="D16" s="42"/>
+      <c r="C16" s="23"/>
+      <c r="D16" s="37"/>
       <c r="E16" s="17"/>
       <c r="F16" s="11"/>
-      <c r="G16" s="41"/>
-      <c r="H16" s="44"/>
-      <c r="I16" s="43"/>
+      <c r="G16" s="36"/>
+      <c r="H16" s="39"/>
+      <c r="I16" s="38"/>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B17" s="7"/>
-      <c r="C17" s="24"/>
-      <c r="D17" s="42"/>
+      <c r="C17" s="23"/>
+      <c r="D17" s="37"/>
       <c r="E17" s="17"/>
       <c r="F17" s="11"/>
-      <c r="G17" s="41"/>
-      <c r="H17" s="44"/>
-      <c r="I17" s="43"/>
+      <c r="G17" s="36"/>
+      <c r="H17" s="39"/>
+      <c r="I17" s="38"/>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="6"/>
       <c r="B18" s="7"/>
-      <c r="C18" s="24"/>
-      <c r="D18" s="42"/>
+      <c r="C18" s="23"/>
+      <c r="D18" s="37"/>
       <c r="E18" s="17"/>
       <c r="F18" s="11"/>
-      <c r="G18" s="41"/>
-      <c r="H18" s="44"/>
-      <c r="I18" s="43"/>
+      <c r="G18" s="36"/>
+      <c r="H18" s="39"/>
+      <c r="I18" s="38"/>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" s="6"/>
       <c r="B19" s="7"/>
-      <c r="C19" s="24"/>
-      <c r="D19" s="42"/>
+      <c r="C19" s="23"/>
+      <c r="D19" s="37"/>
       <c r="E19" s="17"/>
       <c r="F19" s="11"/>
-      <c r="G19" s="41"/>
-      <c r="H19" s="44"/>
-      <c r="I19" s="43"/>
+      <c r="G19" s="36"/>
+      <c r="H19" s="39"/>
+      <c r="I19" s="38"/>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="6"/>
       <c r="B20" s="7"/>
-      <c r="C20" s="24"/>
-      <c r="D20" s="42"/>
+      <c r="C20" s="23"/>
+      <c r="D20" s="37"/>
       <c r="E20" s="17"/>
       <c r="F20" s="11"/>
-      <c r="G20" s="41"/>
-      <c r="H20" s="44"/>
-      <c r="I20" s="43"/>
+      <c r="G20" s="36"/>
+      <c r="H20" s="39"/>
+      <c r="I20" s="38"/>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" s="6"/>
       <c r="B21" s="7"/>
-      <c r="C21" s="24"/>
-      <c r="D21" s="42"/>
+      <c r="C21" s="23"/>
+      <c r="D21" s="37"/>
       <c r="E21" s="17"/>
       <c r="F21" s="11"/>
-      <c r="G21" s="41"/>
-      <c r="H21" s="44"/>
-      <c r="I21" s="43"/>
+      <c r="G21" s="36"/>
+      <c r="H21" s="39"/>
+      <c r="I21" s="38"/>
     </row>
     <row r="22" spans="1:9">
       <c r="A22" s="6"/>
       <c r="B22" s="7"/>
-      <c r="C22" s="24"/>
-      <c r="D22" s="42"/>
+      <c r="C22" s="23"/>
+      <c r="D22" s="37"/>
       <c r="E22" s="17"/>
       <c r="F22" s="11"/>
-      <c r="G22" s="41"/>
-      <c r="H22" s="44"/>
-      <c r="I22" s="43"/>
+      <c r="G22" s="36"/>
+      <c r="H22" s="39"/>
+      <c r="I22" s="38"/>
     </row>
     <row r="23" spans="1:9">
       <c r="A23" s="6"/>
       <c r="B23" s="7"/>
-      <c r="C23" s="24"/>
-      <c r="D23" s="42"/>
+      <c r="C23" s="23"/>
+      <c r="D23" s="37"/>
       <c r="E23" s="17"/>
       <c r="F23" s="11"/>
-      <c r="G23" s="41"/>
-      <c r="H23" s="44"/>
-      <c r="I23" s="43"/>
+      <c r="G23" s="36"/>
+      <c r="H23" s="39"/>
+      <c r="I23" s="38"/>
     </row>
     <row r="24" spans="1:9">
       <c r="A24" s="6"/>
       <c r="B24" s="7"/>
-      <c r="C24" s="24"/>
-      <c r="D24" s="42"/>
+      <c r="C24" s="23"/>
+      <c r="D24" s="37"/>
       <c r="E24" s="17"/>
       <c r="F24" s="11"/>
-      <c r="G24" s="41"/>
-      <c r="H24" s="44"/>
-      <c r="I24" s="43"/>
+      <c r="G24" s="36"/>
+      <c r="H24" s="39"/>
+      <c r="I24" s="38"/>
     </row>
     <row r="25" spans="1:9">
       <c r="A25" s="6"/>
       <c r="B25" s="7"/>
-      <c r="C25" s="24"/>
-      <c r="D25" s="42"/>
+      <c r="C25" s="23"/>
+      <c r="D25" s="37"/>
       <c r="E25" s="17"/>
       <c r="F25" s="11"/>
-      <c r="G25" s="41"/>
-      <c r="H25" s="44"/>
-      <c r="I25" s="43"/>
+      <c r="G25" s="36"/>
+      <c r="H25" s="39"/>
+      <c r="I25" s="38"/>
     </row>
     <row r="26" spans="1:9">
       <c r="A26" s="6"/>
       <c r="B26" s="7"/>
-      <c r="C26" s="24"/>
-      <c r="D26" s="42"/>
+      <c r="C26" s="23"/>
+      <c r="D26" s="37"/>
       <c r="E26" s="17"/>
       <c r="F26" s="11"/>
-      <c r="G26" s="41"/>
-      <c r="H26" s="44"/>
-      <c r="I26" s="43"/>
+      <c r="G26" s="36"/>
+      <c r="H26" s="39"/>
+      <c r="I26" s="38"/>
     </row>
     <row r="27" spans="1:9">
       <c r="A27" s="6"/>
       <c r="B27" s="7"/>
-      <c r="C27" s="24"/>
-      <c r="D27" s="42"/>
+      <c r="C27" s="23"/>
+      <c r="D27" s="37"/>
       <c r="E27" s="17"/>
       <c r="F27" s="11"/>
-      <c r="G27" s="41"/>
-      <c r="H27" s="44"/>
-      <c r="I27" s="43"/>
+      <c r="G27" s="36"/>
+      <c r="H27" s="39"/>
+      <c r="I27" s="38"/>
     </row>
     <row r="28" spans="1:9">
       <c r="A28" s="6"/>
-      <c r="B28" s="46"/>
-      <c r="C28" s="24"/>
-      <c r="D28" s="42"/>
+      <c r="B28" s="41"/>
+      <c r="C28" s="23"/>
+      <c r="D28" s="37"/>
       <c r="E28" s="17"/>
       <c r="F28" s="11"/>
-      <c r="G28" s="41"/>
-      <c r="H28" s="44"/>
-      <c r="I28" s="43"/>
+      <c r="G28" s="36"/>
+      <c r="H28" s="39"/>
+      <c r="I28" s="38"/>
     </row>
     <row r="29" spans="1:9">
       <c r="A29" s="6"/>
       <c r="B29" s="7"/>
-      <c r="C29" s="24"/>
-      <c r="D29" s="42"/>
+      <c r="C29" s="23"/>
+      <c r="D29" s="37"/>
       <c r="E29" s="17"/>
       <c r="F29" s="11"/>
-      <c r="G29" s="41"/>
+      <c r="G29" s="36"/>
       <c r="H29" s="12"/>
-      <c r="I29" s="43"/>
+      <c r="I29" s="38"/>
     </row>
     <row r="30" spans="1:9">
       <c r="A30" s="6"/>
       <c r="B30" s="7"/>
-      <c r="C30" s="24"/>
-      <c r="D30" s="42"/>
+      <c r="C30" s="23"/>
+      <c r="D30" s="37"/>
       <c r="E30" s="17"/>
       <c r="F30" s="11"/>
-      <c r="G30" s="41"/>
+      <c r="G30" s="36"/>
       <c r="H30" s="12"/>
-      <c r="I30" s="43"/>
+      <c r="I30" s="38"/>
     </row>
     <row r="31" spans="1:9">
       <c r="A31" s="6"/>
       <c r="B31" s="7"/>
-      <c r="C31" s="24"/>
-      <c r="D31" s="42"/>
+      <c r="C31" s="23"/>
+      <c r="D31" s="37"/>
       <c r="E31" s="17"/>
       <c r="F31" s="11"/>
-      <c r="G31" s="41"/>
+      <c r="G31" s="36"/>
       <c r="H31" s="12"/>
-      <c r="I31" s="43"/>
+      <c r="I31" s="38"/>
     </row>
     <row r="32" spans="1:9">
       <c r="A32" s="6"/>
       <c r="B32" s="7"/>
-      <c r="C32" s="24"/>
-      <c r="D32" s="42"/>
+      <c r="C32" s="23"/>
+      <c r="D32" s="37"/>
       <c r="E32" s="17"/>
       <c r="F32" s="11"/>
-      <c r="G32" s="41"/>
+      <c r="G32" s="36"/>
       <c r="H32" s="12"/>
-      <c r="I32" s="43"/>
+      <c r="I32" s="38"/>
     </row>
     <row r="33" spans="1:9">
       <c r="A33" s="6"/>
       <c r="B33" s="7"/>
-      <c r="C33" s="24"/>
-      <c r="D33" s="42"/>
+      <c r="C33" s="23"/>
+      <c r="D33" s="37"/>
       <c r="E33" s="17"/>
       <c r="F33" s="11"/>
-      <c r="G33" s="41"/>
+      <c r="G33" s="36"/>
       <c r="H33" s="12"/>
-      <c r="I33" s="43"/>
+      <c r="I33" s="38"/>
     </row>
     <row r="34" spans="1:9">
       <c r="A34" s="6"/>
       <c r="B34" s="7"/>
-      <c r="C34" s="24"/>
-      <c r="D34" s="42"/>
+      <c r="C34" s="23"/>
+      <c r="D34" s="37"/>
       <c r="E34" s="17"/>
       <c r="F34" s="11"/>
-      <c r="G34" s="41"/>
+      <c r="G34" s="36"/>
       <c r="H34" s="12"/>
-      <c r="I34" s="43"/>
+      <c r="I34" s="38"/>
     </row>
     <row r="35" spans="1:9">
       <c r="A35" s="6"/>
       <c r="B35" s="7"/>
-      <c r="C35" s="24"/>
-      <c r="D35" s="42"/>
+      <c r="C35" s="23"/>
+      <c r="D35" s="37"/>
       <c r="E35" s="17"/>
       <c r="F35" s="11"/>
-      <c r="G35" s="41"/>
+      <c r="G35" s="36"/>
       <c r="H35" s="12"/>
-      <c r="I35" s="43"/>
+      <c r="I35" s="38"/>
     </row>
     <row r="36" spans="1:9">
       <c r="A36" s="6"/>
       <c r="B36" s="7"/>
-      <c r="C36" s="24"/>
-      <c r="D36" s="42"/>
+      <c r="C36" s="23"/>
+      <c r="D36" s="37"/>
       <c r="E36" s="17"/>
       <c r="F36" s="11"/>
-      <c r="G36" s="41"/>
+      <c r="G36" s="36"/>
       <c r="H36" s="12"/>
-      <c r="I36" s="43"/>
+      <c r="I36" s="38"/>
     </row>
     <row r="37" spans="1:9">
       <c r="A37" s="6"/>
       <c r="B37" s="7"/>
-      <c r="C37" s="24"/>
-      <c r="D37" s="42"/>
+      <c r="C37" s="23"/>
+      <c r="D37" s="37"/>
       <c r="E37" s="17"/>
       <c r="F37" s="11"/>
-      <c r="G37" s="41"/>
+      <c r="G37" s="36"/>
       <c r="H37" s="12"/>
-      <c r="I37" s="43"/>
+      <c r="I37" s="38"/>
     </row>
     <row r="38" spans="1:9">
       <c r="A38" s="6"/>
       <c r="B38" s="7"/>
-      <c r="C38" s="24"/>
-      <c r="D38" s="42"/>
+      <c r="C38" s="23"/>
+      <c r="D38" s="37"/>
       <c r="E38" s="17"/>
       <c r="F38" s="11"/>
-      <c r="G38" s="41"/>
+      <c r="G38" s="36"/>
       <c r="H38" s="12"/>
-      <c r="I38" s="43"/>
+      <c r="I38" s="38"/>
     </row>
     <row r="39" spans="1:9">
       <c r="A39" s="6"/>
       <c r="B39" s="7"/>
-      <c r="C39" s="24"/>
-      <c r="D39" s="42"/>
+      <c r="C39" s="23"/>
+      <c r="D39" s="37"/>
       <c r="E39" s="17"/>
       <c r="F39" s="11"/>
-      <c r="G39" s="41"/>
+      <c r="G39" s="36"/>
       <c r="H39" s="12"/>
-      <c r="I39" s="43"/>
+      <c r="I39" s="38"/>
     </row>
     <row r="40" spans="1:9">
       <c r="A40" s="6"/>
       <c r="B40" s="7"/>
-      <c r="C40" s="24"/>
-      <c r="D40" s="42"/>
+      <c r="C40" s="23"/>
+      <c r="D40" s="37"/>
       <c r="E40" s="17"/>
       <c r="F40" s="11"/>
-      <c r="G40" s="41"/>
+      <c r="G40" s="36"/>
       <c r="H40" s="12"/>
-      <c r="I40" s="43"/>
+      <c r="I40" s="38"/>
     </row>
     <row r="41" spans="1:9">
       <c r="A41" s="6"/>
       <c r="B41" s="7"/>
-      <c r="C41" s="24"/>
-      <c r="D41" s="42"/>
+      <c r="C41" s="23"/>
+      <c r="D41" s="37"/>
       <c r="E41" s="17"/>
       <c r="F41" s="11"/>
-      <c r="G41" s="41"/>
+      <c r="G41" s="36"/>
       <c r="H41" s="12"/>
-      <c r="I41" s="43"/>
+      <c r="I41" s="38"/>
     </row>
     <row r="42" spans="1:9">
       <c r="A42" s="6"/>
       <c r="B42" s="8"/>
       <c r="C42" s="7"/>
-      <c r="D42" s="29"/>
+      <c r="D42" s="28"/>
       <c r="E42" s="17"/>
       <c r="F42" s="12"/>
-      <c r="G42" s="41"/>
+      <c r="G42" s="36"/>
       <c r="H42" s="12"/>
       <c r="I42" s="12"/>
     </row>
@@ -7265,494 +8136,494 @@
         <v>9</v>
       </c>
       <c r="B2" s="7"/>
-      <c r="C2" s="24"/>
-      <c r="D2" s="42"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="37"/>
       <c r="E2" s="17"/>
       <c r="F2" s="11"/>
-      <c r="G2" s="41"/>
-      <c r="H2" s="44"/>
-      <c r="I2" s="43"/>
+      <c r="G2" s="36"/>
+      <c r="H2" s="39"/>
+      <c r="I2" s="38"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B3" s="7"/>
-      <c r="C3" s="24"/>
-      <c r="D3" s="42"/>
+      <c r="C3" s="23"/>
+      <c r="D3" s="37"/>
       <c r="E3" s="17"/>
       <c r="F3" s="11"/>
-      <c r="G3" s="41"/>
-      <c r="H3" s="44"/>
-      <c r="I3" s="43"/>
+      <c r="G3" s="36"/>
+      <c r="H3" s="39"/>
+      <c r="I3" s="38"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B4" s="7"/>
-      <c r="C4" s="24"/>
-      <c r="D4" s="42"/>
+      <c r="C4" s="23"/>
+      <c r="D4" s="37"/>
       <c r="E4" s="17"/>
       <c r="F4" s="11"/>
-      <c r="G4" s="41"/>
-      <c r="H4" s="44"/>
-      <c r="I4" s="43"/>
+      <c r="G4" s="36"/>
+      <c r="H4" s="39"/>
+      <c r="I4" s="38"/>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B5" s="7"/>
-      <c r="C5" s="24"/>
-      <c r="D5" s="42"/>
+      <c r="C5" s="23"/>
+      <c r="D5" s="37"/>
       <c r="E5" s="17"/>
       <c r="F5" s="11"/>
-      <c r="G5" s="41"/>
-      <c r="H5" s="44"/>
-      <c r="I5" s="43"/>
+      <c r="G5" s="36"/>
+      <c r="H5" s="39"/>
+      <c r="I5" s="38"/>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B6" s="7"/>
-      <c r="C6" s="24"/>
-      <c r="D6" s="42"/>
+      <c r="C6" s="23"/>
+      <c r="D6" s="37"/>
       <c r="E6" s="17"/>
       <c r="F6" s="11"/>
-      <c r="G6" s="41"/>
-      <c r="H6" s="44"/>
-      <c r="I6" s="43"/>
+      <c r="G6" s="36"/>
+      <c r="H6" s="39"/>
+      <c r="I6" s="38"/>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B7" s="7"/>
-      <c r="C7" s="24"/>
-      <c r="D7" s="42"/>
+      <c r="C7" s="23"/>
+      <c r="D7" s="37"/>
       <c r="E7" s="17"/>
       <c r="F7" s="11"/>
-      <c r="G7" s="41"/>
-      <c r="H7" s="45"/>
-      <c r="I7" s="43"/>
+      <c r="G7" s="36"/>
+      <c r="H7" s="40"/>
+      <c r="I7" s="38"/>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B8" s="7"/>
-      <c r="C8" s="24"/>
-      <c r="D8" s="42"/>
+      <c r="C8" s="23"/>
+      <c r="D8" s="37"/>
       <c r="E8" s="17"/>
       <c r="F8" s="11"/>
-      <c r="G8" s="41"/>
-      <c r="H8" s="45"/>
-      <c r="I8" s="43"/>
+      <c r="G8" s="36"/>
+      <c r="H8" s="40"/>
+      <c r="I8" s="38"/>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B9" s="7"/>
-      <c r="C9" s="24"/>
-      <c r="D9" s="42"/>
+      <c r="C9" s="23"/>
+      <c r="D9" s="37"/>
       <c r="E9" s="17"/>
       <c r="F9" s="11"/>
-      <c r="G9" s="41"/>
-      <c r="H9" s="44"/>
-      <c r="I9" s="43"/>
+      <c r="G9" s="36"/>
+      <c r="H9" s="39"/>
+      <c r="I9" s="38"/>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B10" s="7"/>
-      <c r="C10" s="24"/>
-      <c r="D10" s="42"/>
+      <c r="C10" s="23"/>
+      <c r="D10" s="37"/>
       <c r="E10" s="17"/>
       <c r="F10" s="11"/>
-      <c r="G10" s="41"/>
-      <c r="H10" s="44"/>
-      <c r="I10" s="43"/>
+      <c r="G10" s="36"/>
+      <c r="H10" s="39"/>
+      <c r="I10" s="38"/>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B11" s="7"/>
-      <c r="C11" s="24"/>
-      <c r="D11" s="42"/>
+      <c r="C11" s="23"/>
+      <c r="D11" s="37"/>
       <c r="E11" s="17"/>
       <c r="F11" s="11"/>
-      <c r="G11" s="41"/>
-      <c r="H11" s="44"/>
-      <c r="I11" s="43"/>
+      <c r="G11" s="36"/>
+      <c r="H11" s="39"/>
+      <c r="I11" s="38"/>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B12" s="7"/>
-      <c r="C12" s="24"/>
-      <c r="D12" s="42"/>
+      <c r="C12" s="23"/>
+      <c r="D12" s="37"/>
       <c r="E12" s="17"/>
       <c r="F12" s="11"/>
-      <c r="G12" s="41"/>
-      <c r="H12" s="44"/>
-      <c r="I12" s="43"/>
+      <c r="G12" s="36"/>
+      <c r="H12" s="39"/>
+      <c r="I12" s="38"/>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B13" s="7"/>
-      <c r="C13" s="24"/>
-      <c r="D13" s="42"/>
+      <c r="C13" s="23"/>
+      <c r="D13" s="37"/>
       <c r="E13" s="17"/>
       <c r="F13" s="11"/>
-      <c r="G13" s="41"/>
-      <c r="H13" s="44"/>
-      <c r="I13" s="43"/>
+      <c r="G13" s="36"/>
+      <c r="H13" s="39"/>
+      <c r="I13" s="38"/>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B14" s="7"/>
-      <c r="C14" s="24"/>
-      <c r="D14" s="42"/>
+      <c r="C14" s="23"/>
+      <c r="D14" s="37"/>
       <c r="E14" s="17"/>
       <c r="F14" s="11"/>
-      <c r="G14" s="41"/>
-      <c r="H14" s="44"/>
-      <c r="I14" s="43"/>
+      <c r="G14" s="36"/>
+      <c r="H14" s="39"/>
+      <c r="I14" s="38"/>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B15" s="7"/>
-      <c r="C15" s="24"/>
-      <c r="D15" s="42"/>
+      <c r="C15" s="23"/>
+      <c r="D15" s="37"/>
       <c r="E15" s="17"/>
       <c r="F15" s="11"/>
-      <c r="G15" s="41"/>
-      <c r="H15" s="44"/>
-      <c r="I15" s="43"/>
+      <c r="G15" s="36"/>
+      <c r="H15" s="39"/>
+      <c r="I15" s="38"/>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B16" s="7"/>
-      <c r="C16" s="24"/>
-      <c r="D16" s="42"/>
+      <c r="C16" s="23"/>
+      <c r="D16" s="37"/>
       <c r="E16" s="17"/>
       <c r="F16" s="11"/>
-      <c r="G16" s="41"/>
-      <c r="H16" s="44"/>
-      <c r="I16" s="43"/>
+      <c r="G16" s="36"/>
+      <c r="H16" s="39"/>
+      <c r="I16" s="38"/>
     </row>
     <row r="17" spans="1:9">
-      <c r="A17" s="26" t="s">
+      <c r="A17" s="25" t="s">
         <v>9</v>
       </c>
       <c r="B17" s="7"/>
-      <c r="C17" s="24"/>
-      <c r="D17" s="42"/>
+      <c r="C17" s="23"/>
+      <c r="D17" s="37"/>
       <c r="E17" s="17"/>
       <c r="F17" s="11"/>
-      <c r="G17" s="41"/>
-      <c r="H17" s="44"/>
-      <c r="I17" s="43"/>
+      <c r="G17" s="36"/>
+      <c r="H17" s="39"/>
+      <c r="I17" s="38"/>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B18" s="7"/>
-      <c r="C18" s="24"/>
-      <c r="D18" s="42"/>
+      <c r="C18" s="23"/>
+      <c r="D18" s="37"/>
       <c r="E18" s="17"/>
       <c r="F18" s="11"/>
-      <c r="G18" s="41"/>
-      <c r="H18" s="44"/>
-      <c r="I18" s="43"/>
+      <c r="G18" s="36"/>
+      <c r="H18" s="39"/>
+      <c r="I18" s="38"/>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" s="6"/>
       <c r="B19" s="7"/>
-      <c r="C19" s="24"/>
-      <c r="D19" s="42"/>
+      <c r="C19" s="23"/>
+      <c r="D19" s="37"/>
       <c r="E19" s="17"/>
       <c r="F19" s="11"/>
-      <c r="G19" s="41"/>
-      <c r="H19" s="44"/>
-      <c r="I19" s="43"/>
+      <c r="G19" s="36"/>
+      <c r="H19" s="39"/>
+      <c r="I19" s="38"/>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="6"/>
       <c r="B20" s="7"/>
-      <c r="C20" s="24"/>
-      <c r="D20" s="42"/>
+      <c r="C20" s="23"/>
+      <c r="D20" s="37"/>
       <c r="E20" s="17"/>
       <c r="F20" s="11"/>
-      <c r="G20" s="41"/>
-      <c r="H20" s="44"/>
-      <c r="I20" s="43"/>
+      <c r="G20" s="36"/>
+      <c r="H20" s="39"/>
+      <c r="I20" s="38"/>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" s="6"/>
       <c r="B21" s="7"/>
-      <c r="C21" s="24"/>
-      <c r="D21" s="42"/>
+      <c r="C21" s="23"/>
+      <c r="D21" s="37"/>
       <c r="E21" s="17"/>
       <c r="F21" s="11"/>
-      <c r="G21" s="41"/>
-      <c r="H21" s="44"/>
-      <c r="I21" s="43"/>
+      <c r="G21" s="36"/>
+      <c r="H21" s="39"/>
+      <c r="I21" s="38"/>
     </row>
     <row r="22" spans="1:9">
       <c r="A22" s="6"/>
       <c r="B22" s="7"/>
-      <c r="C22" s="24"/>
-      <c r="D22" s="42"/>
+      <c r="C22" s="23"/>
+      <c r="D22" s="37"/>
       <c r="E22" s="17"/>
       <c r="F22" s="11"/>
-      <c r="G22" s="41"/>
-      <c r="H22" s="44"/>
-      <c r="I22" s="43"/>
+      <c r="G22" s="36"/>
+      <c r="H22" s="39"/>
+      <c r="I22" s="38"/>
     </row>
     <row r="23" spans="1:9">
       <c r="A23" s="6"/>
       <c r="B23" s="7"/>
-      <c r="C23" s="24"/>
-      <c r="D23" s="42"/>
+      <c r="C23" s="23"/>
+      <c r="D23" s="37"/>
       <c r="E23" s="17"/>
       <c r="F23" s="11"/>
-      <c r="G23" s="41"/>
-      <c r="H23" s="44"/>
-      <c r="I23" s="43"/>
+      <c r="G23" s="36"/>
+      <c r="H23" s="39"/>
+      <c r="I23" s="38"/>
     </row>
     <row r="24" spans="1:9">
       <c r="A24" s="6"/>
       <c r="B24" s="7"/>
-      <c r="C24" s="24"/>
-      <c r="D24" s="42"/>
+      <c r="C24" s="23"/>
+      <c r="D24" s="37"/>
       <c r="E24" s="17"/>
       <c r="F24" s="11"/>
-      <c r="G24" s="41"/>
-      <c r="H24" s="44"/>
-      <c r="I24" s="43"/>
+      <c r="G24" s="36"/>
+      <c r="H24" s="39"/>
+      <c r="I24" s="38"/>
     </row>
     <row r="25" spans="1:9">
       <c r="A25" s="6"/>
       <c r="B25" s="7"/>
-      <c r="C25" s="24"/>
-      <c r="D25" s="42"/>
+      <c r="C25" s="23"/>
+      <c r="D25" s="37"/>
       <c r="E25" s="17"/>
       <c r="F25" s="11"/>
-      <c r="G25" s="41"/>
-      <c r="H25" s="44"/>
-      <c r="I25" s="43"/>
+      <c r="G25" s="36"/>
+      <c r="H25" s="39"/>
+      <c r="I25" s="38"/>
     </row>
     <row r="26" spans="1:9">
       <c r="A26" s="6"/>
       <c r="B26" s="7"/>
-      <c r="C26" s="24"/>
-      <c r="D26" s="42"/>
+      <c r="C26" s="23"/>
+      <c r="D26" s="37"/>
       <c r="E26" s="17"/>
       <c r="F26" s="11"/>
-      <c r="G26" s="41"/>
-      <c r="H26" s="44"/>
-      <c r="I26" s="43"/>
+      <c r="G26" s="36"/>
+      <c r="H26" s="39"/>
+      <c r="I26" s="38"/>
     </row>
     <row r="27" spans="1:9">
       <c r="A27" s="6"/>
       <c r="B27" s="7"/>
-      <c r="C27" s="24"/>
-      <c r="D27" s="42"/>
+      <c r="C27" s="23"/>
+      <c r="D27" s="37"/>
       <c r="E27" s="17"/>
       <c r="F27" s="11"/>
-      <c r="G27" s="41"/>
-      <c r="H27" s="44"/>
-      <c r="I27" s="43"/>
+      <c r="G27" s="36"/>
+      <c r="H27" s="39"/>
+      <c r="I27" s="38"/>
     </row>
     <row r="28" spans="1:9">
       <c r="A28" s="6"/>
       <c r="B28" s="7"/>
-      <c r="C28" s="24"/>
-      <c r="D28" s="42"/>
+      <c r="C28" s="23"/>
+      <c r="D28" s="37"/>
       <c r="E28" s="17"/>
       <c r="F28" s="11"/>
-      <c r="G28" s="41"/>
-      <c r="H28" s="44"/>
-      <c r="I28" s="43"/>
+      <c r="G28" s="36"/>
+      <c r="H28" s="39"/>
+      <c r="I28" s="38"/>
     </row>
     <row r="29" spans="1:9">
       <c r="A29" s="6"/>
-      <c r="B29" s="46"/>
-      <c r="C29" s="24"/>
-      <c r="D29" s="42"/>
+      <c r="B29" s="41"/>
+      <c r="C29" s="23"/>
+      <c r="D29" s="37"/>
       <c r="E29" s="17"/>
       <c r="F29" s="11"/>
-      <c r="G29" s="41"/>
-      <c r="H29" s="44"/>
-      <c r="I29" s="43"/>
+      <c r="G29" s="36"/>
+      <c r="H29" s="39"/>
+      <c r="I29" s="38"/>
     </row>
     <row r="30" spans="1:9">
       <c r="A30" s="6"/>
       <c r="B30" s="7"/>
-      <c r="C30" s="24"/>
-      <c r="D30" s="42"/>
+      <c r="C30" s="23"/>
+      <c r="D30" s="37"/>
       <c r="E30" s="17"/>
       <c r="F30" s="11"/>
-      <c r="G30" s="41"/>
+      <c r="G30" s="36"/>
       <c r="H30" s="12"/>
-      <c r="I30" s="43"/>
+      <c r="I30" s="38"/>
     </row>
     <row r="31" spans="1:9">
       <c r="A31" s="6"/>
       <c r="B31" s="7"/>
-      <c r="C31" s="24"/>
-      <c r="D31" s="42"/>
+      <c r="C31" s="23"/>
+      <c r="D31" s="37"/>
       <c r="E31" s="17"/>
       <c r="F31" s="11"/>
-      <c r="G31" s="41"/>
+      <c r="G31" s="36"/>
       <c r="H31" s="12"/>
-      <c r="I31" s="43"/>
+      <c r="I31" s="38"/>
     </row>
     <row r="32" spans="1:9">
       <c r="A32" s="6"/>
       <c r="B32" s="7"/>
-      <c r="C32" s="24"/>
-      <c r="D32" s="42"/>
+      <c r="C32" s="23"/>
+      <c r="D32" s="37"/>
       <c r="E32" s="17"/>
       <c r="F32" s="11"/>
-      <c r="G32" s="41"/>
+      <c r="G32" s="36"/>
       <c r="H32" s="12"/>
-      <c r="I32" s="43"/>
+      <c r="I32" s="38"/>
     </row>
     <row r="33" spans="1:9">
       <c r="A33" s="6"/>
       <c r="B33" s="7"/>
-      <c r="C33" s="24"/>
-      <c r="D33" s="42"/>
+      <c r="C33" s="23"/>
+      <c r="D33" s="37"/>
       <c r="E33" s="17"/>
       <c r="F33" s="11"/>
-      <c r="G33" s="41"/>
+      <c r="G33" s="36"/>
       <c r="H33" s="12"/>
-      <c r="I33" s="43"/>
+      <c r="I33" s="38"/>
     </row>
     <row r="34" spans="1:9">
       <c r="A34" s="6"/>
       <c r="B34" s="7"/>
-      <c r="C34" s="24"/>
-      <c r="D34" s="42"/>
+      <c r="C34" s="23"/>
+      <c r="D34" s="37"/>
       <c r="E34" s="17"/>
       <c r="F34" s="11"/>
-      <c r="G34" s="41"/>
+      <c r="G34" s="36"/>
       <c r="H34" s="12"/>
-      <c r="I34" s="43"/>
+      <c r="I34" s="38"/>
     </row>
     <row r="35" spans="1:9">
       <c r="A35" s="6"/>
       <c r="B35" s="7"/>
-      <c r="C35" s="24"/>
-      <c r="D35" s="42"/>
+      <c r="C35" s="23"/>
+      <c r="D35" s="37"/>
       <c r="E35" s="17"/>
       <c r="F35" s="11"/>
-      <c r="G35" s="41"/>
+      <c r="G35" s="36"/>
       <c r="H35" s="12"/>
-      <c r="I35" s="43"/>
+      <c r="I35" s="38"/>
     </row>
     <row r="36" spans="1:9">
       <c r="A36" s="6"/>
       <c r="B36" s="7"/>
-      <c r="C36" s="24"/>
-      <c r="D36" s="42"/>
+      <c r="C36" s="23"/>
+      <c r="D36" s="37"/>
       <c r="E36" s="17"/>
       <c r="F36" s="11"/>
-      <c r="G36" s="41"/>
+      <c r="G36" s="36"/>
       <c r="H36" s="12"/>
-      <c r="I36" s="43"/>
+      <c r="I36" s="38"/>
     </row>
     <row r="37" spans="1:9">
       <c r="A37" s="6"/>
       <c r="B37" s="7"/>
-      <c r="C37" s="24"/>
-      <c r="D37" s="42"/>
+      <c r="C37" s="23"/>
+      <c r="D37" s="37"/>
       <c r="E37" s="17"/>
       <c r="F37" s="11"/>
-      <c r="G37" s="41"/>
+      <c r="G37" s="36"/>
       <c r="H37" s="12"/>
-      <c r="I37" s="43"/>
+      <c r="I37" s="38"/>
     </row>
     <row r="38" spans="1:9">
       <c r="A38" s="6"/>
       <c r="B38" s="7"/>
-      <c r="C38" s="24"/>
-      <c r="D38" s="42"/>
+      <c r="C38" s="23"/>
+      <c r="D38" s="37"/>
       <c r="E38" s="17"/>
       <c r="F38" s="11"/>
-      <c r="G38" s="41"/>
+      <c r="G38" s="36"/>
       <c r="H38" s="12"/>
-      <c r="I38" s="43"/>
+      <c r="I38" s="38"/>
     </row>
     <row r="39" spans="1:9">
       <c r="A39" s="6"/>
       <c r="B39" s="7"/>
-      <c r="C39" s="24"/>
-      <c r="D39" s="42"/>
+      <c r="C39" s="23"/>
+      <c r="D39" s="37"/>
       <c r="E39" s="17"/>
       <c r="F39" s="11"/>
-      <c r="G39" s="41"/>
+      <c r="G39" s="36"/>
       <c r="H39" s="12"/>
-      <c r="I39" s="43"/>
+      <c r="I39" s="38"/>
     </row>
     <row r="40" spans="1:9">
       <c r="A40" s="6"/>
       <c r="B40" s="7"/>
-      <c r="C40" s="24"/>
-      <c r="D40" s="42"/>
+      <c r="C40" s="23"/>
+      <c r="D40" s="37"/>
       <c r="E40" s="17"/>
       <c r="F40" s="11"/>
-      <c r="G40" s="41"/>
+      <c r="G40" s="36"/>
       <c r="H40" s="12"/>
-      <c r="I40" s="43"/>
+      <c r="I40" s="38"/>
     </row>
     <row r="41" spans="1:9">
       <c r="A41" s="6"/>
       <c r="B41" s="7"/>
-      <c r="C41" s="24"/>
-      <c r="D41" s="42"/>
+      <c r="C41" s="23"/>
+      <c r="D41" s="37"/>
       <c r="E41" s="17"/>
       <c r="F41" s="11"/>
-      <c r="G41" s="41"/>
+      <c r="G41" s="36"/>
       <c r="H41" s="12"/>
-      <c r="I41" s="43"/>
+      <c r="I41" s="38"/>
     </row>
     <row r="42" spans="1:9">
       <c r="A42" s="6"/>
       <c r="B42" s="7"/>
-      <c r="C42" s="24"/>
-      <c r="D42" s="42"/>
+      <c r="C42" s="23"/>
+      <c r="D42" s="37"/>
       <c r="E42" s="17"/>
       <c r="F42" s="11"/>
-      <c r="G42" s="41"/>
+      <c r="G42" s="36"/>
       <c r="H42" s="12"/>
-      <c r="I42" s="43"/>
+      <c r="I42" s="38"/>
     </row>
     <row r="43" spans="1:9">
       <c r="A43" s="6"/>
       <c r="B43" s="8"/>
       <c r="C43" s="7"/>
-      <c r="D43" s="29"/>
+      <c r="D43" s="28"/>
       <c r="E43" s="17"/>
       <c r="F43" s="12"/>
-      <c r="G43" s="41"/>
+      <c r="G43" s="36"/>
       <c r="H43" s="12"/>
       <c r="I43" s="12"/>
     </row>

--- a/Treinamento/IndexacaoFG/Arquivos/Relatório de Recusas 17.12.2025 a 24.12.2025.xlsx
+++ b/Treinamento/IndexacaoFG/Arquivos/Relatório de Recusas 17.12.2025 a 24.12.2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29609"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29622"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms.sharepoint.com/teams/BR0010-4356589/Shared Documents/BACK-OFFICE SME/Santander/2025/Relatório de Recusas/05. Maio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CFBB6B4F-67C8-41DD-BD54-C6A263512A42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{89E9FD21-36BF-49DC-B786-845A671CA07D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19530" windowHeight="9780" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19530" windowHeight="9780" firstSheet="7" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="17.12" sheetId="2" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="753" uniqueCount="248">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1092" uniqueCount="373">
   <si>
     <t>SEGURADORA</t>
   </si>
@@ -855,6 +855,408 @@
   </si>
   <si>
     <t>Chassi irregular</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ELISANGELA CRISTINA GOMES AGULHON            </t>
+  </si>
+  <si>
+    <t>Conforme consulta na central de bônus, identificamos que
+a apólice consta ativa na congênere, para que possamos prossegui
+r coma liberação do bloqueio será necessário a apresentação do e
+ndosso de cancelamento emitido, a atualização junto a Central de B
+ônus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHRISTIAN CARLOS DE SOUSA BARROS             </t>
+  </si>
+  <si>
+    <t>Falta de envio laudo cautelar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ELIONAI REZENDE DE CASTRO                    </t>
+  </si>
+  <si>
+    <t>falta de vistoria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VAMILSON SEVERINO CORREIA                    </t>
+  </si>
+  <si>
+    <t>Conforme consulta na central de bônus, identificamos que
+a apólice consta ativa na congênere, para que possamos prossegui
+r coma liberação do bloqueio será necessário a apresentação do e
+ndosso de cancelamento emitido, a atualização junto a Central de B
+ônus.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANDREA ALMEIDA DE MELO PUDO                  </t>
+  </si>
+  <si>
+    <t>Conforme consulta na central de bônus, a apólice foi renovada n
+a congênere de origem. Portanto, peço a gentileza de encaminhar a
+documentação abaixo para análise:Cópia da apólice congênere
+com vigência de 2025 a 2026;Endosso de cancelamento emitido.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VINICIUS DA CONCEICAO CLAUDINO DOS REIS      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">APARECIDA DE LOURDES XIMENES                 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">C A DA COSTA DISTRIBUIDORA DE HORTIFRUTI ME  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALEXSANDRO DE LARA GONCALVES                 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARIA VALERIA BEZERRA RIBAS                  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLAUDINEI JOSE MENDES                        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SILVA COMERCIO DE CALCADOS LTDA ME           </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CARLOS ALBERTO RABELO                        </t>
+  </si>
+  <si>
+    <t>SEGURADO NÃO CORRIGIU AS FOTOS - PRAZO INSPIRADO FOTOS: Frente e lateral ESQ. E DIR, Traseira e lateral do motorista, Painel com carro ligado, Documento do veículo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KARINE FERNANDA DE MORAIS                    </t>
+  </si>
+  <si>
+    <t>Nup- Cancelamento 22.12.2025</t>
+  </si>
+  <si>
+    <t>INTERINVEST TRADING IMPORTACAO E EXPORTACAO L</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> SEGURADO NÃO CORRIGIU AS FOTOS - PRAZO INSPIRADO FOTO: Chassi, LOCAL INCORRETO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SHEILA APARECIDA DA SILVA CHURRASQUINHO ME   </t>
+  </si>
+  <si>
+    <t>FRUSTRADO - FOTOS FORA DO PADRÃO PASSOS INCORRETOS: AMBAS FRENTES 45° KM PARCIAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARCIA DO SOCORRO SILVA DE ANDRADE           </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARILIA SOARES                               </t>
+  </si>
+  <si>
+    <t>BONACUSTICA ESQUADRIAS EM PVC E ALUMINIO LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUCAS DOS SANTOS                             </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JESSICA FABIANA LEAL OLIVEIRA                </t>
+  </si>
+  <si>
+    <t>FRUSTRADO * SEGURADO N FEZ O REENVIO DAS FOTOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EDIMARA ARAUJO DEMETRIO                      </t>
+  </si>
+  <si>
+    <t>FRUSTRADO, PRAZO PARA REENVIO EXPIRADO. FOTOS NÃO CORRIGIDAS: CHASSI (LOCAL INCORRETO)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VILMO CRISPIN DE OLIVEIRA                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAMILA RODRIGUES                             </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MIRIAN DELLATORRE DE SOUSA                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOSE CARLOS DE LIMA                          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JUNIOR FRANCISCO SILVEIRA                    </t>
+  </si>
+  <si>
+    <t>NUP CANCELAMENTO 22/12/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOSE HELIO RIGONATO DE ANDRADE               </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANTONIO NILTON DA SILVA                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">60 552 185 JULIANNI DE NAZARE DUARTE MOY ME  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SORAYA DE OLIVEIRA LIMA                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOSIVAN PEREIRA DA SILVA                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">GENESIO FERREIRA DE OLIVEIRA                 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">EDVAN SANTANA ARAUJO                         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADEMIR SARDETTE                              </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JONATHAN DA SILVA SUTIL                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RONALDO DE OLIVEIRA MARQUES                  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAMUEL GOMES DE SANTANA FILHO                </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAIO ALEXANDRE DOS SANTOS MENDES             </t>
+  </si>
+  <si>
+    <t xml:space="preserve">HJ INSTALACOES LTDA ME                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RINALDO JOSE DA SILVA                        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">LEANDRO FERNANDES COSTA                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIEGO LUIZ RODRIGUES DO VALLE                </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JAIRO ALVES FERREIRA                         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">GLAUBSON NASCIMENTO DA SILVA                 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">FRANCISCO SALES BANDEIRA LIMA                </t>
+  </si>
+  <si>
+    <t>SEGURADO NÃO CORRIGIU AS FOTOS - PRAZO INSPIRADO FOTOS: Documento da moto, Painel com a motocicleta ligada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANDREIA LOURENCO MARTINHAO                   </t>
+  </si>
+  <si>
+    <t>SEGURADO NÃO CORRIGIU AS FOTOS - PRAZO INSPIRADO FOTO: Chassi, LOCAL INCORRETO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANDREZA HAACK BIAZUS                         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARCIA SAIN DE ALMEIDA                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUIS ALBERTO MORALES GRAJALES                </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLAUDIA CRISTINA REINA DE SOUZA              </t>
+  </si>
+  <si>
+    <t>Favor enviar cópia completa d
+a apólice anterior 2025/2026.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANA CAROLINA DE SOUSA FONSECA                </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAIO HENRIQUE RANGEL SILVA                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MIRIAM CANDIDO DA COSTA MORAES               </t>
+  </si>
+  <si>
+    <t>FRUSTRADO - FOTOS FORA DO PADRÃO PASSOS INCORRETOS: AMBAS FRENTES 45°, CHASSI, HODOMETRO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLEITON HARTMANN SCHMITT                     </t>
+  </si>
+  <si>
+    <t>Recusa a pedido</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALAN AMORIM LIMA                             </t>
+  </si>
+  <si>
+    <t>Favor enviar cópia completa da apólice referente 2024/2025 (Não
+será aceito a CI, uma vez em que a CBE não retorna os dados</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAYSSA PAIVA BARBOSA                         </t>
+  </si>
+  <si>
+    <t>Veículo em duplicidade.Informamos que a pr
+oposta em questão se encontra em duplicidade com a apólice 5177202
+541312308340, para prosseguirmos com a emissão se faz necessário r
+ealizar o cancelamento de uma delas, qual podemos prosseguir e qua
+l cancelar?</t>
+  </si>
+  <si>
+    <t>CENTRO DE EDUCACAO MATERNO INFANTIL ZIGUE ZAR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUIS RICARDO ROSA                            </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARIA LUCIA DO NASCIMENTO                    </t>
+  </si>
+  <si>
+    <t>CLIENTE NÃO CORRIGIU AS FOTOS INCORRETAS - PRAZO EXPIRADO FOTO INCORRETA: Frente e lateral do passageiro, Traseira e lateral do motorista, Frente e lateral do motorista, Traseira e lateral do passageiro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PATRICIA VIEIRA LIMA                         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conforme consulta na central de bônus, identificamos que não há
+possibilidade efetuar a transferência de bônus para o(a) senhor(a
+) PATRICIA VIEIRA LIMA, pois esta não consta como condutor na apól
+ice anterior. </t>
+  </si>
+  <si>
+    <t>JONATHAN RIKER GARCIA CPF: 44322179878</t>
+  </si>
+  <si>
+    <t>NUP CANCELAMENTO 23/12/2025</t>
+  </si>
+  <si>
+    <t>3450189721</t>
+  </si>
+  <si>
+    <t>JARDELINO MARTINS DOS SANTOS CPF: 08603032769</t>
+  </si>
+  <si>
+    <t>MF REFORMAS E ESTRUTURAS EM MADEIRAS LTDA EPP</t>
+  </si>
+  <si>
+    <t>Co
+nforme CBE houve quebra de vigência de 64 dias e não houve sinistr
+o , conforme regra reduz 2 classes de bônus, assim sendo o correto
+bônus0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FELIPE DOS SANTOS CARDOSO                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">FLAVIO FELIPE BENTO DE SANT ANA              </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RENER CANDIDO DE MEDEIROS                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOEMI VIEIRA MONACO                          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">IARA CRISTINA PEREIRA DE AQUINO              </t>
+  </si>
+  <si>
+    <t>PRAZO EXPIRADO, FOTO DO CRLV NÃO APRESENTADO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TATIANA LOPES CARDOSO                        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ELINO COSME VERLI                            </t>
+  </si>
+  <si>
+    <t xml:space="preserve">FRUSTRADO * SEGURADO N FEZ O ENVIO DE TODAS AS FOTOS </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHAVES REFRIGERACAO LTDA ME                  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Faltou fotos: Frente e lateral do passageiro, Traseira e lateral do motorista, Painel com carro ligado, Chassi, Frente e lateral do motorista, Traseira e lateral do passageiro </t>
+  </si>
+  <si>
+    <t xml:space="preserve">R H REPRESENTACAO COMERCIAL LTDA ME          </t>
+  </si>
+  <si>
+    <t>CLIENTE NÃO CORRIGIU AS FOTOS INCORRETAS - PRAZO EXPIRADO FOTO INCORRETA: Frente e lateral do passageiro, Painel com carro ligado, Chassi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B N QUEIROZ SERVICOS ME                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLIENTE NÃO CORRIGIU AS FOTOS INCORRETAS - PRAZO EXPIRADO FOTO INCORRETA: Painel com carro ligado </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BEZERRA RIBEIRO COMERCIO LTDA ME             </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JORDANA SILVA SANTOS                         </t>
+  </si>
+  <si>
+    <t>CLIENTE NÃO CORRIGIU AS FOTOS INCORRETAS - PRAZO EXPIRADO FOTO INCORRETA: Frente e lateral do pass, Traseira e lateral do mot, Painel, Documento, Chassi, Traseira e lateral do passageiro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARCIO SILVEIRA LUZ                          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">OF SERVICOS DE CONSTRUCOES LTDA ME           </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MEIRE GRIGOLETO                              </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CARLOS ALBERTO MARTINS                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUCAS SILVA GOMES                            </t>
+  </si>
+  <si>
+    <t>Apólice ainda ativa, no aguardo do cancelamento.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARIANE BARBOSA FERNANDES                    </t>
+  </si>
+  <si>
+    <t>Cópia da apólice congênere
+com vigência de 2025 a 2026; Endosso de cancelamento emitido.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOSIANE MENDES SANTOS                        </t>
+  </si>
+  <si>
+    <t>Co
+nforme CBE houve quebra de vigência de 150 dias e não houve sinist
+ro , conforme regra reduz 4 classes de bônus, assim sendo o corret
+o bônus 1.</t>
+  </si>
+  <si>
+    <t>FRUSTRADO, PRAZO PARA REENVIO EXPIRADO. FOTOS NÃO CORRIGIDAS: FRENTE LAT. DIR. E ESQ. TRASEIRA LAT. DIR. (NAO ENQUADRADA)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AGRI EQUIPAMENTOS INDUSTRIAIS LTDA ME        </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> FOTOS NÃO CORRIGIDAS: Frente e lateral do passageiro e do motorista, Traseira e lateral do motorista e do passageiro (NAO ENQUADRADA), Documento do veículo (NAO APRESENTADO), Chassi (LOCAL ERRADO),, Motor (NAO ENQUADRADO)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RENAN RIBEIRO                                </t>
+  </si>
+  <si>
+    <t>FRUSTRADO, PRAZO PARA REENVIO EXPIRADO. FOTOS NÃO CORRIGIDAS: Frente e lateral do passageiro (NAO ENQUADRADA), Chassi (LOCAL INCORRETO)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MICHELLY CARLA MAILAN COSTELLINI             </t>
+  </si>
+  <si>
+    <t>FRUSTRADO, PRAZO PARA REENVIO EXPIRADO. FOTOS NÃO CORRIGIDAS: Motor e placa (NAO TIROU FOTO)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PNEUFER FERRAMENTAS E PNEUS LTDA EPP         </t>
+  </si>
+  <si>
+    <t>CLIENTE NÃO CORRIGIU AS FOTOS INCORRETAS - PRAZO EXPIRADO FOTO INCORRETA: Documento do veículo, Chassi</t>
   </si>
 </sst>
 </file>
@@ -919,7 +1321,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="18">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -1140,12 +1542,23 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="81">
+  <cellXfs count="93">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1336,11 +1749,9 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -1350,11 +1761,49 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -6221,13 +6670,13 @@
       <c r="C2" s="23">
         <v>46013</v>
       </c>
-      <c r="D2" s="76" t="s">
+      <c r="D2" s="74" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="77">
+      <c r="E2" s="75">
         <v>3450186223</v>
       </c>
-      <c r="F2" s="78" t="s">
+      <c r="F2" s="76" t="s">
         <v>188</v>
       </c>
       <c r="G2" s="31" t="s">
@@ -6248,19 +6697,19 @@
       <c r="C3" s="23">
         <v>46013</v>
       </c>
-      <c r="D3" s="79">
+      <c r="D3" s="21">
         <v>135808481</v>
       </c>
       <c r="E3" s="17">
         <v>3450177005</v>
       </c>
-      <c r="F3" s="74" t="s">
+      <c r="F3" s="11" t="s">
         <v>190</v>
       </c>
       <c r="G3" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="H3" s="71" t="s">
+      <c r="H3" s="70" t="s">
         <v>191</v>
       </c>
       <c r="I3" s="38">
@@ -6277,19 +6726,19 @@
       <c r="C4" s="23">
         <v>46013</v>
       </c>
-      <c r="D4" s="79">
+      <c r="D4" s="21">
         <v>135812315</v>
       </c>
       <c r="E4" s="17">
         <v>3450176829</v>
       </c>
-      <c r="F4" s="74" t="s">
+      <c r="F4" s="11" t="s">
         <v>192</v>
       </c>
       <c r="G4" s="31" t="s">
         <v>40</v>
       </c>
-      <c r="H4" s="71" t="s">
+      <c r="H4" s="70" t="s">
         <v>193</v>
       </c>
       <c r="I4" s="38">
@@ -6306,19 +6755,19 @@
       <c r="C5" s="23">
         <v>46013</v>
       </c>
-      <c r="D5" s="79">
+      <c r="D5" s="21">
         <v>135811117</v>
       </c>
       <c r="E5" s="17">
         <v>3450180900</v>
       </c>
-      <c r="F5" s="74" t="s">
+      <c r="F5" s="11" t="s">
         <v>194</v>
       </c>
       <c r="G5" s="31" t="s">
         <v>40</v>
       </c>
-      <c r="H5" s="72" t="s">
+      <c r="H5" s="71" t="s">
         <v>193</v>
       </c>
       <c r="I5" s="38">
@@ -6335,19 +6784,19 @@
       <c r="C6" s="23">
         <v>46013</v>
       </c>
-      <c r="D6" s="79">
+      <c r="D6" s="21">
         <v>135862092</v>
       </c>
       <c r="E6" s="17">
         <v>3450185398</v>
       </c>
-      <c r="F6" s="74" t="s">
+      <c r="F6" s="11" t="s">
         <v>195</v>
       </c>
       <c r="G6" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="H6" s="73" t="s">
+      <c r="H6" s="72" t="s">
         <v>196</v>
       </c>
       <c r="I6" s="38">
@@ -6364,19 +6813,19 @@
       <c r="C7" s="23">
         <v>46013</v>
       </c>
-      <c r="D7" s="79">
+      <c r="D7" s="21">
         <v>135866772</v>
       </c>
       <c r="E7" s="17">
         <v>3450185860</v>
       </c>
-      <c r="F7" s="74" t="s">
+      <c r="F7" s="11" t="s">
         <v>197</v>
       </c>
       <c r="G7" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="H7" s="73" t="s">
+      <c r="H7" s="72" t="s">
         <v>198</v>
       </c>
       <c r="I7" s="38">
@@ -6393,19 +6842,19 @@
       <c r="C8" s="23">
         <v>46013</v>
       </c>
-      <c r="D8" s="79">
+      <c r="D8" s="21">
         <v>135871496</v>
       </c>
       <c r="E8" s="17">
         <v>3450179425</v>
       </c>
-      <c r="F8" s="74" t="s">
+      <c r="F8" s="11" t="s">
         <v>199</v>
       </c>
       <c r="G8" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="H8" s="73" t="s">
+      <c r="H8" s="72" t="s">
         <v>43</v>
       </c>
       <c r="I8" s="38">
@@ -6422,19 +6871,19 @@
       <c r="C9" s="23">
         <v>46013</v>
       </c>
-      <c r="D9" s="79">
+      <c r="D9" s="21">
         <v>135871623</v>
       </c>
       <c r="E9" s="17">
         <v>3450179106</v>
       </c>
-      <c r="F9" s="74" t="s">
+      <c r="F9" s="11" t="s">
         <v>200</v>
       </c>
       <c r="G9" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="H9" s="73" t="s">
+      <c r="H9" s="72" t="s">
         <v>201</v>
       </c>
       <c r="I9" s="38">
@@ -6451,19 +6900,19 @@
       <c r="C10" s="23">
         <v>46013</v>
       </c>
-      <c r="D10" s="79">
+      <c r="D10" s="21">
         <v>135752257</v>
       </c>
       <c r="E10" s="17">
         <v>3450176565</v>
       </c>
-      <c r="F10" s="74" t="s">
+      <c r="F10" s="11" t="s">
         <v>202</v>
       </c>
       <c r="G10" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="H10" s="80" t="s">
+      <c r="H10" s="72" t="s">
         <v>63</v>
       </c>
       <c r="I10" s="38">
@@ -6480,19 +6929,19 @@
       <c r="C11" s="23">
         <v>46013</v>
       </c>
-      <c r="D11" s="79">
+      <c r="D11" s="21">
         <v>135868110</v>
       </c>
       <c r="E11" s="17">
         <v>3450185970</v>
       </c>
-      <c r="F11" s="74" t="s">
+      <c r="F11" s="11" t="s">
         <v>203</v>
       </c>
       <c r="G11" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="H11" s="73" t="s">
+      <c r="H11" s="72" t="s">
         <v>63</v>
       </c>
       <c r="I11" s="38">
@@ -6509,19 +6958,19 @@
       <c r="C12" s="23">
         <v>46013</v>
       </c>
-      <c r="D12" s="79">
+      <c r="D12" s="21">
         <v>135861776</v>
       </c>
       <c r="E12" s="17">
         <v>3450185354</v>
       </c>
-      <c r="F12" s="74" t="s">
+      <c r="F12" s="11" t="s">
         <v>204</v>
       </c>
       <c r="G12" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="H12" s="73" t="s">
+      <c r="H12" s="72" t="s">
         <v>205</v>
       </c>
       <c r="I12" s="38">
@@ -6538,19 +6987,19 @@
       <c r="C13" s="23">
         <v>46013</v>
       </c>
-      <c r="D13" s="79">
+      <c r="D13" s="21">
         <v>135888226</v>
       </c>
       <c r="E13" s="17">
         <v>3450187455</v>
       </c>
-      <c r="F13" s="74" t="s">
+      <c r="F13" s="11" t="s">
         <v>206</v>
       </c>
       <c r="G13" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="H13" s="73" t="s">
+      <c r="H13" s="72" t="s">
         <v>207</v>
       </c>
       <c r="I13" s="38">
@@ -6567,19 +7016,19 @@
       <c r="C14" s="23">
         <v>46013</v>
       </c>
-      <c r="D14" s="79">
+      <c r="D14" s="21">
         <v>135875849</v>
       </c>
       <c r="E14" s="17">
         <v>3450186388</v>
       </c>
-      <c r="F14" s="74" t="s">
+      <c r="F14" s="11" t="s">
         <v>208</v>
       </c>
       <c r="G14" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="H14" s="73" t="s">
+      <c r="H14" s="72" t="s">
         <v>191</v>
       </c>
       <c r="I14" s="38">
@@ -6596,19 +7045,19 @@
       <c r="C15" s="23">
         <v>46013</v>
       </c>
-      <c r="D15" s="79">
+      <c r="D15" s="21">
         <v>135886383</v>
       </c>
       <c r="E15" s="17">
         <v>3450187257</v>
       </c>
-      <c r="F15" s="74" t="s">
+      <c r="F15" s="11" t="s">
         <v>209</v>
       </c>
       <c r="G15" s="32" t="s">
         <v>37</v>
       </c>
-      <c r="H15" s="73" t="s">
+      <c r="H15" s="72" t="s">
         <v>38</v>
       </c>
       <c r="I15" s="38">
@@ -6625,19 +7074,19 @@
       <c r="C16" s="23">
         <v>46013</v>
       </c>
-      <c r="D16" s="79">
+      <c r="D16" s="21">
         <v>135890986</v>
       </c>
       <c r="E16" s="17">
         <v>3450187708</v>
       </c>
-      <c r="F16" s="74" t="s">
+      <c r="F16" s="11" t="s">
         <v>210</v>
       </c>
       <c r="G16" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="H16" s="80" t="s">
+      <c r="H16" s="72" t="s">
         <v>211</v>
       </c>
       <c r="I16" s="38">
@@ -6654,19 +7103,19 @@
       <c r="C17" s="23">
         <v>46013</v>
       </c>
-      <c r="D17" s="79">
+      <c r="D17" s="21">
         <v>135894834</v>
       </c>
       <c r="E17" s="17">
         <v>3450183495</v>
       </c>
-      <c r="F17" s="74" t="s">
+      <c r="F17" s="11" t="s">
         <v>212</v>
       </c>
       <c r="G17" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="H17" s="73" t="s">
+      <c r="H17" s="72" t="s">
         <v>213</v>
       </c>
       <c r="I17" s="38">
@@ -6683,19 +7132,19 @@
       <c r="C18" s="23">
         <v>46013</v>
       </c>
-      <c r="D18" s="79">
+      <c r="D18" s="21">
         <v>135894378</v>
       </c>
       <c r="E18" s="17">
         <v>3450181493</v>
       </c>
-      <c r="F18" s="74" t="s">
+      <c r="F18" s="11" t="s">
         <v>214</v>
       </c>
       <c r="G18" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="H18" s="73" t="s">
+      <c r="H18" s="72" t="s">
         <v>215</v>
       </c>
       <c r="I18" s="38">
@@ -6712,19 +7161,19 @@
       <c r="C19" s="23">
         <v>46013</v>
       </c>
-      <c r="D19" s="79">
+      <c r="D19" s="21">
         <v>135911447</v>
       </c>
       <c r="E19" s="17">
         <v>3450189370</v>
       </c>
-      <c r="F19" s="74" t="s">
+      <c r="F19" s="11" t="s">
         <v>216</v>
       </c>
       <c r="G19" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="H19" s="73" t="s">
+      <c r="H19" s="72" t="s">
         <v>191</v>
       </c>
       <c r="I19" s="38">
@@ -6741,19 +7190,19 @@
       <c r="C20" s="23">
         <v>46013</v>
       </c>
-      <c r="D20" s="79">
+      <c r="D20" s="21">
         <v>135881322</v>
       </c>
       <c r="E20" s="17">
         <v>3450186850</v>
       </c>
-      <c r="F20" s="74" t="s">
+      <c r="F20" s="11" t="s">
         <v>217</v>
       </c>
       <c r="G20" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="H20" s="73" t="s">
+      <c r="H20" s="72" t="s">
         <v>218</v>
       </c>
       <c r="I20" s="38">
@@ -6770,19 +7219,19 @@
       <c r="C21" s="23">
         <v>46013</v>
       </c>
-      <c r="D21" s="79">
+      <c r="D21" s="21">
         <v>135896317</v>
       </c>
       <c r="E21" s="17">
         <v>3450188148</v>
       </c>
-      <c r="F21" s="74" t="s">
+      <c r="F21" s="11" t="s">
         <v>219</v>
       </c>
       <c r="G21" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="H21" s="73" t="s">
+      <c r="H21" s="72" t="s">
         <v>191</v>
       </c>
       <c r="I21" s="38">
@@ -6799,19 +7248,19 @@
       <c r="C22" s="23">
         <v>46013</v>
       </c>
-      <c r="D22" s="79">
+      <c r="D22" s="21">
         <v>135912171</v>
       </c>
       <c r="E22" s="17">
         <v>3450189446</v>
       </c>
-      <c r="F22" s="74" t="s">
+      <c r="F22" s="11" t="s">
         <v>220</v>
       </c>
       <c r="G22" s="32" t="s">
         <v>37</v>
       </c>
-      <c r="H22" s="73" t="s">
+      <c r="H22" s="72" t="s">
         <v>38</v>
       </c>
       <c r="I22" s="38">
@@ -6828,19 +7277,19 @@
       <c r="C23" s="23">
         <v>46013</v>
       </c>
-      <c r="D23" s="79">
+      <c r="D23" s="21">
         <v>135924259</v>
       </c>
       <c r="E23" s="17">
         <v>3450190205</v>
       </c>
-      <c r="F23" s="74" t="s">
+      <c r="F23" s="11" t="s">
         <v>221</v>
       </c>
       <c r="G23" s="32" t="s">
         <v>37</v>
       </c>
-      <c r="H23" s="73" t="s">
+      <c r="H23" s="72" t="s">
         <v>38</v>
       </c>
       <c r="I23" s="38">
@@ -6857,19 +7306,19 @@
       <c r="C24" s="23">
         <v>46013</v>
       </c>
-      <c r="D24" s="79">
+      <c r="D24" s="21">
         <v>135894649</v>
       </c>
       <c r="E24" s="17">
         <v>3450180184</v>
       </c>
-      <c r="F24" s="74" t="s">
+      <c r="F24" s="11" t="s">
         <v>222</v>
       </c>
       <c r="G24" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="H24" s="73" t="s">
+      <c r="H24" s="72" t="s">
         <v>223</v>
       </c>
       <c r="I24" s="38">
@@ -6886,19 +7335,19 @@
       <c r="C25" s="23">
         <v>46013</v>
       </c>
-      <c r="D25" s="79">
+      <c r="D25" s="21">
         <v>135931820</v>
       </c>
       <c r="E25" s="17">
         <v>3450191063</v>
       </c>
-      <c r="F25" s="74" t="s">
+      <c r="F25" s="11" t="s">
         <v>224</v>
       </c>
       <c r="G25" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="H25" s="73" t="s">
+      <c r="H25" s="72" t="s">
         <v>191</v>
       </c>
       <c r="I25" s="38">
@@ -6915,19 +7364,19 @@
       <c r="C26" s="23">
         <v>46013</v>
       </c>
-      <c r="D26" s="79">
+      <c r="D26" s="21">
         <v>135925147</v>
       </c>
       <c r="E26" s="17">
         <v>3450190425</v>
       </c>
-      <c r="F26" s="74" t="s">
+      <c r="F26" s="11" t="s">
         <v>225</v>
       </c>
       <c r="G26" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="H26" s="73" t="s">
+      <c r="H26" s="72" t="s">
         <v>191</v>
       </c>
       <c r="I26" s="38">
@@ -6944,19 +7393,19 @@
       <c r="C27" s="23">
         <v>46013</v>
       </c>
-      <c r="D27" s="79">
+      <c r="D27" s="21">
         <v>135873601</v>
       </c>
       <c r="E27" s="17">
         <v>3450182142</v>
       </c>
-      <c r="F27" s="74" t="s">
+      <c r="F27" s="11" t="s">
         <v>226</v>
       </c>
       <c r="G27" s="35" t="s">
         <v>21</v>
       </c>
-      <c r="H27" s="73" t="s">
+      <c r="H27" s="72" t="s">
         <v>227</v>
       </c>
       <c r="I27" s="38">
@@ -6973,19 +7422,19 @@
       <c r="C28" s="23">
         <v>46013</v>
       </c>
-      <c r="D28" s="79">
+      <c r="D28" s="21">
         <v>135926970</v>
       </c>
       <c r="E28" s="17">
         <v>3450190634</v>
       </c>
-      <c r="F28" s="74" t="s">
+      <c r="F28" s="11" t="s">
         <v>228</v>
       </c>
       <c r="G28" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="H28" s="71" t="s">
+      <c r="H28" s="70" t="s">
         <v>191</v>
       </c>
       <c r="I28" s="38">
@@ -7002,19 +7451,19 @@
       <c r="C29" s="23">
         <v>46013</v>
       </c>
-      <c r="D29" s="79">
+      <c r="D29" s="21">
         <v>135942800</v>
       </c>
       <c r="E29" s="17">
         <v>3450191833</v>
       </c>
-      <c r="F29" s="74" t="s">
+      <c r="F29" s="11" t="s">
         <v>229</v>
       </c>
       <c r="G29" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="H29" s="71" t="s">
+      <c r="H29" s="70" t="s">
         <v>191</v>
       </c>
       <c r="I29" s="38">
@@ -7031,13 +7480,13 @@
       <c r="C30" s="23">
         <v>46013</v>
       </c>
-      <c r="D30" s="79">
+      <c r="D30" s="21">
         <v>135750474</v>
       </c>
       <c r="E30" s="17">
         <v>3450176400</v>
       </c>
-      <c r="F30" s="74" t="s">
+      <c r="F30" s="11" t="s">
         <v>230</v>
       </c>
       <c r="G30" s="35" t="s">
@@ -7060,19 +7509,19 @@
       <c r="C31" s="23">
         <v>46013</v>
       </c>
-      <c r="D31" s="79">
+      <c r="D31" s="21">
         <v>135762373</v>
       </c>
       <c r="E31" s="17">
         <v>3450177082</v>
       </c>
-      <c r="F31" s="74" t="s">
+      <c r="F31" s="11" t="s">
         <v>231</v>
       </c>
       <c r="G31" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="H31" s="71" t="s">
+      <c r="H31" s="70" t="s">
         <v>191</v>
       </c>
       <c r="I31" s="38">
@@ -7089,19 +7538,19 @@
       <c r="C32" s="23">
         <v>46013</v>
       </c>
-      <c r="D32" s="79">
+      <c r="D32" s="21">
         <v>135859177</v>
       </c>
       <c r="E32" s="17">
         <v>3450174497</v>
       </c>
-      <c r="F32" s="74" t="s">
+      <c r="F32" s="11" t="s">
         <v>232</v>
       </c>
       <c r="G32" s="35" t="s">
         <v>21</v>
       </c>
-      <c r="H32" s="71" t="s">
+      <c r="H32" s="70" t="s">
         <v>233</v>
       </c>
       <c r="I32" s="38">
@@ -7118,13 +7567,13 @@
       <c r="C33" s="23">
         <v>46013</v>
       </c>
-      <c r="D33" s="79">
+      <c r="D33" s="21">
         <v>135777470</v>
       </c>
       <c r="E33" s="17">
         <v>3450178402</v>
       </c>
-      <c r="F33" s="74" t="s">
+      <c r="F33" s="11" t="s">
         <v>234</v>
       </c>
       <c r="G33" s="35" t="s">
@@ -7147,19 +7596,19 @@
       <c r="C34" s="23">
         <v>46013</v>
       </c>
-      <c r="D34" s="79">
+      <c r="D34" s="21">
         <v>135787457</v>
       </c>
       <c r="E34" s="17">
         <v>3450178732</v>
       </c>
-      <c r="F34" s="74" t="s">
+      <c r="F34" s="11" t="s">
         <v>236</v>
       </c>
       <c r="G34" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="H34" s="71" t="s">
+      <c r="H34" s="70" t="s">
         <v>193</v>
       </c>
       <c r="I34" s="38">
@@ -7176,19 +7625,19 @@
       <c r="C35" s="23">
         <v>46013</v>
       </c>
-      <c r="D35" s="79">
+      <c r="D35" s="21">
         <v>135790032</v>
       </c>
       <c r="E35" s="17">
         <v>3450174783</v>
       </c>
-      <c r="F35" s="74" t="s">
+      <c r="F35" s="11" t="s">
         <v>237</v>
       </c>
       <c r="G35" s="31" t="s">
         <v>40</v>
       </c>
-      <c r="H35" s="71" t="s">
+      <c r="H35" s="70" t="s">
         <v>193</v>
       </c>
       <c r="I35" s="38">
@@ -7205,19 +7654,19 @@
       <c r="C36" s="23">
         <v>46013</v>
       </c>
-      <c r="D36" s="79">
+      <c r="D36" s="21">
         <v>135790996</v>
       </c>
       <c r="E36" s="17">
         <v>3450179117</v>
       </c>
-      <c r="F36" s="74" t="s">
+      <c r="F36" s="11" t="s">
         <v>238</v>
       </c>
       <c r="G36" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="H36" s="71" t="s">
+      <c r="H36" s="70" t="s">
         <v>193</v>
       </c>
       <c r="I36" s="38">
@@ -7234,16 +7683,16 @@
       <c r="C37" s="23">
         <v>46013</v>
       </c>
-      <c r="D37" s="79">
+      <c r="D37" s="21">
         <v>135792794</v>
       </c>
       <c r="E37" s="17">
         <v>3450179304</v>
       </c>
-      <c r="F37" s="74" t="s">
+      <c r="F37" s="11" t="s">
         <v>239</v>
       </c>
-      <c r="G37" s="75" t="s">
+      <c r="G37" s="73" t="s">
         <v>40</v>
       </c>
       <c r="H37" s="42" t="s">
@@ -7263,16 +7712,16 @@
       <c r="C38" s="23">
         <v>46013</v>
       </c>
-      <c r="D38" s="79">
+      <c r="D38" s="21">
         <v>135798684</v>
       </c>
       <c r="E38" s="17">
         <v>3450179821</v>
       </c>
-      <c r="F38" s="74" t="s">
+      <c r="F38" s="11" t="s">
         <v>240</v>
       </c>
-      <c r="G38" s="75" t="s">
+      <c r="G38" s="73" t="s">
         <v>40</v>
       </c>
       <c r="H38" s="42" t="s">
@@ -7292,16 +7741,16 @@
       <c r="C39" s="23">
         <v>46013</v>
       </c>
-      <c r="D39" s="79">
+      <c r="D39" s="21">
         <v>135800468</v>
       </c>
       <c r="E39" s="17">
         <v>3450179997</v>
       </c>
-      <c r="F39" s="74" t="s">
+      <c r="F39" s="11" t="s">
         <v>241</v>
       </c>
-      <c r="G39" s="75" t="s">
+      <c r="G39" s="73" t="s">
         <v>40</v>
       </c>
       <c r="H39" s="42" t="s">
@@ -7321,16 +7770,16 @@
       <c r="C40" s="23">
         <v>46013</v>
       </c>
-      <c r="D40" s="79">
+      <c r="D40" s="21">
         <v>135800568</v>
       </c>
       <c r="E40" s="17">
         <v>3450180008</v>
       </c>
-      <c r="F40" s="74" t="s">
+      <c r="F40" s="11" t="s">
         <v>170</v>
       </c>
-      <c r="G40" s="75" t="s">
+      <c r="G40" s="73" t="s">
         <v>40</v>
       </c>
       <c r="H40" s="42" t="s">
@@ -7350,16 +7799,16 @@
       <c r="C41" s="23">
         <v>46013</v>
       </c>
-      <c r="D41" s="79">
+      <c r="D41" s="21">
         <v>135806463</v>
       </c>
       <c r="E41" s="17">
         <v>3450180350</v>
       </c>
-      <c r="F41" s="74" t="s">
+      <c r="F41" s="11" t="s">
         <v>242</v>
       </c>
-      <c r="G41" s="75" t="s">
+      <c r="G41" s="73" t="s">
         <v>40</v>
       </c>
       <c r="H41" s="42" t="s">
@@ -7379,16 +7828,16 @@
       <c r="C42" s="23">
         <v>46013</v>
       </c>
-      <c r="D42" s="79">
+      <c r="D42" s="21">
         <v>135806730</v>
       </c>
       <c r="E42" s="17">
         <v>3450180404</v>
       </c>
-      <c r="F42" s="74" t="s">
+      <c r="F42" s="11" t="s">
         <v>243</v>
       </c>
-      <c r="G42" s="75" t="s">
+      <c r="G42" s="73" t="s">
         <v>40</v>
       </c>
       <c r="H42" s="42" t="s">
@@ -7408,13 +7857,13 @@
       <c r="C43" s="23">
         <v>46013</v>
       </c>
-      <c r="D43" s="79">
+      <c r="D43" s="21">
         <v>135807335</v>
       </c>
       <c r="E43" s="17">
         <v>3450180481</v>
       </c>
-      <c r="F43" s="74" t="s">
+      <c r="F43" s="11" t="s">
         <v>243</v>
       </c>
       <c r="G43" s="18" t="s">
@@ -7437,13 +7886,13 @@
       <c r="C44" s="23">
         <v>46013</v>
       </c>
-      <c r="D44" s="79">
+      <c r="D44" s="21">
         <v>135809115</v>
       </c>
       <c r="E44" s="17">
         <v>3450180657</v>
       </c>
-      <c r="F44" s="74" t="s">
+      <c r="F44" s="11" t="s">
         <v>244</v>
       </c>
       <c r="G44" s="18" t="s">
@@ -7466,13 +7915,13 @@
       <c r="C45" s="23">
         <v>46013</v>
       </c>
-      <c r="D45" s="79">
+      <c r="D45" s="21">
         <v>135809266</v>
       </c>
       <c r="E45" s="17">
         <v>3450180679</v>
       </c>
-      <c r="F45" s="74" t="s">
+      <c r="F45" s="11" t="s">
         <v>245</v>
       </c>
       <c r="G45" s="18" t="s">
@@ -7516,7 +7965,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6E6B8A0-66E5-406F-8D37-9E8A2778B9CB}">
-  <dimension ref="A1:I42"/>
+  <dimension ref="A1:I66"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
@@ -7560,513 +8009,1878 @@
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" s="7">
+      <c r="A2" s="81" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="82">
         <v>46006</v>
       </c>
-      <c r="C2" s="23">
+      <c r="C2" s="83">
         <v>46014</v>
       </c>
-      <c r="D2" s="17" t="s">
+      <c r="D2" s="75" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="17">
+      <c r="E2" s="75">
         <v>3450184859</v>
       </c>
-      <c r="F2" s="11" t="s">
+      <c r="F2" s="76" t="s">
         <v>246</v>
       </c>
-      <c r="G2" s="36" t="s">
+      <c r="G2" s="84" t="s">
         <v>60</v>
       </c>
-      <c r="H2" s="39" t="s">
+      <c r="H2" s="85" t="s">
         <v>247</v>
       </c>
-      <c r="I2" s="38"/>
+      <c r="I2" s="43"/>
     </row>
     <row r="3" spans="1:9">
-      <c r="A3" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="7"/>
-      <c r="C3" s="23"/>
-      <c r="D3" s="37"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="11"/>
-      <c r="G3" s="36"/>
-      <c r="H3" s="39"/>
-      <c r="I3" s="38"/>
+      <c r="A3" s="36" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="38">
+        <v>46031</v>
+      </c>
+      <c r="C3" s="38">
+        <v>46014</v>
+      </c>
+      <c r="D3" s="86">
+        <v>135800368</v>
+      </c>
+      <c r="E3" s="17">
+        <v>3450179920</v>
+      </c>
+      <c r="F3" s="87" t="s">
+        <v>248</v>
+      </c>
+      <c r="G3" s="36" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" s="17" t="s">
+        <v>249</v>
+      </c>
+      <c r="I3" s="38">
+        <v>46007</v>
+      </c>
     </row>
     <row r="4" spans="1:9">
-      <c r="A4" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="7"/>
-      <c r="C4" s="23"/>
-      <c r="D4" s="37"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="11"/>
-      <c r="G4" s="36"/>
-      <c r="H4" s="39"/>
-      <c r="I4" s="38"/>
+      <c r="A4" s="36" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="38">
+        <v>46002</v>
+      </c>
+      <c r="C4" s="38">
+        <v>46014</v>
+      </c>
+      <c r="D4" s="86">
+        <v>135804374</v>
+      </c>
+      <c r="E4" s="17">
+        <v>3450180162</v>
+      </c>
+      <c r="F4" s="87" t="s">
+        <v>250</v>
+      </c>
+      <c r="G4" s="36" t="s">
+        <v>60</v>
+      </c>
+      <c r="H4" t="s">
+        <v>251</v>
+      </c>
+      <c r="I4" s="38">
+        <v>46008</v>
+      </c>
     </row>
     <row r="5" spans="1:9">
-      <c r="A5" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="7"/>
-      <c r="C5" s="23"/>
-      <c r="D5" s="37"/>
-      <c r="E5" s="17"/>
-      <c r="F5" s="11"/>
-      <c r="G5" s="36"/>
-      <c r="H5" s="39"/>
-      <c r="I5" s="38"/>
+      <c r="A5" s="36" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="38">
+        <v>46002</v>
+      </c>
+      <c r="C5" s="38">
+        <v>46014</v>
+      </c>
+      <c r="D5" s="86">
+        <v>135822352</v>
+      </c>
+      <c r="E5" s="17">
+        <v>3450182087</v>
+      </c>
+      <c r="F5" s="87" t="s">
+        <v>252</v>
+      </c>
+      <c r="G5" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="H5" s="92" t="s">
+        <v>253</v>
+      </c>
+      <c r="I5" s="38">
+        <v>46002</v>
+      </c>
     </row>
     <row r="6" spans="1:9">
-      <c r="A6" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" s="7"/>
-      <c r="C6" s="23"/>
-      <c r="D6" s="37"/>
-      <c r="E6" s="17"/>
-      <c r="F6" s="11"/>
-      <c r="G6" s="36"/>
-      <c r="H6" s="40"/>
-      <c r="I6" s="38"/>
+      <c r="A6" s="36" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="38">
+        <v>46002</v>
+      </c>
+      <c r="C6" s="38">
+        <v>46014</v>
+      </c>
+      <c r="D6" s="86">
+        <v>135804209</v>
+      </c>
+      <c r="E6" s="17">
+        <v>3450180151</v>
+      </c>
+      <c r="F6" s="87" t="s">
+        <v>254</v>
+      </c>
+      <c r="G6" s="36" t="s">
+        <v>15</v>
+      </c>
+      <c r="H6" s="21" t="s">
+        <v>255</v>
+      </c>
+      <c r="I6" s="38">
+        <v>46007</v>
+      </c>
     </row>
     <row r="7" spans="1:9">
-      <c r="A7" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" s="7"/>
-      <c r="C7" s="23"/>
-      <c r="D7" s="37"/>
-      <c r="E7" s="17"/>
-      <c r="F7" s="11"/>
-      <c r="G7" s="36"/>
-      <c r="H7" s="40"/>
-      <c r="I7" s="38"/>
+      <c r="A7" s="36" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="38">
+        <v>46003</v>
+      </c>
+      <c r="C7" s="38">
+        <v>46014</v>
+      </c>
+      <c r="D7" s="86">
+        <v>135822468</v>
+      </c>
+      <c r="E7" s="17">
+        <v>3450182109</v>
+      </c>
+      <c r="F7" s="87" t="s">
+        <v>256</v>
+      </c>
+      <c r="G7" s="36" t="s">
+        <v>15</v>
+      </c>
+      <c r="H7" s="17" t="s">
+        <v>257</v>
+      </c>
+      <c r="I7" s="38">
+        <v>46008</v>
+      </c>
     </row>
     <row r="8" spans="1:9">
-      <c r="A8" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="23"/>
-      <c r="D8" s="37"/>
-      <c r="E8" s="17"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="36"/>
-      <c r="H8" s="39"/>
-      <c r="I8" s="38"/>
+      <c r="A8" s="36" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="38">
+        <v>46002</v>
+      </c>
+      <c r="C8" s="38">
+        <v>46014</v>
+      </c>
+      <c r="D8" s="86">
+        <v>135815199</v>
+      </c>
+      <c r="E8" s="17">
+        <v>3450181230</v>
+      </c>
+      <c r="F8" s="87" t="s">
+        <v>258</v>
+      </c>
+      <c r="G8" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="H8" s="92" t="s">
+        <v>253</v>
+      </c>
+      <c r="I8" s="38">
+        <v>46002</v>
+      </c>
     </row>
     <row r="9" spans="1:9">
-      <c r="A9" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9" s="7"/>
-      <c r="C9" s="23"/>
-      <c r="D9" s="37"/>
-      <c r="E9" s="17"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="36"/>
-      <c r="H9" s="39"/>
-      <c r="I9" s="38"/>
+      <c r="A9" s="36" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="38">
+        <v>46002</v>
+      </c>
+      <c r="C9" s="38">
+        <v>46014</v>
+      </c>
+      <c r="D9" s="86">
+        <v>135817939</v>
+      </c>
+      <c r="E9" s="17">
+        <v>3450181526</v>
+      </c>
+      <c r="F9" s="87" t="s">
+        <v>259</v>
+      </c>
+      <c r="G9" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="H9" s="92" t="s">
+        <v>253</v>
+      </c>
+      <c r="I9" s="38">
+        <v>46002</v>
+      </c>
     </row>
     <row r="10" spans="1:9">
-      <c r="A10" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B10" s="7"/>
-      <c r="C10" s="23"/>
-      <c r="D10" s="37"/>
-      <c r="E10" s="17"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="36"/>
-      <c r="H10" s="39"/>
-      <c r="I10" s="38"/>
+      <c r="A10" s="36" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="38">
+        <v>46003</v>
+      </c>
+      <c r="C10" s="38">
+        <v>46014</v>
+      </c>
+      <c r="D10" s="86">
+        <v>135836190</v>
+      </c>
+      <c r="E10" s="17">
+        <v>3450183187</v>
+      </c>
+      <c r="F10" s="87" t="s">
+        <v>260</v>
+      </c>
+      <c r="G10" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="H10" s="92" t="s">
+        <v>253</v>
+      </c>
+      <c r="I10" s="38">
+        <v>46003</v>
+      </c>
     </row>
     <row r="11" spans="1:9">
-      <c r="A11" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11" s="7"/>
-      <c r="C11" s="23"/>
-      <c r="D11" s="37"/>
-      <c r="E11" s="17"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="36"/>
-      <c r="H11" s="39"/>
-      <c r="I11" s="38"/>
+      <c r="A11" s="36" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="38">
+        <v>46003</v>
+      </c>
+      <c r="C11" s="38">
+        <v>46014</v>
+      </c>
+      <c r="D11" s="86">
+        <v>135844482</v>
+      </c>
+      <c r="E11" s="17">
+        <v>3450184166</v>
+      </c>
+      <c r="F11" s="87" t="s">
+        <v>261</v>
+      </c>
+      <c r="G11" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="H11" s="92" t="s">
+        <v>253</v>
+      </c>
+      <c r="I11" s="38">
+        <v>46003</v>
+      </c>
     </row>
     <row r="12" spans="1:9">
-      <c r="A12" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B12" s="7"/>
-      <c r="C12" s="23"/>
-      <c r="D12" s="37"/>
-      <c r="E12" s="17"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="36"/>
-      <c r="H12" s="39"/>
-      <c r="I12" s="38"/>
+      <c r="A12" s="36" t="s">
+        <v>9</v>
+      </c>
+      <c r="B12" s="38">
+        <v>46000</v>
+      </c>
+      <c r="C12" s="38">
+        <v>46014</v>
+      </c>
+      <c r="D12" s="86">
+        <v>135828853</v>
+      </c>
+      <c r="E12" s="17">
+        <v>3450178314</v>
+      </c>
+      <c r="F12" s="87" t="s">
+        <v>262</v>
+      </c>
+      <c r="G12" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="H12" s="92" t="s">
+        <v>253</v>
+      </c>
+      <c r="I12" s="38">
+        <v>46000</v>
+      </c>
     </row>
     <row r="13" spans="1:9">
-      <c r="A13" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B13" s="7"/>
-      <c r="C13" s="23"/>
-      <c r="D13" s="37"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="11"/>
-      <c r="G13" s="36"/>
-      <c r="H13" s="39"/>
-      <c r="I13" s="38"/>
+      <c r="A13" s="36" t="s">
+        <v>9</v>
+      </c>
+      <c r="B13" s="38">
+        <v>46003</v>
+      </c>
+      <c r="C13" s="38">
+        <v>46014</v>
+      </c>
+      <c r="D13" s="86">
+        <v>135843502</v>
+      </c>
+      <c r="E13" s="17">
+        <v>3450184089</v>
+      </c>
+      <c r="F13" s="87" t="s">
+        <v>263</v>
+      </c>
+      <c r="G13" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="H13" s="92" t="s">
+        <v>253</v>
+      </c>
+      <c r="I13" s="38">
+        <v>46003</v>
+      </c>
     </row>
     <row r="14" spans="1:9">
-      <c r="A14" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B14" s="7"/>
-      <c r="C14" s="23"/>
-      <c r="D14" s="37"/>
-      <c r="E14" s="17"/>
-      <c r="F14" s="11"/>
-      <c r="G14" s="36"/>
-      <c r="H14" s="39"/>
-      <c r="I14" s="38"/>
+      <c r="A14" s="36" t="s">
+        <v>9</v>
+      </c>
+      <c r="B14" s="38">
+        <v>46003</v>
+      </c>
+      <c r="C14" s="38">
+        <v>46014</v>
+      </c>
+      <c r="D14" s="86">
+        <v>135845344</v>
+      </c>
+      <c r="E14" s="17">
+        <v>3450184309</v>
+      </c>
+      <c r="F14" s="87" t="s">
+        <v>264</v>
+      </c>
+      <c r="G14" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="H14" s="92" t="s">
+        <v>253</v>
+      </c>
+      <c r="I14" s="38">
+        <v>46003</v>
+      </c>
     </row>
     <row r="15" spans="1:9">
-      <c r="A15" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B15" s="7"/>
-      <c r="C15" s="23"/>
-      <c r="D15" s="37"/>
-      <c r="E15" s="17"/>
-      <c r="F15" s="11"/>
-      <c r="G15" s="36"/>
-      <c r="H15" s="39"/>
-      <c r="I15" s="38"/>
+      <c r="A15" s="79" t="s">
+        <v>9</v>
+      </c>
+      <c r="B15" s="38">
+        <v>46006</v>
+      </c>
+      <c r="C15" s="38">
+        <v>46014</v>
+      </c>
+      <c r="D15" s="86">
+        <v>135862426</v>
+      </c>
+      <c r="E15" s="17">
+        <v>3450185431</v>
+      </c>
+      <c r="F15" s="87" t="s">
+        <v>265</v>
+      </c>
+      <c r="G15" s="36" t="s">
+        <v>21</v>
+      </c>
+      <c r="H15" s="92" t="s">
+        <v>266</v>
+      </c>
+      <c r="I15" s="38">
+        <v>46006</v>
+      </c>
     </row>
     <row r="16" spans="1:9">
-      <c r="A16" s="25" t="s">
-        <v>9</v>
-      </c>
-      <c r="B16" s="7"/>
-      <c r="C16" s="23"/>
-      <c r="D16" s="37"/>
-      <c r="E16" s="17"/>
-      <c r="F16" s="11"/>
-      <c r="G16" s="36"/>
-      <c r="H16" s="39"/>
-      <c r="I16" s="38"/>
+      <c r="A16" s="36" t="s">
+        <v>9</v>
+      </c>
+      <c r="B16" s="38">
+        <v>46007</v>
+      </c>
+      <c r="C16" s="38">
+        <v>46014</v>
+      </c>
+      <c r="D16" s="86">
+        <v>135894268</v>
+      </c>
+      <c r="E16" s="17">
+        <v>3450188093</v>
+      </c>
+      <c r="F16" s="87" t="s">
+        <v>267</v>
+      </c>
+      <c r="G16" s="36" t="s">
+        <v>11</v>
+      </c>
+      <c r="H16" s="92" t="s">
+        <v>268</v>
+      </c>
+      <c r="I16" s="38">
+        <v>46013</v>
+      </c>
     </row>
     <row r="17" spans="1:9">
-      <c r="A17" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B17" s="7"/>
-      <c r="C17" s="23"/>
-      <c r="D17" s="37"/>
-      <c r="E17" s="17"/>
-      <c r="F17" s="11"/>
-      <c r="G17" s="36"/>
-      <c r="H17" s="39"/>
-      <c r="I17" s="38"/>
+      <c r="A17" s="36" t="s">
+        <v>9</v>
+      </c>
+      <c r="B17" s="38">
+        <v>46008</v>
+      </c>
+      <c r="C17" s="38">
+        <v>46014</v>
+      </c>
+      <c r="D17" s="86">
+        <v>135899287</v>
+      </c>
+      <c r="E17" s="17">
+        <v>3450188291</v>
+      </c>
+      <c r="F17" s="87" t="s">
+        <v>269</v>
+      </c>
+      <c r="G17" s="36" t="s">
+        <v>21</v>
+      </c>
+      <c r="H17" s="92" t="s">
+        <v>270</v>
+      </c>
+      <c r="I17" s="38">
+        <v>46008</v>
+      </c>
     </row>
     <row r="18" spans="1:9">
-      <c r="A18" s="6"/>
-      <c r="B18" s="7"/>
-      <c r="C18" s="23"/>
-      <c r="D18" s="37"/>
-      <c r="E18" s="17"/>
-      <c r="F18" s="11"/>
-      <c r="G18" s="36"/>
-      <c r="H18" s="39"/>
-      <c r="I18" s="38"/>
+      <c r="A18" s="36" t="s">
+        <v>9</v>
+      </c>
+      <c r="B18" s="38">
+        <v>46008</v>
+      </c>
+      <c r="C18" s="38">
+        <v>46014</v>
+      </c>
+      <c r="D18" s="86">
+        <v>135908714</v>
+      </c>
+      <c r="E18" s="17">
+        <v>3450189182</v>
+      </c>
+      <c r="F18" s="87" t="s">
+        <v>271</v>
+      </c>
+      <c r="G18" s="36" t="s">
+        <v>21</v>
+      </c>
+      <c r="H18" s="92" t="s">
+        <v>272</v>
+      </c>
+      <c r="I18" s="38">
+        <v>46008</v>
+      </c>
     </row>
     <row r="19" spans="1:9">
-      <c r="A19" s="6"/>
-      <c r="B19" s="7"/>
-      <c r="C19" s="23"/>
-      <c r="D19" s="37"/>
-      <c r="E19" s="17"/>
-      <c r="F19" s="11"/>
-      <c r="G19" s="36"/>
-      <c r="H19" s="39"/>
-      <c r="I19" s="38"/>
+      <c r="A19" s="36" t="s">
+        <v>9</v>
+      </c>
+      <c r="B19" s="38">
+        <v>46003</v>
+      </c>
+      <c r="C19" s="38">
+        <v>46014</v>
+      </c>
+      <c r="D19" s="86">
+        <v>135836307</v>
+      </c>
+      <c r="E19" s="17">
+        <v>3450183209</v>
+      </c>
+      <c r="F19" s="87" t="s">
+        <v>273</v>
+      </c>
+      <c r="G19" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="H19" s="92" t="s">
+        <v>253</v>
+      </c>
+      <c r="I19" s="38">
+        <v>46003</v>
+      </c>
     </row>
     <row r="20" spans="1:9">
-      <c r="A20" s="6"/>
-      <c r="B20" s="7"/>
-      <c r="C20" s="23"/>
-      <c r="D20" s="37"/>
-      <c r="E20" s="17"/>
-      <c r="F20" s="11"/>
-      <c r="G20" s="36"/>
-      <c r="H20" s="39"/>
-      <c r="I20" s="38"/>
+      <c r="A20" s="36" t="s">
+        <v>9</v>
+      </c>
+      <c r="B20" s="38">
+        <v>46002</v>
+      </c>
+      <c r="C20" s="38">
+        <v>46014</v>
+      </c>
+      <c r="D20" s="86">
+        <v>135818945</v>
+      </c>
+      <c r="E20" s="17">
+        <v>3450181625</v>
+      </c>
+      <c r="F20" s="87" t="s">
+        <v>274</v>
+      </c>
+      <c r="G20" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="H20" s="92" t="s">
+        <v>253</v>
+      </c>
+      <c r="I20" s="38">
+        <v>46002</v>
+      </c>
     </row>
     <row r="21" spans="1:9">
-      <c r="A21" s="6"/>
-      <c r="B21" s="7"/>
-      <c r="C21" s="23"/>
-      <c r="D21" s="37"/>
-      <c r="E21" s="17"/>
-      <c r="F21" s="11"/>
-      <c r="G21" s="36"/>
-      <c r="H21" s="39"/>
-      <c r="I21" s="38"/>
+      <c r="A21" s="36" t="s">
+        <v>9</v>
+      </c>
+      <c r="B21" s="38">
+        <v>46002</v>
+      </c>
+      <c r="C21" s="38">
+        <v>46014</v>
+      </c>
+      <c r="D21" s="86">
+        <v>135805722</v>
+      </c>
+      <c r="E21" s="17">
+        <v>3450180250</v>
+      </c>
+      <c r="F21" s="87" t="s">
+        <v>275</v>
+      </c>
+      <c r="G21" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="H21" s="92" t="s">
+        <v>253</v>
+      </c>
+      <c r="I21" s="38">
+        <v>46002</v>
+      </c>
     </row>
     <row r="22" spans="1:9">
-      <c r="A22" s="6"/>
-      <c r="B22" s="7"/>
-      <c r="C22" s="23"/>
-      <c r="D22" s="37"/>
-      <c r="E22" s="17"/>
-      <c r="F22" s="11"/>
-      <c r="G22" s="36"/>
-      <c r="H22" s="39"/>
-      <c r="I22" s="38"/>
+      <c r="A22" s="36" t="s">
+        <v>9</v>
+      </c>
+      <c r="B22" s="38">
+        <v>46009</v>
+      </c>
+      <c r="C22" s="38">
+        <v>46014</v>
+      </c>
+      <c r="D22" s="86">
+        <v>135921411</v>
+      </c>
+      <c r="E22" s="17">
+        <v>3450189908</v>
+      </c>
+      <c r="F22" s="87" t="s">
+        <v>276</v>
+      </c>
+      <c r="G22" s="36" t="s">
+        <v>11</v>
+      </c>
+      <c r="H22" s="92" t="s">
+        <v>268</v>
+      </c>
+      <c r="I22" s="38">
+        <v>46013</v>
+      </c>
     </row>
     <row r="23" spans="1:9">
-      <c r="A23" s="6"/>
-      <c r="B23" s="7"/>
-      <c r="C23" s="23"/>
-      <c r="D23" s="37"/>
-      <c r="E23" s="17"/>
-      <c r="F23" s="11"/>
-      <c r="G23" s="36"/>
-      <c r="H23" s="39"/>
-      <c r="I23" s="38"/>
+      <c r="A23" s="36" t="s">
+        <v>9</v>
+      </c>
+      <c r="B23" s="38">
+        <v>46009</v>
+      </c>
+      <c r="C23" s="38">
+        <v>46014</v>
+      </c>
+      <c r="D23" s="86">
+        <v>135924328</v>
+      </c>
+      <c r="E23" s="17">
+        <v>3450190227</v>
+      </c>
+      <c r="F23" s="87" t="s">
+        <v>277</v>
+      </c>
+      <c r="G23" s="36" t="s">
+        <v>21</v>
+      </c>
+      <c r="H23" s="92" t="s">
+        <v>278</v>
+      </c>
+      <c r="I23" s="38">
+        <v>46009</v>
+      </c>
     </row>
     <row r="24" spans="1:9">
-      <c r="A24" s="6"/>
-      <c r="B24" s="7"/>
-      <c r="C24" s="23"/>
-      <c r="D24" s="37"/>
-      <c r="E24" s="17"/>
-      <c r="F24" s="11"/>
-      <c r="G24" s="36"/>
-      <c r="H24" s="39"/>
-      <c r="I24" s="38"/>
+      <c r="A24" s="36" t="s">
+        <v>9</v>
+      </c>
+      <c r="B24" s="38">
+        <v>46009</v>
+      </c>
+      <c r="C24" s="38">
+        <v>46014</v>
+      </c>
+      <c r="D24" s="86">
+        <v>135935530</v>
+      </c>
+      <c r="E24" s="17">
+        <v>3450191415</v>
+      </c>
+      <c r="F24" s="87" t="s">
+        <v>279</v>
+      </c>
+      <c r="G24" s="36" t="s">
+        <v>21</v>
+      </c>
+      <c r="H24" s="92" t="s">
+        <v>280</v>
+      </c>
+      <c r="I24" s="38">
+        <v>46009</v>
+      </c>
     </row>
     <row r="25" spans="1:9">
-      <c r="A25" s="6"/>
-      <c r="B25" s="7"/>
-      <c r="C25" s="23"/>
-      <c r="D25" s="37"/>
-      <c r="E25" s="17"/>
-      <c r="F25" s="11"/>
-      <c r="G25" s="36"/>
-      <c r="H25" s="39"/>
-      <c r="I25" s="38"/>
+      <c r="A25" s="36" t="s">
+        <v>9</v>
+      </c>
+      <c r="B25" s="38">
+        <v>46014</v>
+      </c>
+      <c r="C25" s="38">
+        <v>46014</v>
+      </c>
+      <c r="D25" s="86">
+        <v>135960647</v>
+      </c>
+      <c r="E25" s="17">
+        <v>3450193274</v>
+      </c>
+      <c r="F25" s="87" t="s">
+        <v>281</v>
+      </c>
+      <c r="G25" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="H25" s="92" t="s">
+        <v>38</v>
+      </c>
+      <c r="I25" s="38">
+        <v>46014</v>
+      </c>
     </row>
     <row r="26" spans="1:9">
-      <c r="A26" s="6"/>
-      <c r="B26" s="7"/>
-      <c r="C26" s="23"/>
-      <c r="D26" s="37"/>
-      <c r="E26" s="17"/>
-      <c r="F26" s="11"/>
-      <c r="G26" s="36"/>
-      <c r="H26" s="39"/>
-      <c r="I26" s="38"/>
+      <c r="A26" s="36" t="s">
+        <v>9</v>
+      </c>
+      <c r="B26" s="38">
+        <v>46028</v>
+      </c>
+      <c r="C26" s="38">
+        <v>46014</v>
+      </c>
+      <c r="D26" s="86">
+        <v>135945091</v>
+      </c>
+      <c r="E26" s="17">
+        <v>3450192020</v>
+      </c>
+      <c r="F26" s="87" t="s">
+        <v>282</v>
+      </c>
+      <c r="G26" s="36" t="s">
+        <v>11</v>
+      </c>
+      <c r="H26" s="92" t="s">
+        <v>268</v>
+      </c>
+      <c r="I26" s="38">
+        <v>46013</v>
+      </c>
     </row>
     <row r="27" spans="1:9">
-      <c r="A27" s="6"/>
-      <c r="B27" s="7"/>
-      <c r="C27" s="23"/>
-      <c r="D27" s="37"/>
-      <c r="E27" s="17"/>
-      <c r="F27" s="11"/>
-      <c r="G27" s="36"/>
-      <c r="H27" s="39"/>
-      <c r="I27" s="38"/>
+      <c r="A27" s="36" t="s">
+        <v>9</v>
+      </c>
+      <c r="B27" s="80">
+        <v>46011</v>
+      </c>
+      <c r="C27" s="38">
+        <v>46014</v>
+      </c>
+      <c r="D27" s="86">
+        <v>135965205</v>
+      </c>
+      <c r="E27" s="17">
+        <v>3450193703</v>
+      </c>
+      <c r="F27" s="87" t="s">
+        <v>283</v>
+      </c>
+      <c r="G27" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="H27" s="92" t="s">
+        <v>38</v>
+      </c>
+      <c r="I27" s="38">
+        <v>46011</v>
+      </c>
     </row>
     <row r="28" spans="1:9">
-      <c r="A28" s="6"/>
-      <c r="B28" s="41"/>
-      <c r="C28" s="23"/>
-      <c r="D28" s="37"/>
-      <c r="E28" s="17"/>
-      <c r="F28" s="11"/>
-      <c r="G28" s="36"/>
-      <c r="H28" s="39"/>
-      <c r="I28" s="38"/>
+      <c r="A28" s="36" t="s">
+        <v>9</v>
+      </c>
+      <c r="B28" s="38">
+        <v>46013</v>
+      </c>
+      <c r="C28" s="38">
+        <v>46014</v>
+      </c>
+      <c r="D28" s="86">
+        <v>135979980</v>
+      </c>
+      <c r="E28" s="17">
+        <v>3450194583</v>
+      </c>
+      <c r="F28" s="87" t="s">
+        <v>284</v>
+      </c>
+      <c r="G28" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="H28" s="92" t="s">
+        <v>38</v>
+      </c>
+      <c r="I28" s="38">
+        <v>46013</v>
+      </c>
     </row>
     <row r="29" spans="1:9">
-      <c r="A29" s="6"/>
-      <c r="B29" s="7"/>
-      <c r="C29" s="23"/>
-      <c r="D29" s="37"/>
-      <c r="E29" s="17"/>
-      <c r="F29" s="11"/>
-      <c r="G29" s="36"/>
-      <c r="H29" s="12"/>
-      <c r="I29" s="38"/>
+      <c r="A29" s="36" t="s">
+        <v>9</v>
+      </c>
+      <c r="B29" s="38">
+        <v>46006</v>
+      </c>
+      <c r="C29" s="38">
+        <v>46014</v>
+      </c>
+      <c r="D29" s="86">
+        <v>135980242</v>
+      </c>
+      <c r="E29" s="17">
+        <v>3450186047</v>
+      </c>
+      <c r="F29" s="87" t="s">
+        <v>285</v>
+      </c>
+      <c r="G29" s="36" t="s">
+        <v>11</v>
+      </c>
+      <c r="H29" s="92" t="s">
+        <v>286</v>
+      </c>
+      <c r="I29" s="38">
+        <v>46013</v>
+      </c>
     </row>
     <row r="30" spans="1:9">
-      <c r="A30" s="6"/>
-      <c r="B30" s="7"/>
-      <c r="C30" s="23"/>
-      <c r="D30" s="37"/>
-      <c r="E30" s="17"/>
-      <c r="F30" s="11"/>
-      <c r="G30" s="36"/>
-      <c r="H30" s="12"/>
-      <c r="I30" s="38"/>
+      <c r="A30" s="36" t="s">
+        <v>9</v>
+      </c>
+      <c r="B30" s="38">
+        <v>46006</v>
+      </c>
+      <c r="C30" s="38">
+        <v>46014</v>
+      </c>
+      <c r="D30" s="86">
+        <v>135988240</v>
+      </c>
+      <c r="E30" s="17">
+        <v>3450185255</v>
+      </c>
+      <c r="F30" s="87" t="s">
+        <v>53</v>
+      </c>
+      <c r="G30" s="36" t="s">
+        <v>11</v>
+      </c>
+      <c r="H30" s="92" t="s">
+        <v>286</v>
+      </c>
+      <c r="I30" s="38">
+        <v>46013</v>
+      </c>
     </row>
     <row r="31" spans="1:9">
-      <c r="A31" s="6"/>
-      <c r="B31" s="7"/>
-      <c r="C31" s="23"/>
-      <c r="D31" s="37"/>
-      <c r="E31" s="17"/>
-      <c r="F31" s="11"/>
-      <c r="G31" s="36"/>
-      <c r="H31" s="12"/>
-      <c r="I31" s="38"/>
+      <c r="A31" s="36" t="s">
+        <v>9</v>
+      </c>
+      <c r="B31" s="38">
+        <v>45999</v>
+      </c>
+      <c r="C31" s="38">
+        <v>46014</v>
+      </c>
+      <c r="D31" s="86">
+        <v>135814543</v>
+      </c>
+      <c r="E31" s="17">
+        <v>3450176500</v>
+      </c>
+      <c r="F31" s="87" t="s">
+        <v>287</v>
+      </c>
+      <c r="G31" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="H31" s="92" t="s">
+        <v>253</v>
+      </c>
+      <c r="I31" s="38">
+        <v>45999</v>
+      </c>
     </row>
     <row r="32" spans="1:9">
-      <c r="A32" s="6"/>
-      <c r="B32" s="7"/>
-      <c r="C32" s="23"/>
-      <c r="D32" s="37"/>
-      <c r="E32" s="17"/>
-      <c r="F32" s="11"/>
-      <c r="G32" s="36"/>
-      <c r="H32" s="12"/>
-      <c r="I32" s="38"/>
+      <c r="A32" s="36" t="s">
+        <v>9</v>
+      </c>
+      <c r="B32" s="38">
+        <v>46002</v>
+      </c>
+      <c r="C32" s="38">
+        <v>46014</v>
+      </c>
+      <c r="D32" s="86">
+        <v>135816530</v>
+      </c>
+      <c r="E32" s="17">
+        <v>3450181383</v>
+      </c>
+      <c r="F32" s="87" t="s">
+        <v>288</v>
+      </c>
+      <c r="G32" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="H32" s="92" t="s">
+        <v>253</v>
+      </c>
+      <c r="I32" s="38">
+        <v>46002</v>
+      </c>
     </row>
     <row r="33" spans="1:9">
-      <c r="A33" s="6"/>
-      <c r="B33" s="7"/>
-      <c r="C33" s="23"/>
-      <c r="D33" s="37"/>
-      <c r="E33" s="17"/>
-      <c r="F33" s="11"/>
-      <c r="G33" s="36"/>
-      <c r="H33" s="12"/>
-      <c r="I33" s="38"/>
+      <c r="A33" s="36" t="s">
+        <v>9</v>
+      </c>
+      <c r="B33" s="38">
+        <v>46002</v>
+      </c>
+      <c r="C33" s="38">
+        <v>46014</v>
+      </c>
+      <c r="D33" s="86">
+        <v>135817976</v>
+      </c>
+      <c r="E33" s="17">
+        <v>3450181548</v>
+      </c>
+      <c r="F33" s="87" t="s">
+        <v>289</v>
+      </c>
+      <c r="G33" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="H33" s="92" t="s">
+        <v>253</v>
+      </c>
+      <c r="I33" s="38">
+        <v>46002</v>
+      </c>
     </row>
     <row r="34" spans="1:9">
-      <c r="A34" s="6"/>
-      <c r="B34" s="7"/>
-      <c r="C34" s="23"/>
-      <c r="D34" s="37"/>
-      <c r="E34" s="17"/>
-      <c r="F34" s="11"/>
-      <c r="G34" s="36"/>
-      <c r="H34" s="12"/>
-      <c r="I34" s="38"/>
+      <c r="A34" s="36" t="s">
+        <v>9</v>
+      </c>
+      <c r="B34" s="38">
+        <v>46002</v>
+      </c>
+      <c r="C34" s="38">
+        <v>46014</v>
+      </c>
+      <c r="D34" s="86">
+        <v>135821428</v>
+      </c>
+      <c r="E34" s="17">
+        <v>3450181955</v>
+      </c>
+      <c r="F34" s="87" t="s">
+        <v>290</v>
+      </c>
+      <c r="G34" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="H34" s="92" t="s">
+        <v>253</v>
+      </c>
+      <c r="I34" s="38">
+        <v>46002</v>
+      </c>
     </row>
     <row r="35" spans="1:9">
-      <c r="A35" s="6"/>
-      <c r="B35" s="7"/>
-      <c r="C35" s="23"/>
-      <c r="D35" s="37"/>
-      <c r="E35" s="17"/>
-      <c r="F35" s="11"/>
-      <c r="G35" s="36"/>
-      <c r="H35" s="12"/>
-      <c r="I35" s="38"/>
+      <c r="A35" s="36" t="s">
+        <v>9</v>
+      </c>
+      <c r="B35" s="38">
+        <v>46003</v>
+      </c>
+      <c r="C35" s="38">
+        <v>46014</v>
+      </c>
+      <c r="D35" s="86">
+        <v>135827714</v>
+      </c>
+      <c r="E35" s="17">
+        <v>3450182329</v>
+      </c>
+      <c r="F35" s="87" t="s">
+        <v>291</v>
+      </c>
+      <c r="G35" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="H35" s="92" t="s">
+        <v>253</v>
+      </c>
+      <c r="I35" s="38">
+        <v>46003</v>
+      </c>
     </row>
     <row r="36" spans="1:9">
-      <c r="A36" s="6"/>
-      <c r="B36" s="7"/>
-      <c r="C36" s="23"/>
-      <c r="D36" s="37"/>
-      <c r="E36" s="17"/>
-      <c r="F36" s="11"/>
-      <c r="G36" s="36"/>
-      <c r="H36" s="12"/>
-      <c r="I36" s="38"/>
+      <c r="A36" s="36" t="s">
+        <v>9</v>
+      </c>
+      <c r="B36" s="38">
+        <v>46003</v>
+      </c>
+      <c r="C36" s="38">
+        <v>46014</v>
+      </c>
+      <c r="D36" s="86">
+        <v>135829029</v>
+      </c>
+      <c r="E36" s="17">
+        <v>3450182428</v>
+      </c>
+      <c r="F36" s="87" t="s">
+        <v>292</v>
+      </c>
+      <c r="G36" s="36" t="s">
+        <v>11</v>
+      </c>
+      <c r="H36" s="92" t="s">
+        <v>268</v>
+      </c>
+      <c r="I36" s="38">
+        <v>46013</v>
+      </c>
     </row>
     <row r="37" spans="1:9">
-      <c r="A37" s="6"/>
-      <c r="B37" s="7"/>
-      <c r="C37" s="23"/>
-      <c r="D37" s="37"/>
-      <c r="E37" s="17"/>
-      <c r="F37" s="11"/>
-      <c r="G37" s="36"/>
-      <c r="H37" s="12"/>
-      <c r="I37" s="38"/>
+      <c r="A37" s="36" t="s">
+        <v>9</v>
+      </c>
+      <c r="B37" s="38">
+        <v>46003</v>
+      </c>
+      <c r="C37" s="38">
+        <v>46014</v>
+      </c>
+      <c r="D37" s="86">
+        <v>135830164</v>
+      </c>
+      <c r="E37" s="17">
+        <v>3450182550</v>
+      </c>
+      <c r="F37" s="87" t="s">
+        <v>293</v>
+      </c>
+      <c r="G37" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="H37" s="92" t="s">
+        <v>253</v>
+      </c>
+      <c r="I37" s="38">
+        <v>46003</v>
+      </c>
     </row>
     <row r="38" spans="1:9">
-      <c r="A38" s="6"/>
-      <c r="B38" s="7"/>
-      <c r="C38" s="23"/>
-      <c r="D38" s="37"/>
-      <c r="E38" s="17"/>
-      <c r="F38" s="11"/>
-      <c r="G38" s="36"/>
-      <c r="H38" s="12"/>
-      <c r="I38" s="38"/>
+      <c r="A38" s="36" t="s">
+        <v>9</v>
+      </c>
+      <c r="B38" s="38">
+        <v>46003</v>
+      </c>
+      <c r="C38" s="38">
+        <v>46014</v>
+      </c>
+      <c r="D38" s="86">
+        <v>135830883</v>
+      </c>
+      <c r="E38" s="17">
+        <v>3450182626</v>
+      </c>
+      <c r="F38" s="87" t="s">
+        <v>294</v>
+      </c>
+      <c r="G38" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="H38" s="92" t="s">
+        <v>253</v>
+      </c>
+      <c r="I38" s="38">
+        <v>46003</v>
+      </c>
     </row>
     <row r="39" spans="1:9">
-      <c r="A39" s="6"/>
-      <c r="B39" s="7"/>
-      <c r="C39" s="23"/>
-      <c r="D39" s="37"/>
-      <c r="E39" s="17"/>
-      <c r="F39" s="11"/>
-      <c r="G39" s="36"/>
-      <c r="H39" s="12"/>
-      <c r="I39" s="38"/>
+      <c r="A39" s="36" t="s">
+        <v>9</v>
+      </c>
+      <c r="B39" s="38">
+        <v>46003</v>
+      </c>
+      <c r="C39" s="38">
+        <v>46014</v>
+      </c>
+      <c r="D39" s="86">
+        <v>135831939</v>
+      </c>
+      <c r="E39" s="17">
+        <v>3450182714</v>
+      </c>
+      <c r="F39" s="87" t="s">
+        <v>295</v>
+      </c>
+      <c r="G39" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="H39" s="92" t="s">
+        <v>253</v>
+      </c>
+      <c r="I39" s="38">
+        <v>46003</v>
+      </c>
     </row>
     <row r="40" spans="1:9">
-      <c r="A40" s="6"/>
-      <c r="B40" s="7"/>
-      <c r="C40" s="23"/>
-      <c r="D40" s="37"/>
-      <c r="E40" s="17"/>
-      <c r="F40" s="11"/>
-      <c r="G40" s="36"/>
-      <c r="H40" s="12"/>
-      <c r="I40" s="38"/>
+      <c r="A40" s="36" t="s">
+        <v>9</v>
+      </c>
+      <c r="B40" s="38">
+        <v>46000</v>
+      </c>
+      <c r="C40" s="38">
+        <v>46014</v>
+      </c>
+      <c r="D40" s="86">
+        <v>135833533</v>
+      </c>
+      <c r="E40" s="17">
+        <v>3450177885</v>
+      </c>
+      <c r="F40" s="87" t="s">
+        <v>296</v>
+      </c>
+      <c r="G40" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="H40" s="92" t="s">
+        <v>253</v>
+      </c>
+      <c r="I40" s="38">
+        <v>46000</v>
+      </c>
     </row>
     <row r="41" spans="1:9">
-      <c r="A41" s="6"/>
-      <c r="B41" s="7"/>
-      <c r="C41" s="23"/>
-      <c r="D41" s="37"/>
-      <c r="E41" s="17"/>
-      <c r="F41" s="11"/>
-      <c r="G41" s="36"/>
-      <c r="H41" s="12"/>
-      <c r="I41" s="38"/>
+      <c r="A41" s="36" t="s">
+        <v>9</v>
+      </c>
+      <c r="B41" s="38">
+        <v>46003</v>
+      </c>
+      <c r="C41" s="38">
+        <v>46014</v>
+      </c>
+      <c r="D41" s="86">
+        <v>135834818</v>
+      </c>
+      <c r="E41" s="17">
+        <v>3450183022</v>
+      </c>
+      <c r="F41" s="87" t="s">
+        <v>297</v>
+      </c>
+      <c r="G41" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="H41" s="92" t="s">
+        <v>253</v>
+      </c>
+      <c r="I41" s="38">
+        <v>46003</v>
+      </c>
     </row>
     <row r="42" spans="1:9">
-      <c r="A42" s="6"/>
-      <c r="B42" s="8"/>
-      <c r="C42" s="7"/>
-      <c r="D42" s="28"/>
-      <c r="E42" s="17"/>
-      <c r="F42" s="12"/>
-      <c r="G42" s="36"/>
-      <c r="H42" s="12"/>
-      <c r="I42" s="12"/>
+      <c r="A42" s="36" t="s">
+        <v>9</v>
+      </c>
+      <c r="B42" s="38">
+        <v>46003</v>
+      </c>
+      <c r="C42" s="38">
+        <v>46014</v>
+      </c>
+      <c r="D42" s="86">
+        <v>135838192</v>
+      </c>
+      <c r="E42" s="17">
+        <v>3450183363</v>
+      </c>
+      <c r="F42" s="87" t="s">
+        <v>298</v>
+      </c>
+      <c r="G42" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="H42" s="92" t="s">
+        <v>253</v>
+      </c>
+      <c r="I42" s="38">
+        <v>46003</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9">
+      <c r="A43" s="36" t="s">
+        <v>9</v>
+      </c>
+      <c r="B43" s="38">
+        <v>46003</v>
+      </c>
+      <c r="C43" s="38">
+        <v>46014</v>
+      </c>
+      <c r="D43" s="86">
+        <v>135842597</v>
+      </c>
+      <c r="E43" s="17">
+        <v>3450183913</v>
+      </c>
+      <c r="F43" s="87" t="s">
+        <v>299</v>
+      </c>
+      <c r="G43" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="H43" s="92" t="s">
+        <v>253</v>
+      </c>
+      <c r="I43" s="38">
+        <v>46003</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9">
+      <c r="A44" s="36" t="s">
+        <v>9</v>
+      </c>
+      <c r="B44" s="38">
+        <v>46003</v>
+      </c>
+      <c r="C44" s="38">
+        <v>46014</v>
+      </c>
+      <c r="D44" s="86">
+        <v>135842945</v>
+      </c>
+      <c r="E44" s="17">
+        <v>3450183979</v>
+      </c>
+      <c r="F44" s="87" t="s">
+        <v>300</v>
+      </c>
+      <c r="G44" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="H44" s="92" t="s">
+        <v>253</v>
+      </c>
+      <c r="I44" s="38">
+        <v>46003</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9">
+      <c r="A45" s="36" t="s">
+        <v>9</v>
+      </c>
+      <c r="B45" s="38">
+        <v>46003</v>
+      </c>
+      <c r="C45" s="38">
+        <v>46014</v>
+      </c>
+      <c r="D45" s="86">
+        <v>135843465</v>
+      </c>
+      <c r="E45" s="17">
+        <v>3450184067</v>
+      </c>
+      <c r="F45" s="87" t="s">
+        <v>301</v>
+      </c>
+      <c r="G45" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="H45" s="92" t="s">
+        <v>253</v>
+      </c>
+      <c r="I45" s="38">
+        <v>46003</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9">
+      <c r="A46" s="36" t="s">
+        <v>9</v>
+      </c>
+      <c r="B46" s="38">
+        <v>46008</v>
+      </c>
+      <c r="C46" s="38">
+        <v>46014</v>
+      </c>
+      <c r="D46" s="86">
+        <v>135904139</v>
+      </c>
+      <c r="E46" s="17">
+        <v>3450188819</v>
+      </c>
+      <c r="F46" s="87" t="s">
+        <v>302</v>
+      </c>
+      <c r="G46" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="H46" s="92" t="s">
+        <v>253</v>
+      </c>
+      <c r="I46" s="38">
+        <v>46008</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9">
+      <c r="A47" s="36" t="s">
+        <v>9</v>
+      </c>
+      <c r="B47" s="38">
+        <v>46011</v>
+      </c>
+      <c r="C47" s="38">
+        <v>46014</v>
+      </c>
+      <c r="D47" s="86">
+        <v>135793523</v>
+      </c>
+      <c r="E47" s="17">
+        <v>3450179360</v>
+      </c>
+      <c r="F47" s="87" t="s">
+        <v>303</v>
+      </c>
+      <c r="G47" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="H47" s="92" t="s">
+        <v>253</v>
+      </c>
+      <c r="I47" s="38">
+        <v>46011</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9">
+      <c r="A48" s="36" t="s">
+        <v>9</v>
+      </c>
+      <c r="B48" s="38">
+        <v>46007</v>
+      </c>
+      <c r="C48" s="38">
+        <v>46014</v>
+      </c>
+      <c r="D48" s="86">
+        <v>135790142</v>
+      </c>
+      <c r="E48" s="17">
+        <v>3450174695</v>
+      </c>
+      <c r="F48" s="87" t="s">
+        <v>304</v>
+      </c>
+      <c r="G48" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="H48" s="92" t="s">
+        <v>159</v>
+      </c>
+      <c r="I48" s="38">
+        <v>46007</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9">
+      <c r="A49" s="36" t="s">
+        <v>9</v>
+      </c>
+      <c r="B49" s="38">
+        <v>46007</v>
+      </c>
+      <c r="C49" s="38">
+        <v>46014</v>
+      </c>
+      <c r="D49" s="86">
+        <v>135879826</v>
+      </c>
+      <c r="E49" s="17">
+        <v>3450186620</v>
+      </c>
+      <c r="F49" s="87" t="s">
+        <v>305</v>
+      </c>
+      <c r="G49" s="36" t="s">
+        <v>21</v>
+      </c>
+      <c r="H49" s="92" t="s">
+        <v>306</v>
+      </c>
+      <c r="I49" s="38">
+        <v>46007</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9">
+      <c r="A50" s="36" t="s">
+        <v>9</v>
+      </c>
+      <c r="B50" s="38">
+        <v>46001</v>
+      </c>
+      <c r="C50" s="38">
+        <v>46014</v>
+      </c>
+      <c r="D50" s="86">
+        <v>135871670</v>
+      </c>
+      <c r="E50" s="17">
+        <v>3450178920</v>
+      </c>
+      <c r="F50" s="87" t="s">
+        <v>307</v>
+      </c>
+      <c r="G50" s="36" t="s">
+        <v>21</v>
+      </c>
+      <c r="H50" s="92" t="s">
+        <v>308</v>
+      </c>
+      <c r="I50" s="38">
+        <v>46001</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9">
+      <c r="A51" s="36" t="s">
+        <v>9</v>
+      </c>
+      <c r="B51" s="38">
+        <v>46007</v>
+      </c>
+      <c r="C51" s="38">
+        <v>46014</v>
+      </c>
+      <c r="D51" s="86">
+        <v>135861676</v>
+      </c>
+      <c r="E51" s="17">
+        <v>3450185332</v>
+      </c>
+      <c r="F51" s="87" t="s">
+        <v>281</v>
+      </c>
+      <c r="G51" s="36" t="s">
+        <v>11</v>
+      </c>
+      <c r="H51" s="92" t="s">
+        <v>268</v>
+      </c>
+      <c r="I51" s="38">
+        <v>46013</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9">
+      <c r="A52" s="36" t="s">
+        <v>9</v>
+      </c>
+      <c r="B52" s="38">
+        <v>46007</v>
+      </c>
+      <c r="C52" s="38">
+        <v>46014</v>
+      </c>
+      <c r="D52" s="86">
+        <v>135885250</v>
+      </c>
+      <c r="E52" s="17">
+        <v>3450187170</v>
+      </c>
+      <c r="F52" s="87" t="s">
+        <v>309</v>
+      </c>
+      <c r="G52" s="36" t="s">
+        <v>11</v>
+      </c>
+      <c r="H52" s="92" t="s">
+        <v>268</v>
+      </c>
+      <c r="I52" s="38">
+        <v>46013</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9">
+      <c r="A53" s="36" t="s">
+        <v>9</v>
+      </c>
+      <c r="B53" s="38">
+        <v>46001</v>
+      </c>
+      <c r="C53" s="38">
+        <v>46014</v>
+      </c>
+      <c r="D53" s="86">
+        <v>135791615</v>
+      </c>
+      <c r="E53" s="17">
+        <v>3450179227</v>
+      </c>
+      <c r="F53" s="87" t="s">
+        <v>310</v>
+      </c>
+      <c r="G53" s="36" t="s">
+        <v>15</v>
+      </c>
+      <c r="H53" s="92" t="s">
+        <v>257</v>
+      </c>
+      <c r="I53" s="38">
+        <v>46007</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9">
+      <c r="A54" s="36" t="s">
+        <v>9</v>
+      </c>
+      <c r="B54" s="38">
+        <v>46001</v>
+      </c>
+      <c r="C54" s="38">
+        <v>46014</v>
+      </c>
+      <c r="D54" s="86">
+        <v>135795351</v>
+      </c>
+      <c r="E54" s="17">
+        <v>3450179612</v>
+      </c>
+      <c r="F54" s="87" t="s">
+        <v>311</v>
+      </c>
+      <c r="G54" s="36" t="s">
+        <v>15</v>
+      </c>
+      <c r="H54" s="92" t="s">
+        <v>257</v>
+      </c>
+      <c r="I54" s="38">
+        <v>46008</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9">
+      <c r="A55" s="36" t="s">
+        <v>9</v>
+      </c>
+      <c r="B55" s="38">
+        <v>46001</v>
+      </c>
+      <c r="C55" s="38">
+        <v>46014</v>
+      </c>
+      <c r="D55" s="86">
+        <v>135796461</v>
+      </c>
+      <c r="E55" s="17">
+        <v>3450179722</v>
+      </c>
+      <c r="F55" s="87" t="s">
+        <v>312</v>
+      </c>
+      <c r="G55" s="36" t="s">
+        <v>15</v>
+      </c>
+      <c r="H55" s="92" t="s">
+        <v>313</v>
+      </c>
+      <c r="I55" s="38">
+        <v>46008</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9">
+      <c r="A56" s="36" t="s">
+        <v>9</v>
+      </c>
+      <c r="B56" s="38">
+        <v>46002</v>
+      </c>
+      <c r="C56" s="38">
+        <v>46014</v>
+      </c>
+      <c r="D56" s="86">
+        <v>135807959</v>
+      </c>
+      <c r="E56" s="17">
+        <v>3450180536</v>
+      </c>
+      <c r="F56" s="87" t="s">
+        <v>314</v>
+      </c>
+      <c r="G56" s="36" t="s">
+        <v>15</v>
+      </c>
+      <c r="H56" s="92" t="s">
+        <v>249</v>
+      </c>
+      <c r="I56" s="38">
+        <v>46007</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9">
+      <c r="A57" s="36" t="s">
+        <v>9</v>
+      </c>
+      <c r="B57" s="38">
+        <v>46002</v>
+      </c>
+      <c r="C57" s="38">
+        <v>46014</v>
+      </c>
+      <c r="D57" s="86">
+        <v>135809645</v>
+      </c>
+      <c r="E57" s="17">
+        <v>3450180690</v>
+      </c>
+      <c r="F57" s="87" t="s">
+        <v>315</v>
+      </c>
+      <c r="G57" s="36" t="s">
+        <v>15</v>
+      </c>
+      <c r="H57" s="92" t="s">
+        <v>249</v>
+      </c>
+      <c r="I57" s="38">
+        <v>46007</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9">
+      <c r="A58" s="36" t="s">
+        <v>9</v>
+      </c>
+      <c r="B58" s="38">
+        <v>46006</v>
+      </c>
+      <c r="C58" s="38">
+        <v>46014</v>
+      </c>
+      <c r="D58" s="86">
+        <v>135866286</v>
+      </c>
+      <c r="E58" s="17">
+        <v>3450185838</v>
+      </c>
+      <c r="F58" s="87" t="s">
+        <v>316</v>
+      </c>
+      <c r="G58" s="36" t="s">
+        <v>21</v>
+      </c>
+      <c r="H58" s="92" t="s">
+        <v>317</v>
+      </c>
+      <c r="I58" s="38">
+        <v>46006</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9">
+      <c r="A59" s="36" t="s">
+        <v>9</v>
+      </c>
+      <c r="B59" s="38">
+        <v>46014</v>
+      </c>
+      <c r="C59" s="38">
+        <v>46014</v>
+      </c>
+      <c r="D59" s="86">
+        <v>136000391</v>
+      </c>
+      <c r="E59" s="17">
+        <v>3450195860</v>
+      </c>
+      <c r="F59" s="87" t="s">
+        <v>318</v>
+      </c>
+      <c r="G59" s="36" t="s">
+        <v>11</v>
+      </c>
+      <c r="H59" s="92" t="s">
+        <v>319</v>
+      </c>
+      <c r="I59" s="38">
+        <v>46014</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9">
+      <c r="A60" s="36" t="s">
+        <v>9</v>
+      </c>
+      <c r="B60" s="38">
+        <v>46013</v>
+      </c>
+      <c r="C60" s="38">
+        <v>46014</v>
+      </c>
+      <c r="D60" s="86">
+        <v>135836302</v>
+      </c>
+      <c r="E60" s="17">
+        <v>3450183198</v>
+      </c>
+      <c r="F60" s="87" t="s">
+        <v>320</v>
+      </c>
+      <c r="G60" s="36" t="s">
+        <v>15</v>
+      </c>
+      <c r="H60" s="92" t="s">
+        <v>321</v>
+      </c>
+      <c r="I60" s="38">
+        <v>46010</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9">
+      <c r="A61" s="36" t="s">
+        <v>9</v>
+      </c>
+      <c r="B61" s="38">
+        <v>46003</v>
+      </c>
+      <c r="C61" s="38">
+        <v>46014</v>
+      </c>
+      <c r="D61" s="86">
+        <v>135839419</v>
+      </c>
+      <c r="E61" s="17">
+        <v>3450183517</v>
+      </c>
+      <c r="F61" s="87" t="s">
+        <v>322</v>
+      </c>
+      <c r="G61" s="36" t="s">
+        <v>55</v>
+      </c>
+      <c r="H61" s="92" t="s">
+        <v>323</v>
+      </c>
+      <c r="I61" s="38">
+        <v>46009</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9">
+      <c r="A62" s="36" t="s">
+        <v>9</v>
+      </c>
+      <c r="B62" s="38">
+        <v>46003</v>
+      </c>
+      <c r="C62" s="38">
+        <v>46014</v>
+      </c>
+      <c r="D62" s="86">
+        <v>135843092</v>
+      </c>
+      <c r="E62" s="17">
+        <v>3450183980</v>
+      </c>
+      <c r="F62" s="87" t="s">
+        <v>324</v>
+      </c>
+      <c r="G62" s="36" t="s">
+        <v>15</v>
+      </c>
+      <c r="H62" s="92" t="s">
+        <v>255</v>
+      </c>
+      <c r="I62" s="38">
+        <v>46010</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9">
+      <c r="A63" s="36" t="s">
+        <v>9</v>
+      </c>
+      <c r="B63" s="38">
+        <v>46006</v>
+      </c>
+      <c r="C63" s="38">
+        <v>46014</v>
+      </c>
+      <c r="D63" s="86">
+        <v>135843995</v>
+      </c>
+      <c r="E63" s="17">
+        <v>3450184122</v>
+      </c>
+      <c r="F63" s="87" t="s">
+        <v>325</v>
+      </c>
+      <c r="G63" s="36" t="s">
+        <v>15</v>
+      </c>
+      <c r="H63" s="92" t="s">
+        <v>255</v>
+      </c>
+      <c r="I63" s="38">
+        <v>46010</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9">
+      <c r="A64" s="36" t="s">
+        <v>9</v>
+      </c>
+      <c r="B64" s="38">
+        <v>46006</v>
+      </c>
+      <c r="C64" s="38">
+        <v>46014</v>
+      </c>
+      <c r="D64" s="86">
+        <v>135867237</v>
+      </c>
+      <c r="E64" s="17">
+        <v>3450185882</v>
+      </c>
+      <c r="F64" s="87" t="s">
+        <v>326</v>
+      </c>
+      <c r="G64" s="36" t="s">
+        <v>21</v>
+      </c>
+      <c r="H64" s="92" t="s">
+        <v>327</v>
+      </c>
+      <c r="I64" s="38">
+        <v>46006</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9">
+      <c r="A65" s="36" t="s">
+        <v>9</v>
+      </c>
+      <c r="B65" s="38">
+        <v>46024</v>
+      </c>
+      <c r="C65" s="38">
+        <v>46014</v>
+      </c>
+      <c r="D65" s="86">
+        <v>135780061</v>
+      </c>
+      <c r="E65" s="17">
+        <v>3450178556</v>
+      </c>
+      <c r="F65" s="87" t="s">
+        <v>328</v>
+      </c>
+      <c r="G65" s="36" t="s">
+        <v>15</v>
+      </c>
+      <c r="H65" s="92" t="s">
+        <v>329</v>
+      </c>
+      <c r="I65" s="38">
+        <v>46006</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9">
+      <c r="A66" s="17"/>
+      <c r="B66" s="17"/>
+      <c r="C66" s="17"/>
+      <c r="D66" s="17"/>
+      <c r="E66" s="17"/>
+      <c r="F66" s="17"/>
+      <c r="G66" s="36"/>
+      <c r="H66" s="92"/>
+      <c r="I66" s="17"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B1:C1">
-    <cfRule type="notContainsBlanks" priority="2">
+    <cfRule type="notContainsBlanks" priority="3">
       <formula>LEN(TRIM(B1))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A18:A41" xr:uid="{EC7C7A5C-617A-4EC2-BB80-7CA761AA8730}">
-      <formula1>#REF!</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G42" xr:uid="{C8229196-52D6-4347-81FE-B1256BABDAAC}">
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G66" xr:uid="{C8229196-52D6-4347-81FE-B1256BABDAAC}">
       <formula1>"Vistoria Frustrada;,Vistoria Recusada,Bônus;,Desistência;,Inadimplência;,Política de Aceitação;,Duplicidade;,Demais Motivos,Falta de Vistoria;,"</formula1>
     </dataValidation>
   </dataValidations>
@@ -8078,7 +9892,7 @@
           <x14:formula1>
             <xm:f>'22.12'!#REF!</xm:f>
           </x14:formula1>
-          <xm:sqref>A2:A17</xm:sqref>
+          <xm:sqref>A2:A65</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -8088,7 +9902,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74836D31-80F5-4003-9D08-4541F6DF416B}">
-  <dimension ref="A1:I43"/>
+  <dimension ref="A1:I38"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.5703125" customWidth="1"/>
@@ -8135,362 +9949,846 @@
       <c r="A2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="23"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="36"/>
-      <c r="H2" s="39"/>
+      <c r="B2" s="7">
+        <v>46013</v>
+      </c>
+      <c r="C2" s="23">
+        <v>46015</v>
+      </c>
+      <c r="D2" s="37" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="17">
+        <v>3450194495</v>
+      </c>
+      <c r="F2" s="77" t="s">
+        <v>330</v>
+      </c>
+      <c r="G2" s="36" t="s">
+        <v>11</v>
+      </c>
+      <c r="H2" s="39" t="s">
+        <v>331</v>
+      </c>
       <c r="I2" s="38"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="7"/>
-      <c r="C3" s="23"/>
-      <c r="D3" s="37"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="11"/>
-      <c r="G3" s="36"/>
-      <c r="H3" s="39"/>
+      <c r="B3" s="7">
+        <v>46009</v>
+      </c>
+      <c r="C3" s="23">
+        <v>46015</v>
+      </c>
+      <c r="D3" s="60" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="88" t="s">
+        <v>332</v>
+      </c>
+      <c r="F3" s="89" t="s">
+        <v>333</v>
+      </c>
+      <c r="G3" s="36" t="s">
+        <v>11</v>
+      </c>
+      <c r="H3" s="39" t="s">
+        <v>331</v>
+      </c>
       <c r="I3" s="38"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="7"/>
-      <c r="C4" s="23"/>
-      <c r="D4" s="37"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="11"/>
-      <c r="G4" s="36"/>
-      <c r="H4" s="39"/>
-      <c r="I4" s="38"/>
+      <c r="B4" s="7">
+        <v>46002</v>
+      </c>
+      <c r="C4" s="23">
+        <v>46015</v>
+      </c>
+      <c r="D4" s="86">
+        <v>135815367</v>
+      </c>
+      <c r="E4" s="17">
+        <v>3450181262</v>
+      </c>
+      <c r="F4" s="78" t="s">
+        <v>334</v>
+      </c>
+      <c r="G4" s="59" t="s">
+        <v>15</v>
+      </c>
+      <c r="H4" s="91" t="s">
+        <v>335</v>
+      </c>
+      <c r="I4" s="38">
+        <v>46014</v>
+      </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="7"/>
-      <c r="C5" s="23"/>
-      <c r="D5" s="37"/>
-      <c r="E5" s="17"/>
-      <c r="F5" s="11"/>
-      <c r="G5" s="36"/>
-      <c r="H5" s="39"/>
-      <c r="I5" s="38"/>
+      <c r="B5" s="7">
+        <v>46006</v>
+      </c>
+      <c r="C5" s="23">
+        <v>46015</v>
+      </c>
+      <c r="D5" s="86">
+        <v>135855577</v>
+      </c>
+      <c r="E5" s="17">
+        <v>3450184837</v>
+      </c>
+      <c r="F5" s="78" t="s">
+        <v>336</v>
+      </c>
+      <c r="G5" s="59" t="s">
+        <v>11</v>
+      </c>
+      <c r="H5" s="39" t="s">
+        <v>331</v>
+      </c>
+      <c r="I5" s="38">
+        <v>46014</v>
+      </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="7"/>
-      <c r="C6" s="23"/>
-      <c r="D6" s="37"/>
-      <c r="E6" s="17"/>
-      <c r="F6" s="11"/>
-      <c r="G6" s="36"/>
-      <c r="H6" s="39"/>
-      <c r="I6" s="38"/>
+      <c r="B6" s="7">
+        <v>46010</v>
+      </c>
+      <c r="C6" s="23">
+        <v>46015</v>
+      </c>
+      <c r="D6" s="86">
+        <v>135891902</v>
+      </c>
+      <c r="E6" s="17">
+        <v>3450187818</v>
+      </c>
+      <c r="F6" s="78" t="s">
+        <v>337</v>
+      </c>
+      <c r="G6" s="59" t="s">
+        <v>11</v>
+      </c>
+      <c r="H6" s="39" t="s">
+        <v>331</v>
+      </c>
+      <c r="I6" s="38">
+        <v>46014</v>
+      </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="7"/>
-      <c r="C7" s="23"/>
-      <c r="D7" s="37"/>
-      <c r="E7" s="17"/>
-      <c r="F7" s="11"/>
-      <c r="G7" s="36"/>
-      <c r="H7" s="40"/>
-      <c r="I7" s="38"/>
+      <c r="B7" s="7">
+        <v>46007</v>
+      </c>
+      <c r="C7" s="23">
+        <v>46015</v>
+      </c>
+      <c r="D7" s="86">
+        <v>135886513</v>
+      </c>
+      <c r="E7" s="17">
+        <v>3450187279</v>
+      </c>
+      <c r="F7" s="78" t="s">
+        <v>338</v>
+      </c>
+      <c r="G7" s="59" t="s">
+        <v>11</v>
+      </c>
+      <c r="H7" s="40" t="s">
+        <v>331</v>
+      </c>
+      <c r="I7" s="38">
+        <v>46014</v>
+      </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="23"/>
-      <c r="D8" s="37"/>
-      <c r="E8" s="17"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="36"/>
-      <c r="H8" s="40"/>
-      <c r="I8" s="38"/>
+      <c r="B8" s="7">
+        <v>46004</v>
+      </c>
+      <c r="C8" s="23">
+        <v>46015</v>
+      </c>
+      <c r="D8" s="86">
+        <v>135840558</v>
+      </c>
+      <c r="E8" s="17">
+        <v>3450183627</v>
+      </c>
+      <c r="F8" s="78" t="s">
+        <v>339</v>
+      </c>
+      <c r="G8" s="59" t="s">
+        <v>11</v>
+      </c>
+      <c r="H8" s="40" t="s">
+        <v>331</v>
+      </c>
+      <c r="I8" s="38">
+        <v>46014</v>
+      </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="7"/>
-      <c r="C9" s="23"/>
-      <c r="D9" s="37"/>
-      <c r="E9" s="17"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="36"/>
-      <c r="H9" s="39"/>
-      <c r="I9" s="38"/>
+      <c r="B9" s="7">
+        <v>46009</v>
+      </c>
+      <c r="C9" s="23">
+        <v>46015</v>
+      </c>
+      <c r="D9" s="86">
+        <v>135920677</v>
+      </c>
+      <c r="E9" s="17">
+        <v>3450189864</v>
+      </c>
+      <c r="F9" s="78" t="s">
+        <v>340</v>
+      </c>
+      <c r="G9" s="59" t="s">
+        <v>21</v>
+      </c>
+      <c r="H9" s="40" t="s">
+        <v>341</v>
+      </c>
+      <c r="I9" s="38">
+        <v>46009</v>
+      </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="7"/>
-      <c r="C10" s="23"/>
-      <c r="D10" s="37"/>
-      <c r="E10" s="17"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="36"/>
-      <c r="H10" s="39"/>
-      <c r="I10" s="38"/>
+      <c r="B10" s="7">
+        <v>46009</v>
+      </c>
+      <c r="C10" s="23">
+        <v>46015</v>
+      </c>
+      <c r="D10" s="86">
+        <v>135923012</v>
+      </c>
+      <c r="E10" s="17">
+        <v>3450190084</v>
+      </c>
+      <c r="F10" s="78" t="s">
+        <v>342</v>
+      </c>
+      <c r="G10" s="59" t="s">
+        <v>40</v>
+      </c>
+      <c r="H10" s="39" t="s">
+        <v>193</v>
+      </c>
+      <c r="I10" s="38">
+        <v>46009</v>
+      </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="7"/>
-      <c r="C11" s="23"/>
-      <c r="D11" s="37"/>
-      <c r="E11" s="17"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="36"/>
-      <c r="H11" s="39"/>
-      <c r="I11" s="38"/>
+      <c r="B11" s="7">
+        <v>46009</v>
+      </c>
+      <c r="C11" s="23">
+        <v>46015</v>
+      </c>
+      <c r="D11" s="86">
+        <v>135933003</v>
+      </c>
+      <c r="E11" s="17">
+        <v>3450191162</v>
+      </c>
+      <c r="F11" s="78" t="s">
+        <v>343</v>
+      </c>
+      <c r="G11" s="59" t="s">
+        <v>21</v>
+      </c>
+      <c r="H11" s="39" t="s">
+        <v>344</v>
+      </c>
+      <c r="I11" s="38">
+        <v>46009</v>
+      </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="7"/>
-      <c r="C12" s="23"/>
-      <c r="D12" s="37"/>
-      <c r="E12" s="17"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="36"/>
-      <c r="H12" s="39"/>
-      <c r="I12" s="38"/>
+      <c r="B12" s="7">
+        <v>46009</v>
+      </c>
+      <c r="C12" s="23">
+        <v>46015</v>
+      </c>
+      <c r="D12" s="86">
+        <v>135934388</v>
+      </c>
+      <c r="E12" s="17">
+        <v>3450191338</v>
+      </c>
+      <c r="F12" s="78" t="s">
+        <v>345</v>
+      </c>
+      <c r="G12" s="59" t="s">
+        <v>21</v>
+      </c>
+      <c r="H12" s="39" t="s">
+        <v>346</v>
+      </c>
+      <c r="I12" s="38">
+        <v>46009</v>
+      </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="7"/>
-      <c r="C13" s="23"/>
-      <c r="D13" s="37"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="11"/>
-      <c r="G13" s="36"/>
-      <c r="H13" s="39"/>
-      <c r="I13" s="38"/>
+      <c r="B13" s="7">
+        <v>46009</v>
+      </c>
+      <c r="C13" s="23">
+        <v>46015</v>
+      </c>
+      <c r="D13" s="86">
+        <v>135938263</v>
+      </c>
+      <c r="E13" s="17">
+        <v>3450191701</v>
+      </c>
+      <c r="F13" s="78" t="s">
+        <v>347</v>
+      </c>
+      <c r="G13" s="59" t="s">
+        <v>21</v>
+      </c>
+      <c r="H13" s="39" t="s">
+        <v>348</v>
+      </c>
+      <c r="I13" s="38">
+        <v>46009</v>
+      </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="7"/>
-      <c r="C14" s="23"/>
-      <c r="D14" s="37"/>
-      <c r="E14" s="17"/>
-      <c r="F14" s="11"/>
-      <c r="G14" s="36"/>
-      <c r="H14" s="39"/>
-      <c r="I14" s="38"/>
+      <c r="B14" s="7">
+        <v>46009</v>
+      </c>
+      <c r="C14" s="23">
+        <v>46015</v>
+      </c>
+      <c r="D14" s="86">
+        <v>135935964</v>
+      </c>
+      <c r="E14" s="17">
+        <v>3450191492</v>
+      </c>
+      <c r="F14" s="78" t="s">
+        <v>349</v>
+      </c>
+      <c r="G14" s="59" t="s">
+        <v>21</v>
+      </c>
+      <c r="H14" s="39" t="s">
+        <v>350</v>
+      </c>
+      <c r="I14" s="38">
+        <v>46009</v>
+      </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B15" s="7"/>
-      <c r="C15" s="23"/>
-      <c r="D15" s="37"/>
-      <c r="E15" s="17"/>
-      <c r="F15" s="11"/>
-      <c r="G15" s="36"/>
-      <c r="H15" s="39"/>
-      <c r="I15" s="38"/>
+      <c r="B15" s="7">
+        <v>46009</v>
+      </c>
+      <c r="C15" s="23">
+        <v>46015</v>
+      </c>
+      <c r="D15" s="86">
+        <v>135937920</v>
+      </c>
+      <c r="E15" s="17">
+        <v>3450191680</v>
+      </c>
+      <c r="F15" s="78" t="s">
+        <v>351</v>
+      </c>
+      <c r="G15" s="59" t="s">
+        <v>21</v>
+      </c>
+      <c r="H15" s="39" t="s">
+        <v>350</v>
+      </c>
+      <c r="I15" s="38">
+        <v>46009</v>
+      </c>
     </row>
     <row r="16" spans="1:9">
-      <c r="A16" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B16" s="7"/>
-      <c r="C16" s="23"/>
-      <c r="D16" s="37"/>
-      <c r="E16" s="17"/>
-      <c r="F16" s="11"/>
-      <c r="G16" s="36"/>
-      <c r="H16" s="39"/>
-      <c r="I16" s="38"/>
+      <c r="A16" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="B16" s="7">
+        <v>46010</v>
+      </c>
+      <c r="C16" s="23">
+        <v>46015</v>
+      </c>
+      <c r="D16" s="86">
+        <v>135959691</v>
+      </c>
+      <c r="E16" s="17">
+        <v>3450193153</v>
+      </c>
+      <c r="F16" s="78" t="s">
+        <v>352</v>
+      </c>
+      <c r="G16" s="59" t="s">
+        <v>11</v>
+      </c>
+      <c r="H16" s="39" t="s">
+        <v>331</v>
+      </c>
+      <c r="I16" s="38">
+        <v>46014</v>
+      </c>
     </row>
     <row r="17" spans="1:9">
-      <c r="A17" s="25" t="s">
-        <v>9</v>
-      </c>
-      <c r="B17" s="7"/>
-      <c r="C17" s="23"/>
-      <c r="D17" s="37"/>
-      <c r="E17" s="17"/>
-      <c r="F17" s="11"/>
-      <c r="G17" s="36"/>
-      <c r="H17" s="39"/>
-      <c r="I17" s="38"/>
+      <c r="A17" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B17" s="7">
+        <v>46009</v>
+      </c>
+      <c r="C17" s="23">
+        <v>46015</v>
+      </c>
+      <c r="D17" s="86">
+        <v>135928783</v>
+      </c>
+      <c r="E17" s="17">
+        <v>3450190777</v>
+      </c>
+      <c r="F17" s="78" t="s">
+        <v>134</v>
+      </c>
+      <c r="G17" s="59" t="s">
+        <v>21</v>
+      </c>
+      <c r="H17" s="39" t="s">
+        <v>353</v>
+      </c>
+      <c r="I17" s="38">
+        <v>46009</v>
+      </c>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B18" s="7"/>
-      <c r="C18" s="23"/>
-      <c r="D18" s="37"/>
-      <c r="E18" s="17"/>
-      <c r="F18" s="11"/>
-      <c r="G18" s="36"/>
-      <c r="H18" s="39"/>
-      <c r="I18" s="38"/>
+      <c r="B18" s="7">
+        <v>46012</v>
+      </c>
+      <c r="C18" s="23">
+        <v>46015</v>
+      </c>
+      <c r="D18" s="86">
+        <v>135968030</v>
+      </c>
+      <c r="E18" s="17">
+        <v>3450193813</v>
+      </c>
+      <c r="F18" s="78" t="s">
+        <v>336</v>
+      </c>
+      <c r="G18" s="59" t="s">
+        <v>37</v>
+      </c>
+      <c r="H18" s="39" t="s">
+        <v>38</v>
+      </c>
+      <c r="I18" s="38">
+        <v>46012</v>
+      </c>
     </row>
     <row r="19" spans="1:9">
-      <c r="A19" s="6"/>
-      <c r="B19" s="7"/>
-      <c r="C19" s="23"/>
-      <c r="D19" s="37"/>
-      <c r="E19" s="17"/>
-      <c r="F19" s="11"/>
-      <c r="G19" s="36"/>
-      <c r="H19" s="39"/>
-      <c r="I19" s="38"/>
+      <c r="A19" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B19" s="7">
+        <v>46019</v>
+      </c>
+      <c r="C19" s="23">
+        <v>46015</v>
+      </c>
+      <c r="D19" s="86">
+        <v>135977998</v>
+      </c>
+      <c r="E19" s="17">
+        <v>3450194430</v>
+      </c>
+      <c r="F19" s="78" t="s">
+        <v>354</v>
+      </c>
+      <c r="G19" s="59" t="s">
+        <v>11</v>
+      </c>
+      <c r="H19" s="39" t="s">
+        <v>331</v>
+      </c>
+      <c r="I19" s="38">
+        <v>46014</v>
+      </c>
     </row>
     <row r="20" spans="1:9">
-      <c r="A20" s="6"/>
-      <c r="B20" s="7"/>
-      <c r="C20" s="23"/>
-      <c r="D20" s="37"/>
-      <c r="E20" s="17"/>
-      <c r="F20" s="11"/>
-      <c r="G20" s="36"/>
-      <c r="H20" s="39"/>
-      <c r="I20" s="38"/>
+      <c r="A20" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B20" s="7">
+        <v>46014</v>
+      </c>
+      <c r="C20" s="23">
+        <v>46015</v>
+      </c>
+      <c r="D20" s="86">
+        <v>135998362</v>
+      </c>
+      <c r="E20" s="17">
+        <v>3450195617</v>
+      </c>
+      <c r="F20" s="78" t="s">
+        <v>355</v>
+      </c>
+      <c r="G20" s="59" t="s">
+        <v>37</v>
+      </c>
+      <c r="H20" s="39" t="s">
+        <v>38</v>
+      </c>
+      <c r="I20" s="38">
+        <v>46014</v>
+      </c>
     </row>
     <row r="21" spans="1:9">
-      <c r="A21" s="6"/>
-      <c r="B21" s="7"/>
-      <c r="C21" s="23"/>
-      <c r="D21" s="37"/>
-      <c r="E21" s="17"/>
-      <c r="F21" s="11"/>
-      <c r="G21" s="36"/>
-      <c r="H21" s="39"/>
-      <c r="I21" s="38"/>
+      <c r="A21" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B21" s="7">
+        <v>46007</v>
+      </c>
+      <c r="C21" s="23">
+        <v>46015</v>
+      </c>
+      <c r="D21" s="86">
+        <v>135997220</v>
+      </c>
+      <c r="E21" s="17">
+        <v>3450186432</v>
+      </c>
+      <c r="F21" s="78" t="s">
+        <v>356</v>
+      </c>
+      <c r="G21" s="59" t="s">
+        <v>37</v>
+      </c>
+      <c r="H21" s="39" t="s">
+        <v>38</v>
+      </c>
+      <c r="I21" s="38">
+        <v>46007</v>
+      </c>
     </row>
     <row r="22" spans="1:9">
-      <c r="A22" s="6"/>
-      <c r="B22" s="7"/>
-      <c r="C22" s="23"/>
-      <c r="D22" s="37"/>
-      <c r="E22" s="17"/>
-      <c r="F22" s="11"/>
-      <c r="G22" s="36"/>
-      <c r="H22" s="39"/>
-      <c r="I22" s="38"/>
+      <c r="A22" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B22" s="7">
+        <v>46009</v>
+      </c>
+      <c r="C22" s="23">
+        <v>46015</v>
+      </c>
+      <c r="D22" s="86">
+        <v>135925497</v>
+      </c>
+      <c r="E22" s="17">
+        <v>3450190469</v>
+      </c>
+      <c r="F22" s="78" t="s">
+        <v>357</v>
+      </c>
+      <c r="G22" s="59" t="s">
+        <v>40</v>
+      </c>
+      <c r="H22" s="39" t="s">
+        <v>193</v>
+      </c>
+      <c r="I22" s="38">
+        <v>46009</v>
+      </c>
     </row>
     <row r="23" spans="1:9">
-      <c r="A23" s="6"/>
-      <c r="B23" s="7"/>
-      <c r="C23" s="23"/>
-      <c r="D23" s="37"/>
-      <c r="E23" s="17"/>
-      <c r="F23" s="11"/>
-      <c r="G23" s="36"/>
-      <c r="H23" s="39"/>
-      <c r="I23" s="38"/>
+      <c r="A23" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B23" s="7">
+        <v>46002</v>
+      </c>
+      <c r="C23" s="23">
+        <v>46015</v>
+      </c>
+      <c r="D23" s="86">
+        <v>135818220</v>
+      </c>
+      <c r="E23" s="17">
+        <v>3450181560</v>
+      </c>
+      <c r="F23" s="78" t="s">
+        <v>358</v>
+      </c>
+      <c r="G23" s="59" t="s">
+        <v>15</v>
+      </c>
+      <c r="H23" s="39" t="s">
+        <v>359</v>
+      </c>
+      <c r="I23" s="38">
+        <v>46013</v>
+      </c>
     </row>
     <row r="24" spans="1:9">
-      <c r="A24" s="6"/>
-      <c r="B24" s="7"/>
-      <c r="C24" s="23"/>
-      <c r="D24" s="37"/>
-      <c r="E24" s="17"/>
-      <c r="F24" s="11"/>
-      <c r="G24" s="36"/>
-      <c r="H24" s="39"/>
-      <c r="I24" s="38"/>
+      <c r="A24" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B24" s="7">
+        <v>46000</v>
+      </c>
+      <c r="C24" s="23">
+        <v>46015</v>
+      </c>
+      <c r="D24" s="86">
+        <v>135777294</v>
+      </c>
+      <c r="E24" s="17">
+        <v>3450178369</v>
+      </c>
+      <c r="F24" s="78" t="s">
+        <v>360</v>
+      </c>
+      <c r="G24" s="59" t="s">
+        <v>15</v>
+      </c>
+      <c r="H24" s="91" t="s">
+        <v>361</v>
+      </c>
+      <c r="I24" s="38">
+        <v>46003</v>
+      </c>
     </row>
     <row r="25" spans="1:9">
-      <c r="A25" s="6"/>
-      <c r="B25" s="7"/>
-      <c r="C25" s="23"/>
-      <c r="D25" s="37"/>
-      <c r="E25" s="17"/>
-      <c r="F25" s="11"/>
-      <c r="G25" s="36"/>
-      <c r="H25" s="39"/>
-      <c r="I25" s="38"/>
+      <c r="A25" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B25" s="7">
+        <v>46002</v>
+      </c>
+      <c r="C25" s="23">
+        <v>46015</v>
+      </c>
+      <c r="D25" s="86">
+        <v>135808265</v>
+      </c>
+      <c r="E25" s="17">
+        <v>3450180558</v>
+      </c>
+      <c r="F25" s="78" t="s">
+        <v>362</v>
+      </c>
+      <c r="G25" s="59" t="s">
+        <v>15</v>
+      </c>
+      <c r="H25" s="91" t="s">
+        <v>363</v>
+      </c>
+      <c r="I25" s="38">
+        <v>46014</v>
+      </c>
     </row>
     <row r="26" spans="1:9">
-      <c r="A26" s="6"/>
-      <c r="B26" s="7"/>
-      <c r="C26" s="23"/>
-      <c r="D26" s="37"/>
-      <c r="E26" s="17"/>
-      <c r="F26" s="11"/>
-      <c r="G26" s="36"/>
-      <c r="H26" s="39"/>
-      <c r="I26" s="38"/>
+      <c r="A26" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B26" s="7">
+        <v>46009</v>
+      </c>
+      <c r="C26" s="23">
+        <v>46015</v>
+      </c>
+      <c r="D26" s="86">
+        <v>135925662</v>
+      </c>
+      <c r="E26" s="17">
+        <v>3450190502</v>
+      </c>
+      <c r="F26" s="78" t="s">
+        <v>42</v>
+      </c>
+      <c r="G26" s="59" t="s">
+        <v>21</v>
+      </c>
+      <c r="H26" s="12" t="s">
+        <v>364</v>
+      </c>
+      <c r="I26" s="38">
+        <v>46009</v>
+      </c>
     </row>
     <row r="27" spans="1:9">
-      <c r="A27" s="6"/>
-      <c r="B27" s="7"/>
-      <c r="C27" s="23"/>
-      <c r="D27" s="37"/>
-      <c r="E27" s="17"/>
-      <c r="F27" s="11"/>
-      <c r="G27" s="36"/>
-      <c r="H27" s="39"/>
-      <c r="I27" s="38"/>
+      <c r="A27" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B27" s="7">
+        <v>46008</v>
+      </c>
+      <c r="C27" s="23">
+        <v>46015</v>
+      </c>
+      <c r="D27" s="86">
+        <v>135908428</v>
+      </c>
+      <c r="E27" s="17">
+        <v>3450189138</v>
+      </c>
+      <c r="F27" s="78" t="s">
+        <v>365</v>
+      </c>
+      <c r="G27" s="59" t="s">
+        <v>21</v>
+      </c>
+      <c r="H27" s="12" t="s">
+        <v>366</v>
+      </c>
+      <c r="I27" s="38">
+        <v>46008</v>
+      </c>
     </row>
     <row r="28" spans="1:9">
-      <c r="A28" s="6"/>
-      <c r="B28" s="7"/>
-      <c r="C28" s="23"/>
-      <c r="D28" s="37"/>
-      <c r="E28" s="17"/>
-      <c r="F28" s="11"/>
-      <c r="G28" s="36"/>
-      <c r="H28" s="39"/>
-      <c r="I28" s="38"/>
+      <c r="A28" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B28" s="7">
+        <v>46008</v>
+      </c>
+      <c r="C28" s="23">
+        <v>46015</v>
+      </c>
+      <c r="D28" s="86">
+        <v>135902709</v>
+      </c>
+      <c r="E28" s="17">
+        <v>3450188566</v>
+      </c>
+      <c r="F28" s="78" t="s">
+        <v>367</v>
+      </c>
+      <c r="G28" s="59" t="s">
+        <v>21</v>
+      </c>
+      <c r="H28" s="12" t="s">
+        <v>368</v>
+      </c>
+      <c r="I28" s="38">
+        <v>46008</v>
+      </c>
     </row>
     <row r="29" spans="1:9">
-      <c r="A29" s="6"/>
-      <c r="B29" s="41"/>
-      <c r="C29" s="23"/>
-      <c r="D29" s="37"/>
-      <c r="E29" s="17"/>
-      <c r="F29" s="11"/>
-      <c r="G29" s="36"/>
-      <c r="H29" s="39"/>
-      <c r="I29" s="38"/>
+      <c r="A29" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B29" s="7">
+        <v>46009</v>
+      </c>
+      <c r="C29" s="23">
+        <v>46015</v>
+      </c>
+      <c r="D29" s="86">
+        <v>135932515</v>
+      </c>
+      <c r="E29" s="17">
+        <v>3450191118</v>
+      </c>
+      <c r="F29" s="78" t="s">
+        <v>369</v>
+      </c>
+      <c r="G29" s="59" t="s">
+        <v>21</v>
+      </c>
+      <c r="H29" s="12" t="s">
+        <v>370</v>
+      </c>
+      <c r="I29" s="38">
+        <v>46009</v>
+      </c>
     </row>
     <row r="30" spans="1:9">
-      <c r="A30" s="6"/>
-      <c r="B30" s="7"/>
-      <c r="C30" s="23"/>
-      <c r="D30" s="37"/>
-      <c r="E30" s="17"/>
-      <c r="F30" s="11"/>
-      <c r="G30" s="36"/>
-      <c r="H30" s="12"/>
-      <c r="I30" s="38"/>
+      <c r="A30" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B30" s="7">
+        <v>46009</v>
+      </c>
+      <c r="C30" s="23">
+        <v>46015</v>
+      </c>
+      <c r="D30" s="86">
+        <v>135932745</v>
+      </c>
+      <c r="E30" s="17">
+        <v>3450191140</v>
+      </c>
+      <c r="F30" s="78" t="s">
+        <v>371</v>
+      </c>
+      <c r="G30" s="59" t="s">
+        <v>21</v>
+      </c>
+      <c r="H30" s="12" t="s">
+        <v>372</v>
+      </c>
+      <c r="I30" s="38">
+        <v>46009</v>
+      </c>
     </row>
     <row r="31" spans="1:9">
       <c r="A31" s="6"/>
       <c r="B31" s="7"/>
       <c r="C31" s="23"/>
-      <c r="D31" s="37"/>
-      <c r="E31" s="17"/>
-      <c r="F31" s="11"/>
+      <c r="D31" s="90"/>
+      <c r="E31" s="51"/>
+      <c r="F31" s="29"/>
       <c r="G31" s="36"/>
       <c r="H31" s="12"/>
       <c r="I31" s="38"/>
@@ -8563,82 +10861,27 @@
     </row>
     <row r="38" spans="1:9">
       <c r="A38" s="6"/>
-      <c r="B38" s="7"/>
-      <c r="C38" s="23"/>
-      <c r="D38" s="37"/>
+      <c r="B38" s="8"/>
+      <c r="C38" s="7"/>
+      <c r="D38" s="28"/>
       <c r="E38" s="17"/>
-      <c r="F38" s="11"/>
+      <c r="F38" s="12"/>
       <c r="G38" s="36"/>
       <c r="H38" s="12"/>
-      <c r="I38" s="38"/>
-    </row>
-    <row r="39" spans="1:9">
-      <c r="A39" s="6"/>
-      <c r="B39" s="7"/>
-      <c r="C39" s="23"/>
-      <c r="D39" s="37"/>
-      <c r="E39" s="17"/>
-      <c r="F39" s="11"/>
-      <c r="G39" s="36"/>
-      <c r="H39" s="12"/>
-      <c r="I39" s="38"/>
-    </row>
-    <row r="40" spans="1:9">
-      <c r="A40" s="6"/>
-      <c r="B40" s="7"/>
-      <c r="C40" s="23"/>
-      <c r="D40" s="37"/>
-      <c r="E40" s="17"/>
-      <c r="F40" s="11"/>
-      <c r="G40" s="36"/>
-      <c r="H40" s="12"/>
-      <c r="I40" s="38"/>
-    </row>
-    <row r="41" spans="1:9">
-      <c r="A41" s="6"/>
-      <c r="B41" s="7"/>
-      <c r="C41" s="23"/>
-      <c r="D41" s="37"/>
-      <c r="E41" s="17"/>
-      <c r="F41" s="11"/>
-      <c r="G41" s="36"/>
-      <c r="H41" s="12"/>
-      <c r="I41" s="38"/>
-    </row>
-    <row r="42" spans="1:9">
-      <c r="A42" s="6"/>
-      <c r="B42" s="7"/>
-      <c r="C42" s="23"/>
-      <c r="D42" s="37"/>
-      <c r="E42" s="17"/>
-      <c r="F42" s="11"/>
-      <c r="G42" s="36"/>
-      <c r="H42" s="12"/>
-      <c r="I42" s="38"/>
-    </row>
-    <row r="43" spans="1:9">
-      <c r="A43" s="6"/>
-      <c r="B43" s="8"/>
-      <c r="C43" s="7"/>
-      <c r="D43" s="28"/>
-      <c r="E43" s="17"/>
-      <c r="F43" s="12"/>
-      <c r="G43" s="36"/>
-      <c r="H43" s="12"/>
-      <c r="I43" s="12"/>
+      <c r="I38" s="12"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B1:C1">
-    <cfRule type="notContainsBlanks" priority="1">
+    <cfRule type="notContainsBlanks" priority="2">
       <formula>LEN(TRIM(B1))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G43" xr:uid="{6BE23EBC-FF30-4764-B2ED-DADD17818F83}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A31:A37" xr:uid="{739D573C-5EC2-4CE2-AADE-3BE4A15DFB2F}">
+      <formula1>$J$2</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G38" xr:uid="{6BE23EBC-FF30-4764-B2ED-DADD17818F83}">
       <formula1>"Vistoria Frustrada;,Vistoria Recusada,Bônus;,Desistência;,Inadimplência;,Política de Aceitação;,Duplicidade;,Demais Motivos,Falta de Vistoria;,"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A19:A42" xr:uid="{739D573C-5EC2-4CE2-AADE-3BE4A15DFB2F}">
-      <formula1>$J$2</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8649,7 +10892,7 @@
           <x14:formula1>
             <xm:f>'22.12'!#REF!</xm:f>
           </x14:formula1>
-          <xm:sqref>A2:A18</xm:sqref>
+          <xm:sqref>A2:A30</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -8658,6 +10901,65 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10001</Type>
+    <SequenceNumber>1000</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10002</Type>
+    <SequenceNumber>1001</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10004</Type>
+    <SequenceNumber>1002</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10006</Type>
+    <SequenceNumber>1003</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+</spe:Receivers>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010006E7B04763359F4AAB0FC84D5027BFC8" ma:contentTypeVersion="44" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="522e863aef51f288a2c445becadad51a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xmlns:ns3="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="e2cd90bc508d2ca63574b1ae88af87c9" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -9035,7 +11337,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <_dlc_DocId xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">QAFFA7D2F2TC-2102087286-531146</_dlc_DocId>
@@ -9078,77 +11380,18 @@
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC9CB02D-0F63-4CE2-B316-61A87327416C}"/>
 </file>
 
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10001</Type>
-    <SequenceNumber>1000</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10002</Type>
-    <SequenceNumber>1001</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10004</Type>
-    <SequenceNumber>1002</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10006</Type>
-    <SequenceNumber>1003</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-</spe:Receivers>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13279B2D-D76C-4CA7-B517-83259B9C0FB4}"/>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0D6986EB-BB58-4D50-AC35-394136E3DEB9}"/>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C48653D8-7562-408C-9B57-D83FFA71DB43}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC9CB02D-0F63-4CE2-B316-61A87327416C}"/>
-</file>
-
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13279B2D-D76C-4CA7-B517-83259B9C0FB4}"/>
 </file>